--- a/Computation/Pensioners Increase Table Loan 1.12.26.xlsx
+++ b/Computation/Pensioners Increase Table Loan 1.12.26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff\Desktop\peoples-information-system\Computation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD426E3-7B45-4BB7-B3A1-BE759DE523A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201D8A0C-5E95-43EF-9C34-07283D02BC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA ENTRY" sheetId="3" r:id="rId1"/>
@@ -2433,60 +2433,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2519,6 +2465,60 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2553,37 +2553,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="32" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2592,104 +2589,71 @@
     <xf numFmtId="172" fontId="32" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2708,6 +2672,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2740,112 +2707,172 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2883,38 +2910,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="17" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D4" s="104">
         <f>'Computation Table'!C82</f>
-        <v>48000.096012647933</v>
+        <v>22799.94860170356</v>
       </c>
       <c r="E4" s="104">
         <f>'Computation Table'!C56</f>
@@ -5039,7 +5039,7 @@
         <v>25000</v>
       </c>
       <c r="D5" s="105">
-        <v>37700.5</v>
+        <v>15979.6</v>
       </c>
       <c r="E5" s="105">
         <v>25000</v>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D8" s="106">
         <f>'Computation Table'!C84</f>
-        <v>2827.5374999999999</v>
+        <v>1198.47</v>
       </c>
       <c r="E8" s="106">
         <f>'Computation Table'!E58</f>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D9" s="106">
         <f>'Computation Table'!C85</f>
-        <v>904.8119999999999</v>
+        <v>383.5104</v>
       </c>
       <c r="E9" s="106">
         <f>'Computation Table'!C59</f>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="105">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E10" s="105"/>
       <c r="F10" s="105">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D12" s="106">
         <f>'Computation Table'!C88</f>
-        <v>754.01</v>
+        <v>319.59200000000004</v>
       </c>
       <c r="E12" s="106">
         <f>'Computation Table'!C62</f>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D13" s="106">
         <f t="shared" ref="D13:F13" si="0">SUM(D5:D12)</f>
-        <v>42486.859499999999</v>
+        <v>20181.172399999999</v>
       </c>
       <c r="E13" s="106">
         <f t="shared" si="0"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D16" s="108">
         <f>'Computation Table'!C100</f>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="E16" s="108">
         <f>'Computation Table'!C74</f>
@@ -6496,14 +6496,14 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" s="1"/>
-      <c r="C20" s="251" t="s">
+      <c r="C20" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="253"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="235"/>
       <c r="I20" s="34"/>
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
@@ -6519,12 +6519,12 @@
       <c r="U20" s="57"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="C21" s="254"/>
-      <c r="D21" s="255"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="255"/>
-      <c r="H21" s="256"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="238"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
@@ -6598,7 +6598,7 @@
       <c r="U23" s="58"/>
     </row>
     <row r="24" spans="2:21" ht="21">
-      <c r="C24" s="257" t="s">
+      <c r="C24" s="239" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="12" t="s">
@@ -6616,22 +6616,22 @@
       </c>
       <c r="H24" s="15"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="258" t="s">
+      <c r="K24" s="240" t="s">
         <v>58</v>
       </c>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="240"/>
+      <c r="N24" s="240"/>
+      <c r="O24" s="240"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="240"/>
+      <c r="R24" s="240"/>
+      <c r="S24" s="240"/>
+      <c r="T24" s="240"/>
       <c r="U24" s="58"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="C25" s="257"/>
+      <c r="C25" s="239"/>
       <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
@@ -6644,22 +6644,22 @@
       <c r="G25" s="2"/>
       <c r="H25" s="15"/>
       <c r="J25" s="42"/>
-      <c r="K25" s="259" t="s">
+      <c r="K25" s="241" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="259"/>
-      <c r="S25" s="259"/>
-      <c r="T25" s="259"/>
+      <c r="L25" s="241"/>
+      <c r="M25" s="241"/>
+      <c r="N25" s="241"/>
+      <c r="O25" s="241"/>
+      <c r="P25" s="241"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
       <c r="U25" s="58"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="C26" s="257"/>
+      <c r="C26" s="239"/>
       <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
@@ -6689,7 +6689,7 @@
       <c r="U26" s="58"/>
     </row>
     <row r="27" spans="2:21" ht="17.399999999999999">
-      <c r="C27" s="257"/>
+      <c r="C27" s="239"/>
       <c r="D27" s="2" t="s">
         <v>57</v>
       </c>
@@ -6701,18 +6701,18 @@
         <v>74252</v>
       </c>
       <c r="J27" s="42"/>
-      <c r="K27" s="260" t="s">
+      <c r="K27" s="242" t="s">
         <v>60</v>
       </c>
-      <c r="L27" s="260"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="260"/>
-      <c r="O27" s="260"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="260"/>
-      <c r="R27" s="260"/>
-      <c r="S27" s="260"/>
-      <c r="T27" s="260"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
+      <c r="N27" s="242"/>
+      <c r="O27" s="242"/>
+      <c r="P27" s="242"/>
+      <c r="Q27" s="242"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
       <c r="U27" s="58"/>
     </row>
     <row r="28" spans="2:21">
@@ -6795,11 +6795,11 @@
       <c r="R29" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="232">
         <f>E24</f>
         <v>45847</v>
       </c>
-      <c r="T29" s="250"/>
+      <c r="T29" s="232"/>
       <c r="U29" s="58"/>
     </row>
     <row r="30" spans="2:21" ht="15.6">
@@ -7105,12 +7105,12 @@
       <c r="O36" s="111"/>
       <c r="P36" s="112"/>
       <c r="Q36" s="115"/>
-      <c r="R36" s="236">
+      <c r="R36" s="249">
         <f>C4</f>
         <v>74252</v>
       </c>
-      <c r="S36" s="236"/>
-      <c r="T36" s="236"/>
+      <c r="S36" s="249"/>
+      <c r="T36" s="249"/>
       <c r="U36" s="58"/>
     </row>
     <row r="37" spans="2:21" ht="15.6">
@@ -7149,9 +7149,9 @@
       <c r="O37" s="111"/>
       <c r="P37" s="112"/>
       <c r="Q37" s="115"/>
-      <c r="R37" s="249"/>
-      <c r="S37" s="249"/>
-      <c r="T37" s="249"/>
+      <c r="R37" s="250"/>
+      <c r="S37" s="250"/>
+      <c r="T37" s="250"/>
       <c r="U37" s="58"/>
     </row>
     <row r="38" spans="2:21" ht="15.6">
@@ -7194,12 +7194,12 @@
       <c r="O38" s="118"/>
       <c r="P38" s="116"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="236">
+      <c r="R38" s="249">
         <f>-C14</f>
         <v>0</v>
       </c>
-      <c r="S38" s="236"/>
-      <c r="T38" s="236"/>
+      <c r="S38" s="249"/>
+      <c r="T38" s="249"/>
       <c r="U38" s="47"/>
     </row>
     <row r="39" spans="2:21" ht="15.6">
@@ -7242,12 +7242,12 @@
       <c r="O39" s="118"/>
       <c r="P39" s="116"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="236">
+      <c r="R39" s="249">
         <f>-C8</f>
         <v>0</v>
       </c>
-      <c r="S39" s="236"/>
-      <c r="T39" s="236"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
       <c r="U39" s="47"/>
     </row>
     <row r="40" spans="2:21" ht="15.6">
@@ -7475,12 +7475,12 @@
       <c r="O44" s="111"/>
       <c r="P44" s="112"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="236">
+      <c r="R44" s="249">
         <f>SUM(R36:T43)</f>
         <v>37000</v>
       </c>
-      <c r="S44" s="236"/>
-      <c r="T44" s="236"/>
+      <c r="S44" s="249"/>
+      <c r="T44" s="249"/>
       <c r="U44" s="58"/>
     </row>
     <row r="45" spans="2:21">
@@ -7646,11 +7646,11 @@
       <c r="O48" s="116"/>
       <c r="P48" s="116"/>
       <c r="Q48" s="116"/>
-      <c r="R48" s="237">
+      <c r="R48" s="255">
         <f>E25</f>
         <v>60</v>
       </c>
-      <c r="S48" s="237"/>
+      <c r="S48" s="255"/>
       <c r="T48" s="109" t="s">
         <v>85</v>
       </c>
@@ -7694,12 +7694,12 @@
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
       <c r="Q49" s="116"/>
-      <c r="R49" s="238">
+      <c r="R49" s="256">
         <f>C1</f>
         <v>1541.3493922672235</v>
       </c>
-      <c r="S49" s="238"/>
-      <c r="T49" s="238"/>
+      <c r="S49" s="256"/>
+      <c r="T49" s="256"/>
       <c r="U49" s="58"/>
     </row>
     <row r="50" spans="2:21" ht="15">
@@ -7740,12 +7740,12 @@
       <c r="O50" s="116"/>
       <c r="P50" s="116"/>
       <c r="Q50" s="116"/>
-      <c r="R50" s="239">
+      <c r="R50" s="257">
         <f>B28</f>
         <v>45909</v>
       </c>
-      <c r="S50" s="239"/>
-      <c r="T50" s="239"/>
+      <c r="S50" s="257"/>
+      <c r="T50" s="257"/>
       <c r="U50" s="58"/>
     </row>
     <row r="51" spans="2:21" ht="15">
@@ -7786,12 +7786,12 @@
       <c r="O51" s="116"/>
       <c r="P51" s="116"/>
       <c r="Q51" s="116"/>
-      <c r="R51" s="239">
+      <c r="R51" s="257">
         <f>G24</f>
         <v>47704</v>
       </c>
-      <c r="S51" s="239"/>
-      <c r="T51" s="239"/>
+      <c r="S51" s="257"/>
+      <c r="T51" s="257"/>
       <c r="U51" s="58"/>
     </row>
     <row r="52" spans="2:21" ht="15">
@@ -7832,12 +7832,12 @@
       <c r="O52" s="116"/>
       <c r="P52" s="116"/>
       <c r="Q52" s="116"/>
-      <c r="R52" s="240">
+      <c r="R52" s="258">
         <f>C16</f>
         <v>9.4100503202476204E-2</v>
       </c>
-      <c r="S52" s="240"/>
-      <c r="T52" s="240"/>
+      <c r="S52" s="258"/>
+      <c r="T52" s="258"/>
       <c r="U52" s="58"/>
     </row>
     <row r="53" spans="2:21" ht="15">
@@ -7878,12 +7878,12 @@
       <c r="O53" s="116"/>
       <c r="P53" s="116"/>
       <c r="Q53" s="116"/>
-      <c r="R53" s="240">
+      <c r="R53" s="258">
         <f>C15</f>
         <v>0.09</v>
       </c>
-      <c r="S53" s="240"/>
-      <c r="T53" s="240"/>
+      <c r="S53" s="258"/>
+      <c r="T53" s="258"/>
       <c r="U53" s="58"/>
     </row>
     <row r="54" spans="2:21" ht="15" thickBot="1">
@@ -8143,19 +8143,19 @@
         <v>1167880610.9452055</v>
       </c>
       <c r="J60" s="42"/>
-      <c r="K60" s="241" t="s">
+      <c r="K60" s="259" t="s">
         <v>249</v>
       </c>
-      <c r="L60" s="241"/>
-      <c r="M60" s="241"/>
+      <c r="L60" s="259"/>
+      <c r="M60" s="259"/>
       <c r="N60" s="112"/>
       <c r="O60" s="112"/>
       <c r="P60" s="112"/>
-      <c r="R60" s="234" t="s">
+      <c r="R60" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="S60" s="234"/>
-      <c r="T60" s="234"/>
+      <c r="S60" s="253"/>
+      <c r="T60" s="253"/>
       <c r="U60" s="58"/>
     </row>
     <row r="61" spans="2:21">
@@ -8195,11 +8195,11 @@
       <c r="N61" s="43"/>
       <c r="O61" s="44"/>
       <c r="P61" s="43"/>
-      <c r="R61" s="242" t="s">
+      <c r="R61" s="260" t="s">
         <v>90</v>
       </c>
-      <c r="S61" s="232"/>
-      <c r="T61" s="232"/>
+      <c r="S61" s="251"/>
+      <c r="T61" s="251"/>
       <c r="U61" s="58"/>
     </row>
     <row r="62" spans="2:21">
@@ -8482,15 +8482,15 @@
         <v>16570982015.097771</v>
       </c>
       <c r="J69" s="16"/>
-      <c r="K69" s="234" t="s">
+      <c r="K69" s="253" t="s">
         <v>250</v>
       </c>
-      <c r="L69" s="235"/>
-      <c r="M69" s="235"/>
-      <c r="R69" s="241" t="s">
+      <c r="L69" s="254"/>
+      <c r="M69" s="254"/>
+      <c r="R69" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="S69" s="241"/>
+      <c r="S69" s="259"/>
       <c r="U69" s="119"/>
     </row>
     <row r="70" spans="2:21">
@@ -8531,10 +8531,10 @@
       <c r="O70" s="44"/>
       <c r="P70" s="43"/>
       <c r="Q70" s="43"/>
-      <c r="R70" s="233" t="s">
+      <c r="R70" s="252" t="s">
         <v>82</v>
       </c>
-      <c r="S70" s="233"/>
+      <c r="S70" s="252"/>
       <c r="T70" s="43"/>
       <c r="U70" s="58"/>
     </row>
@@ -9097,10 +9097,10 @@
         <f>SUM(N99:N102)</f>
         <v>37252</v>
       </c>
-      <c r="P98" s="232" t="s">
+      <c r="P98" s="251" t="s">
         <v>263</v>
       </c>
-      <c r="Q98" s="232"/>
+      <c r="Q98" s="251"/>
       <c r="V98" s="43"/>
     </row>
     <row r="99" spans="3:22">
@@ -9390,24 +9390,6 @@
     <protectedRange sqref="B28:C87" name="Range23"/>
   </protectedRanges>
   <mergeCells count="32">
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="C20:H21"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="K24:T24"/>
-    <mergeCell ref="K25:T25"/>
-    <mergeCell ref="K27:T27"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="R42:T42"/>
     <mergeCell ref="P98:Q98"/>
     <mergeCell ref="R70:S70"/>
     <mergeCell ref="K69:M69"/>
@@ -9422,6 +9404,24 @@
     <mergeCell ref="R60:T60"/>
     <mergeCell ref="R61:T61"/>
     <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="C20:H21"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="K24:T24"/>
+    <mergeCell ref="K25:T25"/>
+    <mergeCell ref="K27:T27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -20518,7 +20518,7 @@
       </c>
       <c r="C82" s="4">
         <f>C100*C94</f>
-        <v>48000.096012647933</v>
+        <v>22799.94860170356</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C83" s="66">
         <f>'DATA ENTRY'!D5</f>
-        <v>37700.5</v>
+        <v>15979.6</v>
       </c>
       <c r="D83" s="66"/>
       <c r="E83" s="66">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="C84" s="4">
         <f t="shared" ref="C84:AR84" si="437">C83*0.075</f>
-        <v>2827.5374999999999</v>
+        <v>1198.47</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="C85" s="4">
         <f>(C83/1000)*C94</f>
-        <v>904.8119999999999</v>
+        <v>383.5104</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="C86" s="4">
         <f>'DATA ENTRY'!D10</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4">
@@ -21492,7 +21492,7 @@
       </c>
       <c r="C88" s="4">
         <f>C93*C83*2</f>
-        <v>754.01</v>
+        <v>319.59200000000004</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C89" s="4">
         <f>SUM(C83:C88)</f>
-        <v>42486.859499999999</v>
+        <v>20181.172399999999</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="C100" s="66">
         <f>C99*C89</f>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="D100" s="66"/>
       <c r="E100" s="66">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="C102" s="4">
         <f>C82-C83</f>
-        <v>10299.596012647933</v>
+        <v>6820.3486017035593</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="C103" s="7">
         <f>C102/C82</f>
-        <v>0.21457448772464974</v>
+        <v>0.29913877091784141</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="7">
@@ -29288,14 +29288,14 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" s="1"/>
-      <c r="C20" s="251" t="s">
+      <c r="C20" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="253"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="235"/>
       <c r="I20" s="34"/>
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
@@ -29311,12 +29311,12 @@
       <c r="U20" s="57"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="C21" s="254"/>
-      <c r="D21" s="255"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="255"/>
-      <c r="H21" s="256"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="238"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
@@ -29390,7 +29390,7 @@
       <c r="U23" s="58"/>
     </row>
     <row r="24" spans="2:21" ht="21">
-      <c r="C24" s="257" t="s">
+      <c r="C24" s="239" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="12" t="s">
@@ -29408,22 +29408,22 @@
       </c>
       <c r="H24" s="15"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="258" t="s">
+      <c r="K24" s="240" t="s">
         <v>58</v>
       </c>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="240"/>
+      <c r="N24" s="240"/>
+      <c r="O24" s="240"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="240"/>
+      <c r="R24" s="240"/>
+      <c r="S24" s="240"/>
+      <c r="T24" s="240"/>
       <c r="U24" s="58"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="C25" s="257"/>
+      <c r="C25" s="239"/>
       <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
@@ -29436,22 +29436,22 @@
       <c r="G25" s="2"/>
       <c r="H25" s="15"/>
       <c r="J25" s="42"/>
-      <c r="K25" s="259" t="s">
+      <c r="K25" s="241" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="259"/>
-      <c r="S25" s="259"/>
-      <c r="T25" s="259"/>
+      <c r="L25" s="241"/>
+      <c r="M25" s="241"/>
+      <c r="N25" s="241"/>
+      <c r="O25" s="241"/>
+      <c r="P25" s="241"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
       <c r="U25" s="58"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="C26" s="257"/>
+      <c r="C26" s="239"/>
       <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
@@ -29481,7 +29481,7 @@
       <c r="U26" s="58"/>
     </row>
     <row r="27" spans="2:21" ht="17.399999999999999">
-      <c r="C27" s="257"/>
+      <c r="C27" s="239"/>
       <c r="D27" s="2" t="s">
         <v>57</v>
       </c>
@@ -29493,18 +29493,18 @@
         <v>30300.000000000004</v>
       </c>
       <c r="J27" s="42"/>
-      <c r="K27" s="260" t="s">
+      <c r="K27" s="242" t="s">
         <v>60</v>
       </c>
-      <c r="L27" s="260"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="260"/>
-      <c r="O27" s="260"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="260"/>
-      <c r="R27" s="260"/>
-      <c r="S27" s="260"/>
-      <c r="T27" s="260"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
+      <c r="N27" s="242"/>
+      <c r="O27" s="242"/>
+      <c r="P27" s="242"/>
+      <c r="Q27" s="242"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
       <c r="U27" s="58"/>
     </row>
     <row r="28" spans="2:21">
@@ -29587,11 +29587,11 @@
       <c r="R29" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="232">
         <f>E24</f>
         <v>45842</v>
       </c>
-      <c r="T29" s="250"/>
+      <c r="T29" s="232"/>
       <c r="U29" s="58"/>
     </row>
     <row r="30" spans="2:21" ht="15.6">
@@ -29897,12 +29897,12 @@
       <c r="O36" s="111"/>
       <c r="P36" s="112"/>
       <c r="Q36" s="115"/>
-      <c r="R36" s="236">
+      <c r="R36" s="249">
         <f>C4</f>
         <v>34415.833333333336</v>
       </c>
-      <c r="S36" s="236"/>
-      <c r="T36" s="236"/>
+      <c r="S36" s="249"/>
+      <c r="T36" s="249"/>
       <c r="U36" s="58"/>
     </row>
     <row r="37" spans="2:21" ht="15.6">
@@ -29941,9 +29941,9 @@
       <c r="O37" s="111"/>
       <c r="P37" s="112"/>
       <c r="Q37" s="115"/>
-      <c r="R37" s="249"/>
-      <c r="S37" s="249"/>
-      <c r="T37" s="249"/>
+      <c r="R37" s="250"/>
+      <c r="S37" s="250"/>
+      <c r="T37" s="250"/>
       <c r="U37" s="58"/>
     </row>
     <row r="38" spans="2:21" ht="15.6">
@@ -29986,12 +29986,12 @@
       <c r="O38" s="118"/>
       <c r="P38" s="116"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="236">
+      <c r="R38" s="249">
         <f>-C14</f>
         <v>0</v>
       </c>
-      <c r="S38" s="236"/>
-      <c r="T38" s="236"/>
+      <c r="S38" s="249"/>
+      <c r="T38" s="249"/>
       <c r="U38" s="47"/>
     </row>
     <row r="39" spans="2:21" ht="15.6">
@@ -30034,12 +30034,12 @@
       <c r="O39" s="118"/>
       <c r="P39" s="116"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="236">
+      <c r="R39" s="249">
         <f>-C8</f>
         <v>0</v>
       </c>
-      <c r="S39" s="236"/>
-      <c r="T39" s="236"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
       <c r="U39" s="47"/>
     </row>
     <row r="40" spans="2:21" ht="15.6">
@@ -30267,12 +30267,12 @@
       <c r="O44" s="111"/>
       <c r="P44" s="112"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="236">
+      <c r="R44" s="249">
         <f>SUM(R36:T43)</f>
         <v>30300.000000000004</v>
       </c>
-      <c r="S44" s="236"/>
-      <c r="T44" s="236"/>
+      <c r="S44" s="249"/>
+      <c r="T44" s="249"/>
       <c r="U44" s="58"/>
     </row>
     <row r="45" spans="2:21">
@@ -30438,11 +30438,11 @@
       <c r="O48" s="116"/>
       <c r="P48" s="116"/>
       <c r="Q48" s="116"/>
-      <c r="R48" s="237">
+      <c r="R48" s="255">
         <f>E25</f>
         <v>48</v>
       </c>
-      <c r="S48" s="237"/>
+      <c r="S48" s="255"/>
       <c r="T48" s="109" t="s">
         <v>85</v>
       </c>
@@ -30486,12 +30486,12 @@
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
       <c r="Q49" s="116"/>
-      <c r="R49" s="238">
+      <c r="R49" s="256">
         <f>C1</f>
         <v>852.8487877766371</v>
       </c>
-      <c r="S49" s="238"/>
-      <c r="T49" s="238"/>
+      <c r="S49" s="256"/>
+      <c r="T49" s="256"/>
       <c r="U49" s="58"/>
     </row>
     <row r="50" spans="2:21" ht="15">
@@ -30532,12 +30532,12 @@
       <c r="O50" s="116"/>
       <c r="P50" s="116"/>
       <c r="Q50" s="116"/>
-      <c r="R50" s="239">
+      <c r="R50" s="257">
         <f>B28</f>
         <v>45904</v>
       </c>
-      <c r="S50" s="239"/>
-      <c r="T50" s="239"/>
+      <c r="S50" s="257"/>
+      <c r="T50" s="257"/>
       <c r="U50" s="58"/>
     </row>
     <row r="51" spans="2:21" ht="15">
@@ -30578,12 +30578,12 @@
       <c r="O51" s="116"/>
       <c r="P51" s="116"/>
       <c r="Q51" s="116"/>
-      <c r="R51" s="239">
+      <c r="R51" s="257">
         <f>G24</f>
         <v>47699</v>
       </c>
-      <c r="S51" s="239"/>
-      <c r="T51" s="239"/>
+      <c r="S51" s="257"/>
+      <c r="T51" s="257"/>
       <c r="U51" s="58"/>
     </row>
     <row r="52" spans="2:21" ht="15">
@@ -30624,12 +30624,12 @@
       <c r="O52" s="116"/>
       <c r="P52" s="116"/>
       <c r="Q52" s="116"/>
-      <c r="R52" s="240">
+      <c r="R52" s="258">
         <f>C16</f>
         <v>9.4100503202476204E-2</v>
       </c>
-      <c r="S52" s="240"/>
-      <c r="T52" s="240"/>
+      <c r="S52" s="258"/>
+      <c r="T52" s="258"/>
       <c r="U52" s="58"/>
     </row>
     <row r="53" spans="2:21" ht="15">
@@ -30670,12 +30670,12 @@
       <c r="O53" s="116"/>
       <c r="P53" s="116"/>
       <c r="Q53" s="116"/>
-      <c r="R53" s="240">
+      <c r="R53" s="258">
         <f>C15</f>
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="S53" s="240"/>
-      <c r="T53" s="240"/>
+      <c r="S53" s="258"/>
+      <c r="T53" s="258"/>
       <c r="U53" s="58"/>
     </row>
     <row r="54" spans="2:21" ht="15" thickBot="1">
@@ -30935,19 +30935,19 @@
         <v>17860.257896515872</v>
       </c>
       <c r="J60" s="42"/>
-      <c r="K60" s="241" t="s">
+      <c r="K60" s="259" t="s">
         <v>88</v>
       </c>
-      <c r="L60" s="241"/>
-      <c r="M60" s="241"/>
+      <c r="L60" s="259"/>
+      <c r="M60" s="259"/>
       <c r="N60" s="112"/>
       <c r="O60" s="112"/>
       <c r="P60" s="112"/>
-      <c r="R60" s="234" t="s">
+      <c r="R60" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="S60" s="234"/>
-      <c r="T60" s="234"/>
+      <c r="S60" s="253"/>
+      <c r="T60" s="253"/>
       <c r="U60" s="58"/>
     </row>
     <row r="61" spans="2:21">
@@ -30987,11 +30987,11 @@
       <c r="N61" s="43"/>
       <c r="O61" s="44"/>
       <c r="P61" s="43"/>
-      <c r="R61" s="242" t="s">
+      <c r="R61" s="260" t="s">
         <v>90</v>
       </c>
-      <c r="S61" s="232"/>
-      <c r="T61" s="232"/>
+      <c r="S61" s="251"/>
+      <c r="T61" s="251"/>
       <c r="U61" s="58"/>
     </row>
     <row r="62" spans="2:21">
@@ -31274,10 +31274,10 @@
         <v>12887.312698670696</v>
       </c>
       <c r="J69" s="16"/>
-      <c r="R69" s="241" t="s">
+      <c r="R69" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="S69" s="241"/>
+      <c r="S69" s="259"/>
       <c r="U69" s="119"/>
     </row>
     <row r="70" spans="2:21">
@@ -31318,10 +31318,10 @@
       <c r="O70" s="44"/>
       <c r="P70" s="43"/>
       <c r="Q70" s="43"/>
-      <c r="R70" s="233" t="s">
+      <c r="R70" s="252" t="s">
         <v>82</v>
       </c>
-      <c r="S70" s="233"/>
+      <c r="S70" s="252"/>
       <c r="T70" s="43"/>
       <c r="U70" s="58"/>
     </row>
@@ -32013,12 +32013,14 @@
     <protectedRange sqref="B28:C87" name="Range23"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="C20:H21"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="K24:T24"/>
+    <mergeCell ref="K25:T25"/>
+    <mergeCell ref="K27:T27"/>
     <mergeCell ref="N33:S33"/>
     <mergeCell ref="N34:S34"/>
     <mergeCell ref="R36:T36"/>
@@ -32035,14 +32037,12 @@
     <mergeCell ref="R39:T39"/>
     <mergeCell ref="R40:T40"/>
     <mergeCell ref="R41:T41"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="C20:H21"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="K24:T24"/>
-    <mergeCell ref="K25:T25"/>
-    <mergeCell ref="K27:T27"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="R51:T51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -33042,14 +33042,14 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" s="1"/>
-      <c r="C20" s="251" t="s">
+      <c r="C20" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="253"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="235"/>
       <c r="I20" s="34"/>
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
@@ -33065,12 +33065,12 @@
       <c r="U20" s="57"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="C21" s="254"/>
-      <c r="D21" s="255"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="255"/>
-      <c r="H21" s="256"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="238"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
@@ -33144,7 +33144,7 @@
       <c r="U23" s="58"/>
     </row>
     <row r="24" spans="2:21" ht="21">
-      <c r="C24" s="257" t="s">
+      <c r="C24" s="239" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="12" t="s">
@@ -33162,22 +33162,22 @@
       </c>
       <c r="H24" s="15"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="258" t="s">
+      <c r="K24" s="240" t="s">
         <v>58</v>
       </c>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="240"/>
+      <c r="N24" s="240"/>
+      <c r="O24" s="240"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="240"/>
+      <c r="R24" s="240"/>
+      <c r="S24" s="240"/>
+      <c r="T24" s="240"/>
       <c r="U24" s="58"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="C25" s="257"/>
+      <c r="C25" s="239"/>
       <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
@@ -33190,22 +33190,22 @@
       <c r="G25" s="2"/>
       <c r="H25" s="15"/>
       <c r="J25" s="42"/>
-      <c r="K25" s="259" t="s">
+      <c r="K25" s="241" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="259"/>
-      <c r="S25" s="259"/>
-      <c r="T25" s="259"/>
+      <c r="L25" s="241"/>
+      <c r="M25" s="241"/>
+      <c r="N25" s="241"/>
+      <c r="O25" s="241"/>
+      <c r="P25" s="241"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
       <c r="U25" s="58"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="C26" s="257"/>
+      <c r="C26" s="239"/>
       <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
@@ -33235,7 +33235,7 @@
       <c r="U26" s="58"/>
     </row>
     <row r="27" spans="2:21" ht="17.399999999999999">
-      <c r="C27" s="257"/>
+      <c r="C27" s="239"/>
       <c r="D27" s="2" t="s">
         <v>57</v>
       </c>
@@ -33247,18 +33247,18 @@
         <v>37000</v>
       </c>
       <c r="J27" s="42"/>
-      <c r="K27" s="260" t="s">
+      <c r="K27" s="242" t="s">
         <v>60</v>
       </c>
-      <c r="L27" s="260"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="260"/>
-      <c r="O27" s="260"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="260"/>
-      <c r="R27" s="260"/>
-      <c r="S27" s="260"/>
-      <c r="T27" s="260"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
+      <c r="N27" s="242"/>
+      <c r="O27" s="242"/>
+      <c r="P27" s="242"/>
+      <c r="Q27" s="242"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
       <c r="U27" s="58"/>
     </row>
     <row r="28" spans="2:21">
@@ -33341,11 +33341,11 @@
       <c r="R29" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="232">
         <f>E24</f>
         <v>45832</v>
       </c>
-      <c r="T29" s="250"/>
+      <c r="T29" s="232"/>
       <c r="U29" s="58"/>
     </row>
     <row r="30" spans="2:21" ht="15.6">
@@ -33651,12 +33651,12 @@
       <c r="O36" s="111"/>
       <c r="P36" s="112"/>
       <c r="Q36" s="115"/>
-      <c r="R36" s="236">
+      <c r="R36" s="249">
         <f>C4</f>
         <v>74252</v>
       </c>
-      <c r="S36" s="236"/>
-      <c r="T36" s="236"/>
+      <c r="S36" s="249"/>
+      <c r="T36" s="249"/>
       <c r="U36" s="58"/>
     </row>
     <row r="37" spans="2:21" ht="15.6">
@@ -33695,9 +33695,9 @@
       <c r="O37" s="111"/>
       <c r="P37" s="112"/>
       <c r="Q37" s="115"/>
-      <c r="R37" s="249"/>
-      <c r="S37" s="249"/>
-      <c r="T37" s="249"/>
+      <c r="R37" s="250"/>
+      <c r="S37" s="250"/>
+      <c r="T37" s="250"/>
       <c r="U37" s="58"/>
     </row>
     <row r="38" spans="2:21" ht="15.6">
@@ -33740,12 +33740,12 @@
       <c r="O38" s="118"/>
       <c r="P38" s="116"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="236">
+      <c r="R38" s="249">
         <f>-C14</f>
         <v>0</v>
       </c>
-      <c r="S38" s="236"/>
-      <c r="T38" s="236"/>
+      <c r="S38" s="249"/>
+      <c r="T38" s="249"/>
       <c r="U38" s="47"/>
     </row>
     <row r="39" spans="2:21" ht="15.6">
@@ -33788,12 +33788,12 @@
       <c r="O39" s="118"/>
       <c r="P39" s="116"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="236">
+      <c r="R39" s="249">
         <f>-C8</f>
         <v>0</v>
       </c>
-      <c r="S39" s="236"/>
-      <c r="T39" s="236"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
       <c r="U39" s="47"/>
     </row>
     <row r="40" spans="2:21" ht="15.6">
@@ -34021,12 +34021,12 @@
       <c r="O44" s="111"/>
       <c r="P44" s="112"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="236">
+      <c r="R44" s="249">
         <f>SUM(R36:T43)</f>
         <v>37000</v>
       </c>
-      <c r="S44" s="236"/>
-      <c r="T44" s="236"/>
+      <c r="S44" s="249"/>
+      <c r="T44" s="249"/>
       <c r="U44" s="58"/>
     </row>
     <row r="45" spans="2:21">
@@ -34192,11 +34192,11 @@
       <c r="O48" s="116"/>
       <c r="P48" s="116"/>
       <c r="Q48" s="116"/>
-      <c r="R48" s="237">
+      <c r="R48" s="255">
         <f>E25</f>
         <v>60</v>
       </c>
-      <c r="S48" s="237"/>
+      <c r="S48" s="255"/>
       <c r="T48" s="109" t="s">
         <v>85</v>
       </c>
@@ -34240,12 +34240,12 @@
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
       <c r="Q49" s="116"/>
-      <c r="R49" s="238">
+      <c r="R49" s="256">
         <f>C1</f>
         <v>1541.3493922672235</v>
       </c>
-      <c r="S49" s="238"/>
-      <c r="T49" s="238"/>
+      <c r="S49" s="256"/>
+      <c r="T49" s="256"/>
       <c r="U49" s="58"/>
     </row>
     <row r="50" spans="2:21" ht="15">
@@ -34286,12 +34286,12 @@
       <c r="O50" s="116"/>
       <c r="P50" s="116"/>
       <c r="Q50" s="116"/>
-      <c r="R50" s="239">
+      <c r="R50" s="257">
         <f>B28</f>
         <v>45893</v>
       </c>
-      <c r="S50" s="239"/>
-      <c r="T50" s="239"/>
+      <c r="S50" s="257"/>
+      <c r="T50" s="257"/>
       <c r="U50" s="58"/>
     </row>
     <row r="51" spans="2:21" ht="15">
@@ -34332,12 +34332,12 @@
       <c r="O51" s="116"/>
       <c r="P51" s="116"/>
       <c r="Q51" s="116"/>
-      <c r="R51" s="239">
+      <c r="R51" s="257">
         <f>G24</f>
         <v>47688</v>
       </c>
-      <c r="S51" s="239"/>
-      <c r="T51" s="239"/>
+      <c r="S51" s="257"/>
+      <c r="T51" s="257"/>
       <c r="U51" s="58"/>
     </row>
     <row r="52" spans="2:21" ht="15">
@@ -34378,12 +34378,12 @@
       <c r="O52" s="116"/>
       <c r="P52" s="116"/>
       <c r="Q52" s="116"/>
-      <c r="R52" s="240">
+      <c r="R52" s="258">
         <f>C16</f>
         <v>9.4100503202476204E-2</v>
       </c>
-      <c r="S52" s="240"/>
-      <c r="T52" s="240"/>
+      <c r="S52" s="258"/>
+      <c r="T52" s="258"/>
       <c r="U52" s="58"/>
     </row>
     <row r="53" spans="2:21" ht="15">
@@ -34424,12 +34424,12 @@
       <c r="O53" s="116"/>
       <c r="P53" s="116"/>
       <c r="Q53" s="116"/>
-      <c r="R53" s="240">
+      <c r="R53" s="258">
         <f>C15</f>
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="S53" s="240"/>
-      <c r="T53" s="240"/>
+      <c r="S53" s="258"/>
+      <c r="T53" s="258"/>
       <c r="U53" s="58"/>
     </row>
     <row r="54" spans="2:21" ht="15" thickBot="1">
@@ -34689,19 +34689,19 @@
         <v>26059.39864176065</v>
       </c>
       <c r="J60" s="42"/>
-      <c r="K60" s="241" t="s">
+      <c r="K60" s="259" t="s">
         <v>88</v>
       </c>
-      <c r="L60" s="241"/>
-      <c r="M60" s="241"/>
+      <c r="L60" s="259"/>
+      <c r="M60" s="259"/>
       <c r="N60" s="112"/>
       <c r="O60" s="112"/>
       <c r="P60" s="112"/>
-      <c r="R60" s="234" t="s">
+      <c r="R60" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="S60" s="234"/>
-      <c r="T60" s="234"/>
+      <c r="S60" s="253"/>
+      <c r="T60" s="253"/>
       <c r="U60" s="58"/>
     </row>
     <row r="61" spans="2:21">
@@ -34741,11 +34741,11 @@
       <c r="N61" s="43"/>
       <c r="O61" s="44"/>
       <c r="P61" s="43"/>
-      <c r="R61" s="242" t="s">
+      <c r="R61" s="260" t="s">
         <v>90</v>
       </c>
-      <c r="S61" s="232"/>
-      <c r="T61" s="232"/>
+      <c r="S61" s="251"/>
+      <c r="T61" s="251"/>
       <c r="U61" s="58"/>
     </row>
     <row r="62" spans="2:21">
@@ -35028,10 +35028,10 @@
         <v>20008.563302249109</v>
       </c>
       <c r="J69" s="16"/>
-      <c r="R69" s="241" t="s">
+      <c r="R69" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="S69" s="241"/>
+      <c r="S69" s="259"/>
       <c r="U69" s="119"/>
     </row>
     <row r="70" spans="2:21">
@@ -35072,10 +35072,10 @@
       <c r="O70" s="44"/>
       <c r="P70" s="43"/>
       <c r="Q70" s="43"/>
-      <c r="R70" s="233" t="s">
+      <c r="R70" s="252" t="s">
         <v>82</v>
       </c>
-      <c r="S70" s="233"/>
+      <c r="S70" s="252"/>
       <c r="T70" s="43"/>
       <c r="U70" s="58"/>
     </row>
@@ -35767,15 +35767,11 @@
     <protectedRange sqref="B28:C87" name="Range23"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="K24:T24"/>
-    <mergeCell ref="K25:T25"/>
-    <mergeCell ref="K27:T27"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="K60:M60"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
     <mergeCell ref="C24:C27"/>
     <mergeCell ref="C20:H21"/>
     <mergeCell ref="N34:S34"/>
@@ -35792,11 +35788,15 @@
     <mergeCell ref="R42:T42"/>
     <mergeCell ref="R44:T44"/>
     <mergeCell ref="N32:S32"/>
-    <mergeCell ref="K60:M60"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="K24:T24"/>
+    <mergeCell ref="K25:T25"/>
+    <mergeCell ref="K27:T27"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S30:T30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -35831,7 +35831,7 @@
       </c>
       <c r="C1" s="1">
         <f>'DATA ENTRY'!D16</f>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
     </row>
     <row r="2" spans="2:63">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="C3" s="4">
         <f>'DATA ENTRY'!D4</f>
-        <v>48000.096012647933</v>
+        <v>22799.94860170356</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -36097,7 +36097,7 @@
       </c>
       <c r="C4" s="4">
         <f>'DATA ENTRY'!D13</f>
-        <v>42486.859499999999</v>
+        <v>20181.172399999999</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -36166,7 +36166,7 @@
       </c>
       <c r="C5" s="4">
         <f>'DATA ENTRY'!D8</f>
-        <v>2827.5374999999999</v>
+        <v>1198.47</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="C6" s="4">
         <f>'DATA ENTRY'!D9</f>
-        <v>904.8119999999999</v>
+        <v>383.5104</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -36304,7 +36304,7 @@
       </c>
       <c r="C7" s="4">
         <f>'DATA ENTRY'!D10</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -36442,7 +36442,7 @@
       </c>
       <c r="C9" s="4">
         <f>'DATA ENTRY'!D12</f>
-        <v>754.01</v>
+        <v>319.59200000000004</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -36511,247 +36511,247 @@
       </c>
       <c r="C10" s="6">
         <f>C4-C5-C6-C7-C8-C9</f>
-        <v>37700.5</v>
+        <v>15979.599999999999</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" ref="D10:BK10" si="0">-$C1</f>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="J10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="K10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="Q10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="R10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="S10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="T10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="V10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="W10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="X10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="Y10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="Z10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AB10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AC10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AD10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AE10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AG10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AH10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AI10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AJ10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AK10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AL10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AM10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AN10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AO10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AP10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AQ10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AR10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AS10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AT10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AU10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AV10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AW10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AX10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AY10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="AZ10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BA10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BB10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BC10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BD10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BE10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BF10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BG10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BH10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BI10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BJ10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
       <c r="BK10" s="6">
         <f t="shared" si="0"/>
-        <v>-2000.0040005269973</v>
+        <v>-949.99785840431502</v>
       </c>
     </row>
     <row r="12" spans="2:63">
@@ -36760,11 +36760,11 @@
       </c>
       <c r="C12" s="7">
         <f>IRR(C10:AA10)</f>
-        <v>2.0298089579339651E-2</v>
+        <v>3.0632825618161608E-2</v>
       </c>
       <c r="D12">
         <f>C12/5</f>
-        <v>4.0596179158679298E-3</v>
+        <v>6.1265651236323219E-3</v>
       </c>
     </row>
     <row r="13" spans="2:63">
@@ -36799,14 +36799,14 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" s="1"/>
-      <c r="C20" s="251" t="s">
+      <c r="C20" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="253"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="235"/>
       <c r="I20" s="34"/>
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
@@ -36822,12 +36822,12 @@
       <c r="U20" s="57"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="C21" s="254"/>
-      <c r="D21" s="255"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="255"/>
-      <c r="H21" s="256"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="238"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
@@ -36887,7 +36887,7 @@
       </c>
       <c r="H23" s="20">
         <f>C10</f>
-        <v>37700.5</v>
+        <v>15979.599999999999</v>
       </c>
       <c r="J23" s="42"/>
       <c r="K23" s="43"/>
@@ -36903,7 +36903,7 @@
       <c r="U23" s="58"/>
     </row>
     <row r="24" spans="2:21" ht="21">
-      <c r="C24" s="257" t="s">
+      <c r="C24" s="239" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="12" t="s">
@@ -36921,22 +36921,22 @@
       </c>
       <c r="H24" s="15"/>
       <c r="J24" s="42"/>
-      <c r="K24" s="258" t="s">
+      <c r="K24" s="240" t="s">
         <v>58</v>
       </c>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="240"/>
+      <c r="N24" s="240"/>
+      <c r="O24" s="240"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="240"/>
+      <c r="R24" s="240"/>
+      <c r="S24" s="240"/>
+      <c r="T24" s="240"/>
       <c r="U24" s="58"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="C25" s="257"/>
+      <c r="C25" s="239"/>
       <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
@@ -36949,22 +36949,22 @@
       <c r="G25" s="2"/>
       <c r="H25" s="15"/>
       <c r="J25" s="42"/>
-      <c r="K25" s="259" t="s">
+      <c r="K25" s="241" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="259"/>
-      <c r="S25" s="259"/>
-      <c r="T25" s="259"/>
+      <c r="L25" s="241"/>
+      <c r="M25" s="241"/>
+      <c r="N25" s="241"/>
+      <c r="O25" s="241"/>
+      <c r="P25" s="241"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
       <c r="U25" s="58"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="C26" s="257"/>
+      <c r="C26" s="239"/>
       <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
@@ -36994,7 +36994,7 @@
       <c r="U26" s="58"/>
     </row>
     <row r="27" spans="2:21" ht="17.399999999999999">
-      <c r="C27" s="257"/>
+      <c r="C27" s="239"/>
       <c r="D27" s="2" t="s">
         <v>57</v>
       </c>
@@ -37003,21 +37003,21 @@
       <c r="G27" s="2"/>
       <c r="H27" s="24">
         <f>C10</f>
-        <v>37700.5</v>
+        <v>15979.599999999999</v>
       </c>
       <c r="J27" s="42"/>
-      <c r="K27" s="260" t="s">
+      <c r="K27" s="242" t="s">
         <v>60</v>
       </c>
-      <c r="L27" s="260"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="260"/>
-      <c r="O27" s="260"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="260"/>
-      <c r="R27" s="260"/>
-      <c r="S27" s="260"/>
-      <c r="T27" s="260"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
+      <c r="N27" s="242"/>
+      <c r="O27" s="242"/>
+      <c r="P27" s="242"/>
+      <c r="Q27" s="242"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
       <c r="U27" s="58"/>
     </row>
     <row r="28" spans="2:21">
@@ -37034,19 +37034,19 @@
       </c>
       <c r="E28" s="28">
         <f t="shared" ref="E28:E51" si="2">C$1</f>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F28" s="29">
         <f>E28-G28</f>
-        <v>1234.7558743411028</v>
+        <v>460.49755815633984</v>
       </c>
       <c r="G28" s="30">
         <f t="shared" ref="G28:G51" si="3">H27*C$12</f>
-        <v>765.24812618589453</v>
+        <v>489.50030024797519</v>
       </c>
       <c r="H28" s="29">
         <f>H27-F28</f>
-        <v>36465.744125658894</v>
+        <v>15519.102441843659</v>
       </c>
       <c r="J28" s="42"/>
       <c r="K28" s="112"/>
@@ -37075,19 +37075,19 @@
       </c>
       <c r="E29" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F29" s="29">
         <f t="shared" ref="F29:F51" si="5">E29-G29</f>
-        <v>1259.8190596870945</v>
+        <v>474.60389955293221</v>
       </c>
       <c r="G29" s="30">
         <f t="shared" si="3"/>
-        <v>740.18494083990288</v>
+        <v>475.39395885138282</v>
       </c>
       <c r="H29" s="29">
         <f t="shared" ref="H29:H51" si="6">H28-F29</f>
-        <v>35205.925065971802</v>
+        <v>15044.498542290727</v>
       </c>
       <c r="J29" s="42"/>
       <c r="K29" s="112"/>
@@ -37100,11 +37100,11 @@
       <c r="R29" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="232">
         <f>E24</f>
         <v>46035</v>
       </c>
-      <c r="T29" s="250"/>
+      <c r="T29" s="232"/>
       <c r="U29" s="58"/>
     </row>
     <row r="30" spans="2:21" ht="15.6">
@@ -37121,19 +37121,19 @@
       </c>
       <c r="E30" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F30" s="29">
         <f t="shared" si="5"/>
-        <v>1285.3909798143825</v>
+        <v>489.14235804563668</v>
       </c>
       <c r="G30" s="30">
         <f t="shared" si="3"/>
-        <v>714.6130207126148</v>
+        <v>460.85550035867834</v>
       </c>
       <c r="H30" s="29">
         <f t="shared" si="6"/>
-        <v>33920.534086157422</v>
+        <v>14555.356184245091</v>
       </c>
       <c r="J30" s="42"/>
       <c r="K30" s="112"/>
@@ -37167,19 +37167,19 @@
       </c>
       <c r="E31" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F31" s="29">
         <f t="shared" si="5"/>
-        <v>1311.4819610671298</v>
+        <v>504.12617060210505</v>
       </c>
       <c r="G31" s="30">
         <f t="shared" si="3"/>
-        <v>688.52203945986741</v>
+        <v>445.87168780220998</v>
       </c>
       <c r="H31" s="29">
         <f t="shared" si="6"/>
-        <v>32609.052125090293</v>
+        <v>14051.230013642986</v>
       </c>
       <c r="J31" s="42"/>
       <c r="K31" s="112"/>
@@ -37208,19 +37208,19 @@
       </c>
       <c r="E32" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F32" s="29">
         <f t="shared" si="5"/>
-        <v>1338.1025393945586</v>
+        <v>519.56897967571092</v>
       </c>
       <c r="G32" s="30">
         <f t="shared" si="3"/>
-        <v>661.90146113243873</v>
+        <v>430.4288787286041</v>
       </c>
       <c r="H32" s="29">
         <f t="shared" si="6"/>
-        <v>31270.949585695733</v>
+        <v>13531.661033967275</v>
       </c>
       <c r="J32" s="45"/>
       <c r="K32" s="113" t="s">
@@ -37254,19 +37254,19 @@
       </c>
       <c r="E33" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F33" s="29">
         <f t="shared" si="5"/>
-        <v>1365.2634646055312</v>
+        <v>535.48484562672309</v>
       </c>
       <c r="G33" s="30">
         <f t="shared" si="3"/>
-        <v>634.74053592146618</v>
+        <v>414.51301277759194</v>
       </c>
       <c r="H33" s="29">
         <f t="shared" si="6"/>
-        <v>29905.686121090203</v>
+        <v>12996.176188340552</v>
       </c>
       <c r="J33" s="45"/>
       <c r="K33" s="113" t="s">
@@ -37300,19 +37300,19 @@
       </c>
       <c r="E34" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F34" s="29">
         <f t="shared" si="5"/>
-        <v>1392.9757047094938</v>
+        <v>551.88825952397474</v>
       </c>
       <c r="G34" s="30">
         <f t="shared" si="3"/>
-        <v>607.02829581750348</v>
+        <v>398.10959888034034</v>
       </c>
       <c r="H34" s="29">
         <f t="shared" si="6"/>
-        <v>28512.710416380709</v>
+        <v>12444.287928816579</v>
       </c>
       <c r="J34" s="45"/>
       <c r="K34" s="113" t="s">
@@ -37346,19 +37346,19 @@
       </c>
       <c r="E35" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F35" s="29">
         <f t="shared" si="5"/>
-        <v>1421.2504503455309</v>
+        <v>568.79415633868325</v>
       </c>
       <c r="G35" s="30">
         <f t="shared" si="3"/>
-        <v>578.75355018146638</v>
+        <v>381.20370206563172</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="6"/>
-        <v>27091.459966035178</v>
+        <v>11875.493772477896</v>
       </c>
       <c r="J35" s="42"/>
       <c r="K35" s="112"/>
@@ -37387,19 +37387,19 @@
       </c>
       <c r="E36" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F36" s="29">
         <f t="shared" si="5"/>
-        <v>1450.0991193013215</v>
+        <v>586.21792854243552</v>
       </c>
       <c r="G36" s="30">
         <f t="shared" si="3"/>
-        <v>549.90488122567592</v>
+        <v>363.77992986187951</v>
       </c>
       <c r="H36" s="29">
         <f t="shared" si="6"/>
-        <v>25641.360846733856</v>
+        <v>11289.27584393546</v>
       </c>
       <c r="J36" s="42"/>
       <c r="K36" s="112"/>
@@ -37411,12 +37411,12 @@
       <c r="O36" s="111"/>
       <c r="P36" s="112"/>
       <c r="Q36" s="115"/>
-      <c r="R36" s="236">
+      <c r="R36" s="249">
         <f>C4</f>
-        <v>42486.859499999999</v>
-      </c>
-      <c r="S36" s="236"/>
-      <c r="T36" s="236"/>
+        <v>20181.172399999999</v>
+      </c>
+      <c r="S36" s="249"/>
+      <c r="T36" s="249"/>
       <c r="U36" s="58"/>
     </row>
     <row r="37" spans="2:21" ht="15.6">
@@ -37433,19 +37433,19 @@
       </c>
       <c r="E37" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F37" s="29">
         <f t="shared" si="5"/>
-        <v>1479.5333611238211</v>
+        <v>604.17544012171584</v>
       </c>
       <c r="G37" s="30">
         <f t="shared" si="3"/>
-        <v>520.47063940317616</v>
+        <v>345.82241828259919</v>
       </c>
       <c r="H37" s="29">
         <f t="shared" si="6"/>
-        <v>24161.827485610036</v>
+        <v>10685.100403813743</v>
       </c>
       <c r="J37" s="42"/>
       <c r="K37" s="112"/>
@@ -37455,9 +37455,9 @@
       <c r="O37" s="111"/>
       <c r="P37" s="112"/>
       <c r="Q37" s="115"/>
-      <c r="R37" s="249"/>
-      <c r="S37" s="249"/>
-      <c r="T37" s="249"/>
+      <c r="R37" s="250"/>
+      <c r="S37" s="250"/>
+      <c r="T37" s="250"/>
       <c r="U37" s="58"/>
     </row>
     <row r="38" spans="2:21" ht="15.6">
@@ -37474,19 +37474,19 @@
       </c>
       <c r="E38" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F38" s="29">
         <f t="shared" si="5"/>
-        <v>1509.5650618235338</v>
+        <v>622.68304102174045</v>
       </c>
       <c r="G38" s="30">
         <f t="shared" si="3"/>
-        <v>490.43893870346341</v>
+        <v>327.31481738257457</v>
       </c>
       <c r="H38" s="29">
         <f t="shared" si="6"/>
-        <v>22652.262423786502</v>
+        <v>10062.417362792003</v>
       </c>
       <c r="J38" s="49"/>
       <c r="K38" s="116"/>
@@ -37500,12 +37500,12 @@
       <c r="O38" s="118"/>
       <c r="P38" s="116"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="236">
+      <c r="R38" s="249">
         <f>-C14</f>
         <v>0</v>
       </c>
-      <c r="S38" s="236"/>
-      <c r="T38" s="236"/>
+      <c r="S38" s="249"/>
+      <c r="T38" s="249"/>
       <c r="U38" s="47"/>
     </row>
     <row r="39" spans="2:21" ht="15.6">
@@ -37522,19 +37522,19 @@
       </c>
       <c r="E39" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F39" s="29">
         <f t="shared" si="5"/>
-        <v>1540.2063486742693</v>
+        <v>641.75758203274609</v>
       </c>
       <c r="G39" s="30">
         <f t="shared" si="3"/>
-        <v>459.79765185272794</v>
+        <v>308.240276371569</v>
       </c>
       <c r="H39" s="29">
         <f t="shared" si="6"/>
-        <v>21112.056075112232</v>
+        <v>9420.659780759257</v>
       </c>
       <c r="J39" s="49"/>
       <c r="K39" s="116"/>
@@ -37548,12 +37548,12 @@
       <c r="O39" s="118"/>
       <c r="P39" s="116"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="236">
+      <c r="R39" s="249">
         <f>-C8</f>
         <v>-300</v>
       </c>
-      <c r="S39" s="236"/>
-      <c r="T39" s="236"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
       <c r="U39" s="47"/>
     </row>
     <row r="40" spans="2:21" ht="15.6">
@@ -37570,19 +37570,19 @@
       </c>
       <c r="E40" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F40" s="29">
         <f t="shared" si="5"/>
-        <v>1571.4695951103272</v>
+        <v>661.41643013228816</v>
       </c>
       <c r="G40" s="30">
         <f t="shared" si="3"/>
-        <v>428.53440541666998</v>
+        <v>288.58142827202687</v>
       </c>
       <c r="H40" s="29">
         <f t="shared" si="6"/>
-        <v>19540.586480001904</v>
+        <v>8759.2433506269681</v>
       </c>
       <c r="J40" s="49"/>
       <c r="K40" s="116"/>
@@ -37598,7 +37598,7 @@
       <c r="Q40" s="46"/>
       <c r="R40" s="243">
         <f>-C7</f>
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="S40" s="243"/>
       <c r="T40" s="243"/>
@@ -37618,19 +37618,19 @@
       </c>
       <c r="E41" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F41" s="29">
         <f t="shared" si="5"/>
-        <v>1603.3674257230855</v>
+        <v>681.67748429751759</v>
       </c>
       <c r="G41" s="30">
         <f t="shared" si="3"/>
-        <v>396.63657480391191</v>
+        <v>268.32037410679749</v>
       </c>
       <c r="H41" s="29">
         <f t="shared" si="6"/>
-        <v>17937.219054278819</v>
+        <v>8077.5658663294507</v>
       </c>
       <c r="J41" s="49"/>
       <c r="K41" s="116"/>
@@ -37646,7 +37646,7 @@
       <c r="Q41" s="46"/>
       <c r="R41" s="243">
         <f>-C5</f>
-        <v>-2827.5374999999999</v>
+        <v>-1198.47</v>
       </c>
       <c r="S41" s="243"/>
       <c r="T41" s="243"/>
@@ -37666,19 +37666,19 @@
       </c>
       <c r="E42" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F42" s="29">
         <f t="shared" si="5"/>
-        <v>1635.9127213590077</v>
+        <v>702.55919180183048</v>
       </c>
       <c r="G42" s="30">
         <f t="shared" si="3"/>
-        <v>364.09127916798951</v>
+        <v>247.43866660248455</v>
       </c>
       <c r="H42" s="29">
         <f t="shared" si="6"/>
-        <v>16301.306332919812</v>
+        <v>7375.0066745276199</v>
       </c>
       <c r="J42" s="49"/>
       <c r="K42" s="116"/>
@@ -37694,7 +37694,7 @@
       <c r="Q42" s="46"/>
       <c r="R42" s="243">
         <f>-C6</f>
-        <v>-904.8119999999999</v>
+        <v>-383.5104</v>
       </c>
       <c r="S42" s="243"/>
       <c r="T42" s="243"/>
@@ -37714,19 +37714,19 @@
       </c>
       <c r="E43" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="5"/>
-        <v>1669.1186243211341</v>
+        <v>724.08056501073247</v>
       </c>
       <c r="G43" s="30">
         <f t="shared" si="3"/>
-        <v>330.88537620586311</v>
+        <v>225.91729339358253</v>
       </c>
       <c r="H43" s="29">
         <f t="shared" si="6"/>
-        <v>14632.187708598678</v>
+        <v>6650.9261095168877</v>
       </c>
       <c r="J43" s="16"/>
       <c r="L43" s="117" t="s">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="R43" s="243">
         <f>-C9</f>
-        <v>-754.01</v>
+        <v>-319.59200000000004</v>
       </c>
       <c r="S43" s="243"/>
       <c r="T43" s="243"/>
@@ -37757,19 +37757,19 @@
       </c>
       <c r="E44" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="5"/>
-        <v>1702.9985436761488</v>
+        <v>746.26119869220622</v>
       </c>
       <c r="G44" s="30">
         <f t="shared" si="3"/>
-        <v>297.00545685084853</v>
+        <v>203.73665971210883</v>
       </c>
       <c r="H44" s="29">
         <f t="shared" si="6"/>
-        <v>12929.189164922529</v>
+        <v>5904.6649108246811</v>
       </c>
       <c r="J44" s="42"/>
       <c r="K44" s="112"/>
@@ -37781,12 +37781,12 @@
       <c r="O44" s="111"/>
       <c r="P44" s="112"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="236">
+      <c r="R44" s="249">
         <f>SUM(R36:T43)</f>
-        <v>37700.5</v>
-      </c>
-      <c r="S44" s="236"/>
-      <c r="T44" s="236"/>
+        <v>15979.599999999999</v>
+      </c>
+      <c r="S44" s="249"/>
+      <c r="T44" s="249"/>
       <c r="U44" s="58"/>
     </row>
     <row r="45" spans="2:21">
@@ -37803,19 +37803,19 @@
       </c>
       <c r="E45" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="5"/>
-        <v>1737.5661606691722</v>
+        <v>769.12128785734478</v>
       </c>
       <c r="G45" s="30">
         <f t="shared" si="3"/>
-        <v>262.43783985782511</v>
+        <v>180.87657054697021</v>
       </c>
       <c r="H45" s="29">
         <f t="shared" si="6"/>
-        <v>11191.623004253357</v>
+        <v>5135.543622967336</v>
       </c>
       <c r="J45" s="42"/>
       <c r="K45" s="43"/>
@@ -37844,19 +37844,19 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F46" s="29">
         <f t="shared" si="5"/>
-        <v>1772.8354342484643</v>
+        <v>792.6816461474948</v>
       </c>
       <c r="G46" s="30">
         <f t="shared" si="3"/>
-        <v>227.16856627853298</v>
+        <v>157.31621225682028</v>
       </c>
       <c r="H46" s="29">
         <f t="shared" si="6"/>
-        <v>9418.7875700048935</v>
+        <v>4342.8619768198414</v>
       </c>
       <c r="J46" s="42"/>
       <c r="K46" s="120" t="s">
@@ -37887,19 +37887,19 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F47" s="29">
         <f t="shared" si="5"/>
-        <v>1808.820606702267</v>
+        <v>816.96372478464821</v>
       </c>
       <c r="G47" s="30">
         <f t="shared" si="3"/>
-        <v>191.18339382473016</v>
+        <v>133.03413361966679</v>
       </c>
       <c r="H47" s="29">
         <f t="shared" si="6"/>
-        <v>7609.966963302626</v>
+        <v>3525.8982520351933</v>
       </c>
       <c r="J47" s="42"/>
       <c r="K47" s="43"/>
@@ -37928,19 +37928,19 @@
       </c>
       <c r="E48" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F48" s="29">
         <f t="shared" si="5"/>
-        <v>1845.5362094100653</v>
+        <v>841.98963210234012</v>
       </c>
       <c r="G48" s="30">
         <f t="shared" si="3"/>
-        <v>154.46779111693203</v>
+        <v>108.0082263019749</v>
       </c>
       <c r="H48" s="29">
         <f t="shared" si="6"/>
-        <v>5764.4307538925605</v>
+        <v>2683.9086199328531</v>
       </c>
       <c r="J48" s="42"/>
       <c r="K48" s="43"/>
@@ -37952,11 +37952,11 @@
       <c r="O48" s="116"/>
       <c r="P48" s="116"/>
       <c r="Q48" s="116"/>
-      <c r="R48" s="237">
+      <c r="R48" s="255">
         <f>E25</f>
         <v>24</v>
       </c>
-      <c r="S48" s="237"/>
+      <c r="S48" s="255"/>
       <c r="T48" s="109" t="s">
         <v>85</v>
       </c>
@@ -37976,19 +37976,19 @@
       </c>
       <c r="E49" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F49" s="29">
         <f t="shared" si="5"/>
-        <v>1882.9970687105856</v>
+        <v>867.78215367483119</v>
       </c>
       <c r="G49" s="30">
         <f t="shared" si="3"/>
-        <v>117.00693181641159</v>
+        <v>82.215704729483861</v>
       </c>
       <c r="H49" s="29">
         <f t="shared" si="6"/>
-        <v>3881.4336851819749</v>
+        <v>1816.126466258022</v>
       </c>
       <c r="J49" s="42"/>
       <c r="K49" s="43"/>
@@ -38000,12 +38000,12 @@
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
       <c r="Q49" s="116"/>
-      <c r="R49" s="238">
+      <c r="R49" s="256">
         <f>C1</f>
-        <v>2000.0040005269973</v>
-      </c>
-      <c r="S49" s="238"/>
-      <c r="T49" s="238"/>
+        <v>949.99785840431502</v>
+      </c>
+      <c r="S49" s="256"/>
+      <c r="T49" s="256"/>
       <c r="U49" s="58"/>
     </row>
     <row r="50" spans="2:21" ht="15">
@@ -38022,19 +38022,19 @@
       </c>
       <c r="E50" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F50" s="29">
         <f t="shared" si="5"/>
-        <v>1921.2183118889072</v>
+        <v>894.36477306290499</v>
       </c>
       <c r="G50" s="30">
         <f t="shared" si="3"/>
-        <v>78.78568863809015</v>
+        <v>55.633085341410052</v>
       </c>
       <c r="H50" s="29">
         <f t="shared" si="6"/>
-        <v>1960.2153732930676</v>
+        <v>921.761693195117</v>
       </c>
       <c r="J50" s="42"/>
       <c r="K50" s="43"/>
@@ -38046,12 +38046,12 @@
       <c r="O50" s="116"/>
       <c r="P50" s="116"/>
       <c r="Q50" s="116"/>
-      <c r="R50" s="239">
+      <c r="R50" s="257">
         <f>B28</f>
         <v>46125</v>
       </c>
-      <c r="S50" s="239"/>
-      <c r="T50" s="239"/>
+      <c r="S50" s="257"/>
+      <c r="T50" s="257"/>
       <c r="U50" s="58"/>
     </row>
     <row r="51" spans="2:21" ht="15">
@@ -38068,19 +38068,19 @@
       </c>
       <c r="E51" s="28">
         <f t="shared" si="2"/>
-        <v>2000.0040005269973</v>
+        <v>949.99785840431502</v>
       </c>
       <c r="F51" s="29">
         <f t="shared" si="5"/>
-        <v>1960.2153732850959</v>
+        <v>921.7616931951676</v>
       </c>
       <c r="G51" s="30">
         <f t="shared" si="3"/>
-        <v>39.788627241901402</v>
+        <v>28.236165209147401</v>
       </c>
       <c r="H51" s="29">
         <f t="shared" si="6"/>
-        <v>7.971721061039716E-9</v>
+        <v>-5.0590642786119133E-11</v>
       </c>
       <c r="J51" s="42"/>
       <c r="K51" s="43"/>
@@ -38092,12 +38092,12 @@
       <c r="O51" s="116"/>
       <c r="P51" s="116"/>
       <c r="Q51" s="116"/>
-      <c r="R51" s="239" t="str">
+      <c r="R51" s="257" t="str">
         <f>G24</f>
         <v>Mar-2028</v>
       </c>
-      <c r="S51" s="239"/>
-      <c r="T51" s="239"/>
+      <c r="S51" s="257"/>
+      <c r="T51" s="257"/>
       <c r="U51" s="58"/>
     </row>
     <row r="52" spans="2:21" ht="15">
@@ -38127,12 +38127,12 @@
       <c r="O52" s="116"/>
       <c r="P52" s="116"/>
       <c r="Q52" s="116"/>
-      <c r="R52" s="240">
+      <c r="R52" s="258">
         <f>C16</f>
         <v>9.4100503202476204E-2</v>
       </c>
-      <c r="S52" s="240"/>
-      <c r="T52" s="240"/>
+      <c r="S52" s="258"/>
+      <c r="T52" s="258"/>
       <c r="U52" s="58"/>
     </row>
     <row r="53" spans="2:21" ht="15">
@@ -38150,12 +38150,12 @@
       <c r="O53" s="116"/>
       <c r="P53" s="116"/>
       <c r="Q53" s="116"/>
-      <c r="R53" s="240">
+      <c r="R53" s="258">
         <f>C15</f>
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="S53" s="240"/>
-      <c r="T53" s="240"/>
+      <c r="S53" s="258"/>
+      <c r="T53" s="258"/>
       <c r="U53" s="58"/>
     </row>
     <row r="54" spans="2:21" ht="15" thickBot="1">
@@ -38275,19 +38275,19 @@
       <c r="G60" s="219"/>
       <c r="H60" s="218"/>
       <c r="J60" s="42"/>
-      <c r="K60" s="241" t="s">
+      <c r="K60" s="259" t="s">
         <v>273</v>
       </c>
-      <c r="L60" s="241"/>
-      <c r="M60" s="241"/>
+      <c r="L60" s="259"/>
+      <c r="M60" s="259"/>
       <c r="N60" s="112"/>
       <c r="O60" s="112"/>
       <c r="P60" s="112"/>
-      <c r="R60" s="234" t="s">
+      <c r="R60" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="S60" s="234"/>
-      <c r="T60" s="234"/>
+      <c r="S60" s="253"/>
+      <c r="T60" s="253"/>
       <c r="U60" s="58"/>
     </row>
     <row r="61" spans="2:21">
@@ -38299,19 +38299,19 @@
       <c r="G61" s="219"/>
       <c r="H61" s="218"/>
       <c r="J61" s="42"/>
-      <c r="K61" s="233" t="s">
+      <c r="K61" s="252" t="s">
         <v>267</v>
       </c>
-      <c r="L61" s="233"/>
-      <c r="M61" s="233"/>
+      <c r="L61" s="252"/>
+      <c r="M61" s="252"/>
       <c r="N61" s="43"/>
       <c r="O61" s="44"/>
       <c r="P61" s="43"/>
-      <c r="R61" s="242" t="s">
+      <c r="R61" s="260" t="s">
         <v>90</v>
       </c>
-      <c r="S61" s="232"/>
-      <c r="T61" s="232"/>
+      <c r="S61" s="251"/>
+      <c r="T61" s="251"/>
       <c r="U61" s="58"/>
     </row>
     <row r="62" spans="2:21">
@@ -38434,16 +38434,16 @@
       <c r="G69" s="219"/>
       <c r="H69" s="218"/>
       <c r="J69" s="16"/>
-      <c r="K69" s="234" t="str">
+      <c r="K69" s="253" t="str">
         <f>D22</f>
         <v>YADAO, MELENCIO C.</v>
       </c>
-      <c r="L69" s="234"/>
-      <c r="M69" s="234"/>
-      <c r="R69" s="241" t="s">
+      <c r="L69" s="253"/>
+      <c r="M69" s="253"/>
+      <c r="R69" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="S69" s="241"/>
+      <c r="S69" s="259"/>
       <c r="U69" s="119"/>
     </row>
     <row r="70" spans="2:21">
@@ -38464,10 +38464,10 @@
       <c r="O70" s="44"/>
       <c r="P70" s="43"/>
       <c r="Q70" s="43"/>
-      <c r="R70" s="233" t="s">
+      <c r="R70" s="252" t="s">
         <v>82</v>
       </c>
-      <c r="S70" s="233"/>
+      <c r="S70" s="252"/>
       <c r="T70" s="43"/>
       <c r="U70" s="58"/>
     </row>
@@ -38804,20 +38804,12 @@
     <protectedRange sqref="B28:C87" name="Range23"/>
   </protectedRanges>
   <mergeCells count="32">
-    <mergeCell ref="K61:M61"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="K60:M60"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="R52:T52"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="C20:H21"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="K24:T24"/>
+    <mergeCell ref="K25:T25"/>
+    <mergeCell ref="K27:T27"/>
     <mergeCell ref="R43:T43"/>
     <mergeCell ref="S30:T30"/>
     <mergeCell ref="N32:S32"/>
@@ -38830,12 +38822,20 @@
     <mergeCell ref="R40:T40"/>
     <mergeCell ref="R41:T41"/>
     <mergeCell ref="R42:T42"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="C20:H21"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="K24:T24"/>
-    <mergeCell ref="K25:T25"/>
-    <mergeCell ref="K27:T27"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="R52:T52"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="K60:M60"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="R69:S69"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -38862,115 +38862,115 @@
     <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1"/>
     <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1"/>
     <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="272" t="s">
+      <c r="B6" s="363" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="272"/>
-      <c r="D6" s="272"/>
-      <c r="E6" s="272"/>
-      <c r="F6" s="272"/>
-      <c r="G6" s="272"/>
-      <c r="H6" s="272"/>
-      <c r="I6" s="272"/>
-      <c r="J6" s="272"/>
-      <c r="K6" s="272"/>
-      <c r="L6" s="272"/>
-      <c r="M6" s="272"/>
-      <c r="N6" s="272"/>
-      <c r="O6" s="272"/>
-      <c r="P6" s="272"/>
-      <c r="Q6" s="272"/>
-      <c r="R6" s="272"/>
-      <c r="S6" s="272"/>
-      <c r="T6" s="272"/>
-      <c r="U6" s="272"/>
-      <c r="V6" s="272"/>
-      <c r="W6" s="272"/>
-      <c r="X6" s="272"/>
-      <c r="Y6" s="272"/>
-      <c r="Z6" s="272"/>
-      <c r="AA6" s="272"/>
-      <c r="AB6" s="272"/>
-      <c r="AC6" s="272"/>
-      <c r="AD6" s="272"/>
-      <c r="AE6" s="272"/>
-      <c r="AF6" s="272"/>
-      <c r="AG6" s="272"/>
-      <c r="AH6" s="272"/>
+      <c r="C6" s="363"/>
+      <c r="D6" s="363"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="363"/>
+      <c r="H6" s="363"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="363"/>
+      <c r="K6" s="363"/>
+      <c r="L6" s="363"/>
+      <c r="M6" s="363"/>
+      <c r="N6" s="363"/>
+      <c r="O6" s="363"/>
+      <c r="P6" s="363"/>
+      <c r="Q6" s="363"/>
+      <c r="R6" s="363"/>
+      <c r="S6" s="363"/>
+      <c r="T6" s="363"/>
+      <c r="U6" s="363"/>
+      <c r="V6" s="363"/>
+      <c r="W6" s="363"/>
+      <c r="X6" s="363"/>
+      <c r="Y6" s="363"/>
+      <c r="Z6" s="363"/>
+      <c r="AA6" s="363"/>
+      <c r="AB6" s="363"/>
+      <c r="AC6" s="363"/>
+      <c r="AD6" s="363"/>
+      <c r="AE6" s="363"/>
+      <c r="AF6" s="363"/>
+      <c r="AG6" s="363"/>
+      <c r="AH6" s="363"/>
     </row>
     <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="272" t="s">
+      <c r="B7" s="363" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="272"/>
-      <c r="D7" s="272"/>
-      <c r="E7" s="272"/>
-      <c r="F7" s="272"/>
-      <c r="G7" s="272"/>
-      <c r="H7" s="272"/>
-      <c r="I7" s="272"/>
-      <c r="J7" s="272"/>
-      <c r="K7" s="272"/>
-      <c r="L7" s="272"/>
-      <c r="M7" s="272"/>
-      <c r="N7" s="272"/>
-      <c r="O7" s="272"/>
-      <c r="P7" s="272"/>
-      <c r="Q7" s="272"/>
-      <c r="R7" s="272"/>
-      <c r="S7" s="272"/>
-      <c r="T7" s="272"/>
-      <c r="U7" s="272"/>
-      <c r="V7" s="272"/>
-      <c r="W7" s="272"/>
-      <c r="X7" s="272"/>
-      <c r="Y7" s="272"/>
-      <c r="Z7" s="272"/>
-      <c r="AA7" s="272"/>
-      <c r="AB7" s="272"/>
-      <c r="AC7" s="272"/>
-      <c r="AD7" s="272"/>
-      <c r="AE7" s="272"/>
-      <c r="AF7" s="272"/>
-      <c r="AG7" s="272"/>
-      <c r="AH7" s="272"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="363"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="363"/>
+      <c r="M7" s="363"/>
+      <c r="N7" s="363"/>
+      <c r="O7" s="363"/>
+      <c r="P7" s="363"/>
+      <c r="Q7" s="363"/>
+      <c r="R7" s="363"/>
+      <c r="S7" s="363"/>
+      <c r="T7" s="363"/>
+      <c r="U7" s="363"/>
+      <c r="V7" s="363"/>
+      <c r="W7" s="363"/>
+      <c r="X7" s="363"/>
+      <c r="Y7" s="363"/>
+      <c r="Z7" s="363"/>
+      <c r="AA7" s="363"/>
+      <c r="AB7" s="363"/>
+      <c r="AC7" s="363"/>
+      <c r="AD7" s="363"/>
+      <c r="AE7" s="363"/>
+      <c r="AF7" s="363"/>
+      <c r="AG7" s="363"/>
+      <c r="AH7" s="363"/>
     </row>
     <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="272" t="s">
+      <c r="B8" s="363" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="272"/>
-      <c r="D8" s="272"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
-      <c r="G8" s="272"/>
-      <c r="H8" s="272"/>
-      <c r="I8" s="272"/>
-      <c r="J8" s="272"/>
-      <c r="K8" s="272"/>
-      <c r="L8" s="272"/>
-      <c r="M8" s="272"/>
-      <c r="N8" s="272"/>
-      <c r="O8" s="272"/>
-      <c r="P8" s="272"/>
-      <c r="Q8" s="272"/>
-      <c r="R8" s="272"/>
-      <c r="S8" s="272"/>
-      <c r="T8" s="272"/>
-      <c r="U8" s="272"/>
-      <c r="V8" s="272"/>
-      <c r="W8" s="272"/>
-      <c r="X8" s="272"/>
-      <c r="Y8" s="272"/>
-      <c r="Z8" s="272"/>
-      <c r="AA8" s="272"/>
-      <c r="AB8" s="272"/>
-      <c r="AC8" s="272"/>
-      <c r="AD8" s="272"/>
-      <c r="AE8" s="272"/>
-      <c r="AF8" s="272"/>
-      <c r="AG8" s="272"/>
-      <c r="AH8" s="272"/>
+      <c r="C8" s="363"/>
+      <c r="D8" s="363"/>
+      <c r="E8" s="363"/>
+      <c r="F8" s="363"/>
+      <c r="G8" s="363"/>
+      <c r="H8" s="363"/>
+      <c r="I8" s="363"/>
+      <c r="J8" s="363"/>
+      <c r="K8" s="363"/>
+      <c r="L8" s="363"/>
+      <c r="M8" s="363"/>
+      <c r="N8" s="363"/>
+      <c r="O8" s="363"/>
+      <c r="P8" s="363"/>
+      <c r="Q8" s="363"/>
+      <c r="R8" s="363"/>
+      <c r="S8" s="363"/>
+      <c r="T8" s="363"/>
+      <c r="U8" s="363"/>
+      <c r="V8" s="363"/>
+      <c r="W8" s="363"/>
+      <c r="X8" s="363"/>
+      <c r="Y8" s="363"/>
+      <c r="Z8" s="363"/>
+      <c r="AA8" s="363"/>
+      <c r="AB8" s="363"/>
+      <c r="AC8" s="363"/>
+      <c r="AD8" s="363"/>
+      <c r="AE8" s="363"/>
+      <c r="AF8" s="363"/>
+      <c r="AG8" s="363"/>
+      <c r="AH8" s="363"/>
     </row>
     <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="I9" s="124"/>
@@ -38980,47 +38980,47 @@
     </row>
     <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="125"/>
-      <c r="B10" s="273" t="s">
+      <c r="B10" s="345" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="274"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="274"/>
-      <c r="F10" s="274"/>
-      <c r="G10" s="274"/>
-      <c r="H10" s="274"/>
-      <c r="I10" s="274"/>
-      <c r="J10" s="274"/>
-      <c r="K10" s="274"/>
-      <c r="L10" s="274"/>
-      <c r="M10" s="274"/>
-      <c r="N10" s="274"/>
-      <c r="O10" s="274"/>
-      <c r="P10" s="274"/>
-      <c r="Q10" s="274"/>
-      <c r="R10" s="274"/>
-      <c r="S10" s="274"/>
-      <c r="T10" s="274"/>
-      <c r="U10" s="274"/>
-      <c r="V10" s="274"/>
-      <c r="W10" s="274"/>
-      <c r="X10" s="274"/>
-      <c r="Y10" s="274"/>
-      <c r="Z10" s="274"/>
-      <c r="AA10" s="274"/>
-      <c r="AB10" s="274"/>
-      <c r="AC10" s="274"/>
-      <c r="AD10" s="274"/>
-      <c r="AE10" s="274"/>
-      <c r="AF10" s="274"/>
-      <c r="AG10" s="274"/>
-      <c r="AH10" s="275"/>
+      <c r="C10" s="346"/>
+      <c r="D10" s="346"/>
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
+      <c r="G10" s="346"/>
+      <c r="H10" s="346"/>
+      <c r="I10" s="346"/>
+      <c r="J10" s="346"/>
+      <c r="K10" s="346"/>
+      <c r="L10" s="346"/>
+      <c r="M10" s="346"/>
+      <c r="N10" s="346"/>
+      <c r="O10" s="346"/>
+      <c r="P10" s="346"/>
+      <c r="Q10" s="346"/>
+      <c r="R10" s="346"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="346"/>
+      <c r="U10" s="346"/>
+      <c r="V10" s="346"/>
+      <c r="W10" s="346"/>
+      <c r="X10" s="346"/>
+      <c r="Y10" s="346"/>
+      <c r="Z10" s="346"/>
+      <c r="AA10" s="346"/>
+      <c r="AB10" s="346"/>
+      <c r="AC10" s="346"/>
+      <c r="AD10" s="346"/>
+      <c r="AE10" s="346"/>
+      <c r="AF10" s="346"/>
+      <c r="AG10" s="346"/>
+      <c r="AH10" s="347"/>
     </row>
     <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="Y11" s="276" t="s">
+      <c r="Y11" s="364" t="s">
         <v>61</v>
       </c>
-      <c r="Z11" s="276"/>
+      <c r="Z11" s="364"/>
       <c r="AA11" s="126">
         <v>0</v>
       </c>
@@ -39073,145 +39073,145 @@
       </c>
     </row>
     <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="277" t="s">
+      <c r="B13" s="360" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="277"/>
-      <c r="D13" s="277"/>
-      <c r="E13" s="277"/>
-      <c r="F13" s="277"/>
-      <c r="G13" s="277"/>
-      <c r="H13" s="277"/>
-      <c r="I13" s="277" t="s">
+      <c r="C13" s="360"/>
+      <c r="D13" s="360"/>
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="G13" s="360"/>
+      <c r="H13" s="360"/>
+      <c r="I13" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="277"/>
-      <c r="K13" s="277"/>
-      <c r="L13" s="277"/>
-      <c r="M13" s="277"/>
-      <c r="N13" s="277"/>
-      <c r="O13" s="277"/>
-      <c r="P13" s="277"/>
-      <c r="Q13" s="277" t="s">
+      <c r="J13" s="360"/>
+      <c r="K13" s="360"/>
+      <c r="L13" s="360"/>
+      <c r="M13" s="360"/>
+      <c r="N13" s="360"/>
+      <c r="O13" s="360"/>
+      <c r="P13" s="360"/>
+      <c r="Q13" s="360" t="s">
         <v>103</v>
       </c>
-      <c r="R13" s="277"/>
-      <c r="S13" s="277"/>
-      <c r="T13" s="277"/>
-      <c r="U13" s="277"/>
-      <c r="V13" s="277"/>
-      <c r="W13" s="277"/>
-      <c r="X13" s="277" t="s">
+      <c r="R13" s="360"/>
+      <c r="S13" s="360"/>
+      <c r="T13" s="360"/>
+      <c r="U13" s="360"/>
+      <c r="V13" s="360"/>
+      <c r="W13" s="360"/>
+      <c r="X13" s="360" t="s">
         <v>104</v>
       </c>
-      <c r="Y13" s="277"/>
-      <c r="Z13" s="277"/>
-      <c r="AA13" s="277"/>
-      <c r="AB13" s="277"/>
-      <c r="AC13" s="277"/>
-      <c r="AD13" s="277"/>
-      <c r="AE13" s="277"/>
-      <c r="AF13" s="277"/>
-      <c r="AG13" s="277"/>
-      <c r="AH13" s="277"/>
+      <c r="Y13" s="360"/>
+      <c r="Z13" s="360"/>
+      <c r="AA13" s="360"/>
+      <c r="AB13" s="360"/>
+      <c r="AC13" s="360"/>
+      <c r="AD13" s="360"/>
+      <c r="AE13" s="360"/>
+      <c r="AF13" s="360"/>
+      <c r="AG13" s="360"/>
+      <c r="AH13" s="360"/>
       <c r="AI13" s="130"/>
     </row>
     <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="B14" s="2"/>
-      <c r="C14" s="277" t="s">
+      <c r="C14" s="360" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="277"/>
-      <c r="E14" s="277"/>
-      <c r="F14" s="277"/>
-      <c r="G14" s="277"/>
-      <c r="H14" s="277"/>
+      <c r="D14" s="360"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
+      <c r="G14" s="360"/>
+      <c r="H14" s="360"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="277" t="s">
+      <c r="J14" s="360" t="s">
         <v>106</v>
       </c>
-      <c r="K14" s="277"/>
-      <c r="L14" s="277"/>
-      <c r="M14" s="277"/>
-      <c r="N14" s="277"/>
-      <c r="O14" s="277"/>
-      <c r="P14" s="277"/>
+      <c r="K14" s="360"/>
+      <c r="L14" s="360"/>
+      <c r="M14" s="360"/>
+      <c r="N14" s="360"/>
+      <c r="O14" s="360"/>
+      <c r="P14" s="360"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="131" t="s">
         <v>107</v>
       </c>
       <c r="X14" s="2"/>
-      <c r="Y14" s="277" t="s">
+      <c r="Y14" s="360" t="s">
         <v>108</v>
       </c>
-      <c r="Z14" s="277"/>
-      <c r="AA14" s="277"/>
-      <c r="AB14" s="277"/>
-      <c r="AC14" s="277"/>
-      <c r="AD14" s="277"/>
-      <c r="AE14" s="277"/>
-      <c r="AF14" s="277"/>
-      <c r="AG14" s="277"/>
-      <c r="AH14" s="277"/>
+      <c r="Z14" s="360"/>
+      <c r="AA14" s="360"/>
+      <c r="AB14" s="360"/>
+      <c r="AC14" s="360"/>
+      <c r="AD14" s="360"/>
+      <c r="AE14" s="360"/>
+      <c r="AF14" s="360"/>
+      <c r="AG14" s="360"/>
+      <c r="AH14" s="360"/>
     </row>
     <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="2"/>
-      <c r="C15" s="277" t="s">
+      <c r="C15" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="277"/>
-      <c r="E15" s="277"/>
-      <c r="F15" s="277"/>
-      <c r="G15" s="277"/>
-      <c r="H15" s="277"/>
+      <c r="D15" s="360"/>
+      <c r="E15" s="360"/>
+      <c r="F15" s="360"/>
+      <c r="G15" s="360"/>
+      <c r="H15" s="360"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="277" t="s">
+      <c r="J15" s="360" t="s">
         <v>110</v>
       </c>
-      <c r="K15" s="277"/>
-      <c r="L15" s="277"/>
-      <c r="M15" s="277"/>
-      <c r="N15" s="277"/>
-      <c r="O15" s="277"/>
-      <c r="P15" s="277"/>
+      <c r="K15" s="360"/>
+      <c r="L15" s="360"/>
+      <c r="M15" s="360"/>
+      <c r="N15" s="360"/>
+      <c r="O15" s="360"/>
+      <c r="P15" s="360"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="131" t="s">
         <v>111</v>
       </c>
       <c r="X15" s="2"/>
-      <c r="Y15" s="277" t="s">
+      <c r="Y15" s="360" t="s">
         <v>112</v>
       </c>
-      <c r="Z15" s="277"/>
-      <c r="AA15" s="277"/>
-      <c r="AB15" s="277"/>
-      <c r="AC15" s="277"/>
-      <c r="AD15" s="277"/>
-      <c r="AE15" s="277"/>
-      <c r="AF15" s="277"/>
-      <c r="AG15" s="277"/>
-      <c r="AH15" s="277"/>
+      <c r="Z15" s="360"/>
+      <c r="AA15" s="360"/>
+      <c r="AB15" s="360"/>
+      <c r="AC15" s="360"/>
+      <c r="AD15" s="360"/>
+      <c r="AE15" s="360"/>
+      <c r="AF15" s="360"/>
+      <c r="AG15" s="360"/>
+      <c r="AH15" s="360"/>
     </row>
     <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B16" s="2"/>
-      <c r="C16" s="277" t="s">
+      <c r="C16" s="360" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="277"/>
-      <c r="E16" s="277"/>
-      <c r="F16" s="277"/>
-      <c r="G16" s="277"/>
-      <c r="H16" s="277"/>
+      <c r="D16" s="360"/>
+      <c r="E16" s="360"/>
+      <c r="F16" s="360"/>
+      <c r="G16" s="360"/>
+      <c r="H16" s="360"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="277" t="s">
+      <c r="J16" s="360" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="277"/>
-      <c r="L16" s="277"/>
-      <c r="M16" s="277"/>
-      <c r="N16" s="277"/>
-      <c r="O16" s="277"/>
-      <c r="P16" s="277"/>
+      <c r="K16" s="360"/>
+      <c r="L16" s="360"/>
+      <c r="M16" s="360"/>
+      <c r="N16" s="360"/>
+      <c r="O16" s="360"/>
+      <c r="P16" s="360"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="131" t="s">
         <v>115</v>
@@ -39221,35 +39221,35 @@
         <v>116</v>
       </c>
       <c r="Z16" s="131"/>
-      <c r="AA16" s="278"/>
-      <c r="AB16" s="278"/>
-      <c r="AC16" s="278"/>
-      <c r="AD16" s="278"/>
-      <c r="AE16" s="278"/>
+      <c r="AA16" s="365"/>
+      <c r="AB16" s="365"/>
+      <c r="AC16" s="365"/>
+      <c r="AD16" s="365"/>
+      <c r="AE16" s="365"/>
       <c r="AF16" s="131"/>
       <c r="AG16" s="131"/>
       <c r="AH16" s="131"/>
     </row>
     <row r="17" spans="2:34" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="2"/>
-      <c r="C17" s="277" t="s">
+      <c r="C17" s="360" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="277"/>
-      <c r="E17" s="277"/>
-      <c r="F17" s="277"/>
-      <c r="G17" s="277"/>
-      <c r="H17" s="277"/>
+      <c r="D17" s="360"/>
+      <c r="E17" s="360"/>
+      <c r="F17" s="360"/>
+      <c r="G17" s="360"/>
+      <c r="H17" s="360"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="277" t="s">
+      <c r="J17" s="360" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="277"/>
-      <c r="L17" s="277"/>
-      <c r="M17" s="277"/>
-      <c r="N17" s="277"/>
-      <c r="O17" s="277"/>
-      <c r="P17" s="277"/>
+      <c r="K17" s="360"/>
+      <c r="L17" s="360"/>
+      <c r="M17" s="360"/>
+      <c r="N17" s="360"/>
+      <c r="O17" s="360"/>
+      <c r="P17" s="360"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="131" t="s">
         <v>119</v>
@@ -39257,56 +39257,56 @@
     </row>
     <row r="18" spans="2:34" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="2"/>
-      <c r="C18" s="277" t="s">
+      <c r="C18" s="360" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="277"/>
-      <c r="E18" s="277"/>
-      <c r="F18" s="277"/>
-      <c r="G18" s="277"/>
-      <c r="H18" s="277"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
+      <c r="G18" s="360"/>
+      <c r="H18" s="360"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="277" t="s">
+      <c r="J18" s="360" t="s">
         <v>121</v>
       </c>
-      <c r="K18" s="277"/>
-      <c r="L18" s="277"/>
-      <c r="M18" s="277"/>
-      <c r="N18" s="277"/>
-      <c r="O18" s="277"/>
-      <c r="P18" s="277"/>
+      <c r="K18" s="360"/>
+      <c r="L18" s="360"/>
+      <c r="M18" s="360"/>
+      <c r="N18" s="360"/>
+      <c r="O18" s="360"/>
+      <c r="P18" s="360"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="131" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="19" spans="2:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="232"/>
+      <c r="B19" s="251"/>
+      <c r="C19" s="251"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
       <c r="I19" s="132"/>
       <c r="J19" s="131" t="s">
         <v>123</v>
       </c>
       <c r="K19" s="131"/>
-      <c r="L19" s="292"/>
-      <c r="M19" s="292"/>
-      <c r="N19" s="292"/>
-      <c r="O19" s="292"/>
-      <c r="P19" s="293"/>
+      <c r="L19" s="361"/>
+      <c r="M19" s="361"/>
+      <c r="N19" s="361"/>
+      <c r="O19" s="361"/>
+      <c r="P19" s="362"/>
       <c r="Q19" s="132"/>
       <c r="R19" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="T19" s="279"/>
-      <c r="U19" s="279"/>
-      <c r="V19" s="279"/>
-      <c r="W19" s="279"/>
-      <c r="X19" s="279"/>
+      <c r="T19" s="354"/>
+      <c r="U19" s="354"/>
+      <c r="V19" s="354"/>
+      <c r="W19" s="354"/>
+      <c r="X19" s="354"/>
     </row>
     <row r="20" spans="2:34" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="133" t="s">
@@ -39315,21 +39315,21 @@
       <c r="C20" s="134"/>
       <c r="D20" s="134"/>
       <c r="E20" s="134"/>
-      <c r="F20" s="280">
+      <c r="F20" s="355">
         <f>'DATA ENTRY'!D5</f>
-        <v>37700.5</v>
-      </c>
-      <c r="G20" s="280"/>
-      <c r="H20" s="280"/>
-      <c r="I20" s="280"/>
-      <c r="J20" s="280"/>
-      <c r="K20" s="280"/>
-      <c r="L20" s="281"/>
-      <c r="M20" s="281"/>
-      <c r="N20" s="281"/>
-      <c r="O20" s="281"/>
-      <c r="P20" s="281"/>
-      <c r="Q20" s="282"/>
+        <v>15979.6</v>
+      </c>
+      <c r="G20" s="355"/>
+      <c r="H20" s="355"/>
+      <c r="I20" s="355"/>
+      <c r="J20" s="355"/>
+      <c r="K20" s="355"/>
+      <c r="L20" s="356"/>
+      <c r="M20" s="356"/>
+      <c r="N20" s="356"/>
+      <c r="O20" s="356"/>
+      <c r="P20" s="356"/>
+      <c r="Q20" s="357"/>
       <c r="R20" s="133" t="s">
         <v>125</v>
       </c>
@@ -39338,108 +39338,108 @@
       <c r="U20" s="135"/>
       <c r="V20" s="135"/>
       <c r="W20" s="135"/>
-      <c r="X20" s="281">
+      <c r="X20" s="356">
         <f>'DATA ENTRY'!D16</f>
-        <v>2000.0040005269973</v>
-      </c>
-      <c r="Y20" s="280"/>
-      <c r="Z20" s="280"/>
-      <c r="AA20" s="280"/>
-      <c r="AB20" s="280"/>
-      <c r="AC20" s="280"/>
-      <c r="AD20" s="280"/>
-      <c r="AE20" s="280"/>
-      <c r="AF20" s="280"/>
-      <c r="AG20" s="280"/>
-      <c r="AH20" s="282"/>
+        <v>949.99785840431502</v>
+      </c>
+      <c r="Y20" s="355"/>
+      <c r="Z20" s="355"/>
+      <c r="AA20" s="355"/>
+      <c r="AB20" s="355"/>
+      <c r="AC20" s="355"/>
+      <c r="AD20" s="355"/>
+      <c r="AE20" s="355"/>
+      <c r="AF20" s="355"/>
+      <c r="AG20" s="355"/>
+      <c r="AH20" s="357"/>
     </row>
     <row r="21" spans="2:34" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="136"/>
       <c r="C21" s="137"/>
       <c r="D21" s="137"/>
       <c r="E21" s="137"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="283"/>
-      <c r="H21" s="283"/>
-      <c r="I21" s="283"/>
-      <c r="J21" s="283"/>
-      <c r="K21" s="283"/>
-      <c r="L21" s="283"/>
-      <c r="M21" s="283"/>
-      <c r="N21" s="283"/>
-      <c r="O21" s="283"/>
-      <c r="P21" s="283"/>
-      <c r="Q21" s="284"/>
+      <c r="F21" s="282"/>
+      <c r="G21" s="282"/>
+      <c r="H21" s="282"/>
+      <c r="I21" s="282"/>
+      <c r="J21" s="282"/>
+      <c r="K21" s="282"/>
+      <c r="L21" s="282"/>
+      <c r="M21" s="282"/>
+      <c r="N21" s="282"/>
+      <c r="O21" s="282"/>
+      <c r="P21" s="282"/>
+      <c r="Q21" s="283"/>
       <c r="R21" s="136"/>
       <c r="S21" s="137"/>
       <c r="T21" s="137"/>
       <c r="U21" s="137"/>
       <c r="V21" s="137"/>
       <c r="W21" s="137"/>
-      <c r="X21" s="283"/>
-      <c r="Y21" s="283"/>
-      <c r="Z21" s="283"/>
-      <c r="AA21" s="283"/>
-      <c r="AB21" s="283"/>
-      <c r="AC21" s="283"/>
-      <c r="AD21" s="283"/>
-      <c r="AE21" s="283"/>
-      <c r="AF21" s="283"/>
-      <c r="AG21" s="283"/>
-      <c r="AH21" s="284"/>
+      <c r="X21" s="282"/>
+      <c r="Y21" s="282"/>
+      <c r="Z21" s="282"/>
+      <c r="AA21" s="282"/>
+      <c r="AB21" s="282"/>
+      <c r="AC21" s="282"/>
+      <c r="AD21" s="282"/>
+      <c r="AE21" s="282"/>
+      <c r="AF21" s="282"/>
+      <c r="AG21" s="282"/>
+      <c r="AH21" s="283"/>
     </row>
     <row r="22" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="285" t="s">
+      <c r="B22" s="335" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="286"/>
-      <c r="D22" s="287"/>
-      <c r="E22" s="288"/>
-      <c r="F22" s="288"/>
-      <c r="G22" s="288"/>
-      <c r="H22" s="288"/>
-      <c r="I22" s="289"/>
+      <c r="C22" s="336"/>
+      <c r="D22" s="340"/>
+      <c r="E22" s="341"/>
+      <c r="F22" s="341"/>
+      <c r="G22" s="341"/>
+      <c r="H22" s="341"/>
+      <c r="I22" s="342"/>
       <c r="J22" s="139" t="s">
         <v>127</v>
       </c>
       <c r="K22" s="137"/>
       <c r="L22" s="137"/>
       <c r="M22" s="137"/>
-      <c r="N22" s="290"/>
-      <c r="O22" s="290"/>
-      <c r="P22" s="290"/>
-      <c r="Q22" s="290"/>
-      <c r="R22" s="290"/>
-      <c r="S22" s="290"/>
-      <c r="T22" s="290"/>
-      <c r="U22" s="291"/>
+      <c r="N22" s="358"/>
+      <c r="O22" s="358"/>
+      <c r="P22" s="358"/>
+      <c r="Q22" s="358"/>
+      <c r="R22" s="358"/>
+      <c r="S22" s="358"/>
+      <c r="T22" s="358"/>
+      <c r="U22" s="359"/>
       <c r="V22" s="140" t="s">
         <v>128</v>
       </c>
       <c r="W22" s="141"/>
       <c r="X22" s="141"/>
       <c r="Y22" s="141"/>
-      <c r="Z22" s="290"/>
-      <c r="AA22" s="290"/>
-      <c r="AB22" s="290"/>
-      <c r="AC22" s="290"/>
-      <c r="AD22" s="290"/>
-      <c r="AE22" s="290"/>
-      <c r="AF22" s="290"/>
-      <c r="AG22" s="290"/>
-      <c r="AH22" s="291"/>
+      <c r="Z22" s="358"/>
+      <c r="AA22" s="358"/>
+      <c r="AB22" s="358"/>
+      <c r="AC22" s="358"/>
+      <c r="AD22" s="358"/>
+      <c r="AE22" s="358"/>
+      <c r="AF22" s="358"/>
+      <c r="AG22" s="358"/>
+      <c r="AH22" s="359"/>
     </row>
     <row r="23" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="294" t="s">
+      <c r="B23" s="333" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="295"/>
-      <c r="D23" s="296"/>
-      <c r="E23" s="297"/>
-      <c r="F23" s="297"/>
-      <c r="G23" s="297"/>
-      <c r="H23" s="297"/>
-      <c r="I23" s="298"/>
+      <c r="C23" s="334"/>
+      <c r="D23" s="337"/>
+      <c r="E23" s="338"/>
+      <c r="F23" s="338"/>
+      <c r="G23" s="338"/>
+      <c r="H23" s="338"/>
+      <c r="I23" s="339"/>
       <c r="J23" s="143"/>
       <c r="K23" s="142" t="s">
         <v>130</v>
@@ -39455,11 +39455,11 @@
       <c r="T23" s="144"/>
       <c r="U23" s="145"/>
       <c r="V23" s="146"/>
-      <c r="W23" s="294" t="s">
+      <c r="W23" s="333" t="s">
         <v>131</v>
       </c>
-      <c r="X23" s="299"/>
-      <c r="Y23" s="299"/>
+      <c r="X23" s="343"/>
+      <c r="Y23" s="343"/>
       <c r="Z23" s="144"/>
       <c r="AA23" s="144"/>
       <c r="AB23" s="144"/>
@@ -39471,14 +39471,14 @@
       <c r="AH23" s="145"/>
     </row>
     <row r="24" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="285"/>
-      <c r="C24" s="286"/>
-      <c r="D24" s="287"/>
-      <c r="E24" s="288"/>
-      <c r="F24" s="288"/>
-      <c r="G24" s="288"/>
-      <c r="H24" s="288"/>
-      <c r="I24" s="289"/>
+      <c r="B24" s="335"/>
+      <c r="C24" s="336"/>
+      <c r="D24" s="340"/>
+      <c r="E24" s="341"/>
+      <c r="F24" s="341"/>
+      <c r="G24" s="341"/>
+      <c r="H24" s="341"/>
+      <c r="I24" s="342"/>
       <c r="J24" s="2"/>
       <c r="K24" s="138" t="s">
         <v>132</v>
@@ -39494,11 +39494,11 @@
       <c r="T24" s="147"/>
       <c r="U24" s="148"/>
       <c r="V24" s="2"/>
-      <c r="W24" s="285" t="s">
+      <c r="W24" s="335" t="s">
         <v>133</v>
       </c>
-      <c r="X24" s="300"/>
-      <c r="Y24" s="300"/>
+      <c r="X24" s="344"/>
+      <c r="Y24" s="344"/>
       <c r="Z24" s="147"/>
       <c r="AA24" s="147"/>
       <c r="AB24" s="147"/>
@@ -39510,41 +39510,41 @@
       <c r="AH24" s="148"/>
     </row>
     <row r="25" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="273" t="s">
+      <c r="B25" s="345" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="274"/>
-      <c r="D25" s="274"/>
-      <c r="E25" s="274"/>
-      <c r="F25" s="274"/>
-      <c r="G25" s="274"/>
-      <c r="H25" s="274"/>
-      <c r="I25" s="274"/>
-      <c r="J25" s="274"/>
-      <c r="K25" s="274"/>
-      <c r="L25" s="274"/>
-      <c r="M25" s="274"/>
-      <c r="N25" s="274"/>
-      <c r="O25" s="274"/>
-      <c r="P25" s="274"/>
-      <c r="Q25" s="274"/>
-      <c r="R25" s="274"/>
-      <c r="S25" s="274"/>
-      <c r="T25" s="274"/>
-      <c r="U25" s="274"/>
-      <c r="V25" s="274"/>
-      <c r="W25" s="274"/>
-      <c r="X25" s="274"/>
-      <c r="Y25" s="274"/>
-      <c r="Z25" s="274"/>
-      <c r="AA25" s="274"/>
-      <c r="AB25" s="274"/>
-      <c r="AC25" s="274"/>
-      <c r="AD25" s="274"/>
-      <c r="AE25" s="274"/>
-      <c r="AF25" s="274"/>
-      <c r="AG25" s="274"/>
-      <c r="AH25" s="275"/>
+      <c r="C25" s="346"/>
+      <c r="D25" s="346"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
+      <c r="G25" s="346"/>
+      <c r="H25" s="346"/>
+      <c r="I25" s="346"/>
+      <c r="J25" s="346"/>
+      <c r="K25" s="346"/>
+      <c r="L25" s="346"/>
+      <c r="M25" s="346"/>
+      <c r="N25" s="346"/>
+      <c r="O25" s="346"/>
+      <c r="P25" s="346"/>
+      <c r="Q25" s="346"/>
+      <c r="R25" s="346"/>
+      <c r="S25" s="346"/>
+      <c r="T25" s="346"/>
+      <c r="U25" s="346"/>
+      <c r="V25" s="346"/>
+      <c r="W25" s="346"/>
+      <c r="X25" s="346"/>
+      <c r="Y25" s="346"/>
+      <c r="Z25" s="346"/>
+      <c r="AA25" s="346"/>
+      <c r="AB25" s="346"/>
+      <c r="AC25" s="346"/>
+      <c r="AD25" s="346"/>
+      <c r="AE25" s="346"/>
+      <c r="AF25" s="346"/>
+      <c r="AG25" s="346"/>
+      <c r="AH25" s="347"/>
     </row>
     <row r="26" spans="2:34" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B26" s="149" t="s">
@@ -39628,83 +39628,83 @@
       <c r="AH27" s="152"/>
     </row>
     <row r="28" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="301" t="s">
+      <c r="B28" s="348" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
-      <c r="F28" s="302"/>
-      <c r="G28" s="303"/>
-      <c r="H28" s="301" t="s">
+      <c r="C28" s="349"/>
+      <c r="D28" s="349"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
+      <c r="G28" s="350"/>
+      <c r="H28" s="348" t="s">
         <v>65</v>
       </c>
-      <c r="I28" s="302"/>
-      <c r="J28" s="302"/>
-      <c r="K28" s="302"/>
-      <c r="L28" s="303"/>
-      <c r="M28" s="301" t="s">
+      <c r="I28" s="349"/>
+      <c r="J28" s="349"/>
+      <c r="K28" s="349"/>
+      <c r="L28" s="350"/>
+      <c r="M28" s="348" t="s">
         <v>140</v>
       </c>
-      <c r="N28" s="302"/>
-      <c r="O28" s="302"/>
-      <c r="P28" s="302"/>
-      <c r="Q28" s="302"/>
-      <c r="R28" s="303"/>
-      <c r="S28" s="304" t="s">
+      <c r="N28" s="349"/>
+      <c r="O28" s="349"/>
+      <c r="P28" s="349"/>
+      <c r="Q28" s="349"/>
+      <c r="R28" s="350"/>
+      <c r="S28" s="351" t="s">
         <v>141</v>
       </c>
-      <c r="T28" s="305"/>
-      <c r="U28" s="305"/>
-      <c r="V28" s="305"/>
-      <c r="W28" s="305"/>
-      <c r="X28" s="305"/>
-      <c r="Y28" s="305"/>
-      <c r="Z28" s="305"/>
-      <c r="AA28" s="304" t="s">
+      <c r="T28" s="352"/>
+      <c r="U28" s="352"/>
+      <c r="V28" s="352"/>
+      <c r="W28" s="352"/>
+      <c r="X28" s="352"/>
+      <c r="Y28" s="352"/>
+      <c r="Z28" s="352"/>
+      <c r="AA28" s="351" t="s">
         <v>142</v>
       </c>
-      <c r="AB28" s="305"/>
-      <c r="AC28" s="305"/>
-      <c r="AD28" s="305"/>
-      <c r="AE28" s="305"/>
-      <c r="AF28" s="305"/>
-      <c r="AG28" s="305"/>
-      <c r="AH28" s="306"/>
+      <c r="AB28" s="352"/>
+      <c r="AC28" s="352"/>
+      <c r="AD28" s="352"/>
+      <c r="AE28" s="352"/>
+      <c r="AF28" s="352"/>
+      <c r="AG28" s="352"/>
+      <c r="AH28" s="353"/>
     </row>
     <row r="29" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B29" s="311" t="s">
+      <c r="B29" s="326" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="312"/>
-      <c r="D29" s="312"/>
-      <c r="E29" s="312"/>
-      <c r="F29" s="312"/>
-      <c r="G29" s="313"/>
-      <c r="H29" s="314">
+      <c r="C29" s="327"/>
+      <c r="D29" s="327"/>
+      <c r="E29" s="327"/>
+      <c r="F29" s="327"/>
+      <c r="G29" s="328"/>
+      <c r="H29" s="329">
         <v>716611</v>
       </c>
-      <c r="I29" s="315"/>
-      <c r="J29" s="315"/>
-      <c r="K29" s="315"/>
-      <c r="L29" s="316"/>
-      <c r="M29" s="311" t="s">
+      <c r="I29" s="330"/>
+      <c r="J29" s="330"/>
+      <c r="K29" s="330"/>
+      <c r="L29" s="331"/>
+      <c r="M29" s="326" t="s">
         <v>272</v>
       </c>
-      <c r="N29" s="312"/>
-      <c r="O29" s="312"/>
-      <c r="P29" s="312"/>
-      <c r="Q29" s="312"/>
-      <c r="R29" s="313"/>
+      <c r="N29" s="327"/>
+      <c r="O29" s="327"/>
+      <c r="P29" s="327"/>
+      <c r="Q29" s="327"/>
+      <c r="R29" s="328"/>
       <c r="S29" s="126"/>
-      <c r="T29" s="317" t="s">
+      <c r="T29" s="332" t="s">
         <v>97</v>
       </c>
-      <c r="U29" s="317"/>
-      <c r="V29" s="317" t="s">
+      <c r="U29" s="332"/>
+      <c r="V29" s="332" t="s">
         <v>97</v>
       </c>
-      <c r="W29" s="317"/>
+      <c r="W29" s="332"/>
       <c r="X29" s="127"/>
       <c r="Y29" s="127"/>
       <c r="Z29" s="128"/>
@@ -39803,106 +39803,106 @@
       <c r="N32" s="154" t="s">
         <v>145</v>
       </c>
-      <c r="O32" s="307">
+      <c r="O32" s="323">
         <v>65</v>
       </c>
-      <c r="P32" s="308"/>
-      <c r="Q32" s="309" t="s">
+      <c r="P32" s="324"/>
+      <c r="Q32" s="325" t="s">
         <v>146</v>
       </c>
-      <c r="R32" s="309"/>
-      <c r="S32" s="309"/>
-      <c r="T32" s="309"/>
+      <c r="R32" s="325"/>
+      <c r="S32" s="325"/>
+      <c r="T32" s="325"/>
       <c r="U32" s="155"/>
-      <c r="V32" s="310" t="s">
+      <c r="V32" s="312" t="s">
         <v>147</v>
       </c>
-      <c r="W32" s="310"/>
+      <c r="W32" s="312"/>
       <c r="X32" s="155"/>
-      <c r="Y32" s="310" t="s">
+      <c r="Y32" s="312" t="s">
         <v>148</v>
       </c>
-      <c r="Z32" s="310"/>
-      <c r="AA32" s="310"/>
-      <c r="AB32" s="310" t="s">
+      <c r="Z32" s="312"/>
+      <c r="AA32" s="312"/>
+      <c r="AB32" s="312" t="s">
         <v>149</v>
       </c>
-      <c r="AC32" s="310"/>
-      <c r="AD32" s="310"/>
-      <c r="AE32" s="310"/>
-      <c r="AF32" s="310"/>
-      <c r="AG32" s="310"/>
-      <c r="AH32" s="310"/>
+      <c r="AC32" s="312"/>
+      <c r="AD32" s="312"/>
+      <c r="AE32" s="312"/>
+      <c r="AF32" s="312"/>
+      <c r="AG32" s="312"/>
+      <c r="AH32" s="312"/>
     </row>
     <row r="33" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="324"/>
-      <c r="C33" s="325"/>
-      <c r="D33" s="325"/>
-      <c r="E33" s="325"/>
-      <c r="F33" s="325"/>
-      <c r="G33" s="325"/>
-      <c r="H33" s="326"/>
-      <c r="I33" s="327">
+      <c r="B33" s="313"/>
+      <c r="C33" s="314"/>
+      <c r="D33" s="314"/>
+      <c r="E33" s="314"/>
+      <c r="F33" s="314"/>
+      <c r="G33" s="314"/>
+      <c r="H33" s="315"/>
+      <c r="I33" s="316">
         <v>22254</v>
       </c>
-      <c r="J33" s="328"/>
-      <c r="K33" s="328"/>
-      <c r="L33" s="328"/>
-      <c r="M33" s="328"/>
-      <c r="N33" s="328"/>
-      <c r="O33" s="328"/>
-      <c r="P33" s="329"/>
-      <c r="Q33" s="309"/>
-      <c r="R33" s="309"/>
-      <c r="S33" s="309"/>
-      <c r="T33" s="309"/>
+      <c r="J33" s="317"/>
+      <c r="K33" s="317"/>
+      <c r="L33" s="317"/>
+      <c r="M33" s="317"/>
+      <c r="N33" s="317"/>
+      <c r="O33" s="317"/>
+      <c r="P33" s="318"/>
+      <c r="Q33" s="325"/>
+      <c r="R33" s="325"/>
+      <c r="S33" s="325"/>
+      <c r="T33" s="325"/>
       <c r="U33" s="155"/>
-      <c r="V33" s="310" t="s">
+      <c r="V33" s="312" t="s">
         <v>150</v>
       </c>
-      <c r="W33" s="310"/>
+      <c r="W33" s="312"/>
       <c r="X33" s="155"/>
-      <c r="Y33" s="310" t="s">
+      <c r="Y33" s="312" t="s">
         <v>151</v>
       </c>
-      <c r="Z33" s="310"/>
-      <c r="AA33" s="310"/>
-      <c r="AB33" s="330"/>
-      <c r="AC33" s="331"/>
-      <c r="AD33" s="331"/>
-      <c r="AE33" s="331"/>
-      <c r="AF33" s="331"/>
-      <c r="AG33" s="331"/>
-      <c r="AH33" s="332"/>
+      <c r="Z33" s="312"/>
+      <c r="AA33" s="312"/>
+      <c r="AB33" s="319"/>
+      <c r="AC33" s="320"/>
+      <c r="AD33" s="320"/>
+      <c r="AE33" s="320"/>
+      <c r="AF33" s="320"/>
+      <c r="AG33" s="320"/>
+      <c r="AH33" s="321"/>
     </row>
     <row r="34" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="333" t="s">
+      <c r="B34" s="322" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="333"/>
-      <c r="D34" s="333"/>
-      <c r="E34" s="333"/>
-      <c r="F34" s="333"/>
-      <c r="G34" s="333"/>
-      <c r="H34" s="333"/>
-      <c r="I34" s="333" t="s">
+      <c r="C34" s="322"/>
+      <c r="D34" s="322"/>
+      <c r="E34" s="322"/>
+      <c r="F34" s="322"/>
+      <c r="G34" s="322"/>
+      <c r="H34" s="322"/>
+      <c r="I34" s="322" t="s">
         <v>153</v>
       </c>
-      <c r="J34" s="333"/>
-      <c r="K34" s="333"/>
-      <c r="L34" s="333"/>
-      <c r="M34" s="333"/>
-      <c r="N34" s="333"/>
-      <c r="O34" s="333"/>
-      <c r="P34" s="333"/>
-      <c r="Q34" s="333"/>
-      <c r="R34" s="333"/>
-      <c r="S34" s="333"/>
-      <c r="T34" s="333"/>
-      <c r="U34" s="333"/>
-      <c r="V34" s="333"/>
-      <c r="W34" s="333"/>
-      <c r="X34" s="333"/>
+      <c r="J34" s="322"/>
+      <c r="K34" s="322"/>
+      <c r="L34" s="322"/>
+      <c r="M34" s="322"/>
+      <c r="N34" s="322"/>
+      <c r="O34" s="322"/>
+      <c r="P34" s="322"/>
+      <c r="Q34" s="322"/>
+      <c r="R34" s="322"/>
+      <c r="S34" s="322"/>
+      <c r="T34" s="322"/>
+      <c r="U34" s="322"/>
+      <c r="V34" s="322"/>
+      <c r="W34" s="322"/>
+      <c r="X34" s="322"/>
       <c r="Z34" s="135"/>
       <c r="AA34" s="135"/>
       <c r="AB34" s="135" t="s">
@@ -39916,39 +39916,39 @@
       <c r="AH34" s="135"/>
     </row>
     <row r="35" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="318"/>
-      <c r="C35" s="319"/>
-      <c r="D35" s="319"/>
-      <c r="E35" s="319"/>
-      <c r="F35" s="319"/>
-      <c r="G35" s="319"/>
-      <c r="H35" s="320"/>
-      <c r="I35" s="321"/>
-      <c r="J35" s="322"/>
-      <c r="K35" s="322"/>
-      <c r="L35" s="322"/>
-      <c r="M35" s="322"/>
-      <c r="N35" s="322"/>
-      <c r="O35" s="322"/>
-      <c r="P35" s="322"/>
-      <c r="Q35" s="322"/>
-      <c r="R35" s="322"/>
-      <c r="S35" s="322"/>
-      <c r="T35" s="322"/>
-      <c r="U35" s="322"/>
-      <c r="V35" s="322"/>
-      <c r="W35" s="322"/>
-      <c r="X35" s="322"/>
-      <c r="Y35" s="322"/>
-      <c r="Z35" s="322"/>
-      <c r="AA35" s="323"/>
-      <c r="AB35" s="321"/>
-      <c r="AC35" s="322"/>
-      <c r="AD35" s="322"/>
-      <c r="AE35" s="322"/>
-      <c r="AF35" s="322"/>
-      <c r="AG35" s="322"/>
-      <c r="AH35" s="323"/>
+      <c r="B35" s="306"/>
+      <c r="C35" s="307"/>
+      <c r="D35" s="307"/>
+      <c r="E35" s="307"/>
+      <c r="F35" s="307"/>
+      <c r="G35" s="307"/>
+      <c r="H35" s="308"/>
+      <c r="I35" s="309"/>
+      <c r="J35" s="310"/>
+      <c r="K35" s="310"/>
+      <c r="L35" s="310"/>
+      <c r="M35" s="310"/>
+      <c r="N35" s="310"/>
+      <c r="O35" s="310"/>
+      <c r="P35" s="310"/>
+      <c r="Q35" s="310"/>
+      <c r="R35" s="310"/>
+      <c r="S35" s="310"/>
+      <c r="T35" s="310"/>
+      <c r="U35" s="310"/>
+      <c r="V35" s="310"/>
+      <c r="W35" s="310"/>
+      <c r="X35" s="310"/>
+      <c r="Y35" s="310"/>
+      <c r="Z35" s="310"/>
+      <c r="AA35" s="311"/>
+      <c r="AB35" s="309"/>
+      <c r="AC35" s="310"/>
+      <c r="AD35" s="310"/>
+      <c r="AE35" s="310"/>
+      <c r="AF35" s="310"/>
+      <c r="AG35" s="310"/>
+      <c r="AH35" s="311"/>
     </row>
     <row r="36" spans="2:34" ht="20.100000000000001" customHeight="1">
       <c r="B36" s="130" t="s">
@@ -39973,43 +39973,43 @@
       <c r="U36" s="135"/>
       <c r="V36" s="135"/>
       <c r="W36" s="135"/>
-      <c r="X36" s="310" t="s">
+      <c r="X36" s="312" t="s">
         <v>157</v>
       </c>
-      <c r="Y36" s="310"/>
-      <c r="Z36" s="310"/>
-      <c r="AA36" s="310"/>
-      <c r="AB36" s="310"/>
-      <c r="AC36" s="310"/>
-      <c r="AD36" s="310"/>
-      <c r="AE36" s="310"/>
-      <c r="AF36" s="310"/>
-      <c r="AG36" s="310"/>
-      <c r="AH36" s="310"/>
+      <c r="Y36" s="312"/>
+      <c r="Z36" s="312"/>
+      <c r="AA36" s="312"/>
+      <c r="AB36" s="312"/>
+      <c r="AC36" s="312"/>
+      <c r="AD36" s="312"/>
+      <c r="AE36" s="312"/>
+      <c r="AF36" s="312"/>
+      <c r="AG36" s="312"/>
+      <c r="AH36" s="312"/>
     </row>
     <row r="37" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="321"/>
-      <c r="C37" s="322"/>
-      <c r="D37" s="322"/>
-      <c r="E37" s="322"/>
-      <c r="F37" s="322"/>
-      <c r="G37" s="322"/>
-      <c r="H37" s="322"/>
-      <c r="I37" s="322"/>
-      <c r="J37" s="323"/>
-      <c r="K37" s="318"/>
-      <c r="L37" s="319"/>
-      <c r="M37" s="319"/>
-      <c r="N37" s="319"/>
-      <c r="O37" s="319"/>
-      <c r="P37" s="319"/>
-      <c r="Q37" s="319"/>
-      <c r="R37" s="319"/>
-      <c r="S37" s="319"/>
-      <c r="T37" s="319"/>
-      <c r="U37" s="319"/>
-      <c r="V37" s="319"/>
-      <c r="W37" s="320"/>
+      <c r="B37" s="309"/>
+      <c r="C37" s="310"/>
+      <c r="D37" s="310"/>
+      <c r="E37" s="310"/>
+      <c r="F37" s="310"/>
+      <c r="G37" s="310"/>
+      <c r="H37" s="310"/>
+      <c r="I37" s="310"/>
+      <c r="J37" s="311"/>
+      <c r="K37" s="306"/>
+      <c r="L37" s="307"/>
+      <c r="M37" s="307"/>
+      <c r="N37" s="307"/>
+      <c r="O37" s="307"/>
+      <c r="P37" s="307"/>
+      <c r="Q37" s="307"/>
+      <c r="R37" s="307"/>
+      <c r="S37" s="307"/>
+      <c r="T37" s="307"/>
+      <c r="U37" s="307"/>
+      <c r="V37" s="307"/>
+      <c r="W37" s="308"/>
       <c r="X37" s="156">
         <v>9</v>
       </c>
@@ -40051,74 +40051,74 @@
       <c r="C38" s="135"/>
       <c r="D38" s="135"/>
       <c r="E38" s="135"/>
-      <c r="F38" s="334" t="s">
+      <c r="F38" s="303" t="s">
         <v>240</v>
       </c>
-      <c r="G38" s="335"/>
-      <c r="H38" s="335"/>
-      <c r="I38" s="335"/>
-      <c r="J38" s="335"/>
-      <c r="K38" s="335"/>
-      <c r="L38" s="335"/>
-      <c r="M38" s="335"/>
-      <c r="N38" s="335"/>
-      <c r="O38" s="335"/>
-      <c r="P38" s="335"/>
-      <c r="Q38" s="335"/>
-      <c r="R38" s="335"/>
-      <c r="S38" s="335"/>
-      <c r="T38" s="335"/>
-      <c r="U38" s="335"/>
-      <c r="V38" s="335"/>
-      <c r="W38" s="335"/>
-      <c r="X38" s="335"/>
-      <c r="Y38" s="335"/>
-      <c r="Z38" s="335"/>
-      <c r="AA38" s="335"/>
-      <c r="AB38" s="335"/>
-      <c r="AC38" s="335"/>
-      <c r="AD38" s="335"/>
-      <c r="AE38" s="335"/>
-      <c r="AF38" s="335"/>
-      <c r="AG38" s="335"/>
-      <c r="AH38" s="336"/>
+      <c r="G38" s="304"/>
+      <c r="H38" s="304"/>
+      <c r="I38" s="304"/>
+      <c r="J38" s="304"/>
+      <c r="K38" s="304"/>
+      <c r="L38" s="304"/>
+      <c r="M38" s="304"/>
+      <c r="N38" s="304"/>
+      <c r="O38" s="304"/>
+      <c r="P38" s="304"/>
+      <c r="Q38" s="304"/>
+      <c r="R38" s="304"/>
+      <c r="S38" s="304"/>
+      <c r="T38" s="304"/>
+      <c r="U38" s="304"/>
+      <c r="V38" s="304"/>
+      <c r="W38" s="304"/>
+      <c r="X38" s="304"/>
+      <c r="Y38" s="304"/>
+      <c r="Z38" s="304"/>
+      <c r="AA38" s="304"/>
+      <c r="AB38" s="304"/>
+      <c r="AC38" s="304"/>
+      <c r="AD38" s="304"/>
+      <c r="AE38" s="304"/>
+      <c r="AF38" s="304"/>
+      <c r="AG38" s="304"/>
+      <c r="AH38" s="305"/>
     </row>
     <row r="39" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="287" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
-      <c r="G39" s="338"/>
-      <c r="H39" s="338"/>
-      <c r="I39" s="338"/>
-      <c r="J39" s="338"/>
-      <c r="K39" s="338"/>
-      <c r="L39" s="338"/>
-      <c r="M39" s="338"/>
-      <c r="N39" s="338"/>
-      <c r="O39" s="338"/>
-      <c r="P39" s="338"/>
-      <c r="Q39" s="338"/>
-      <c r="R39" s="338"/>
-      <c r="S39" s="338"/>
-      <c r="T39" s="338"/>
-      <c r="U39" s="338"/>
-      <c r="V39" s="338"/>
-      <c r="W39" s="338"/>
-      <c r="X39" s="338"/>
-      <c r="Y39" s="338"/>
-      <c r="Z39" s="338"/>
-      <c r="AA39" s="338"/>
-      <c r="AB39" s="338"/>
-      <c r="AC39" s="338"/>
-      <c r="AD39" s="338"/>
-      <c r="AE39" s="338"/>
-      <c r="AF39" s="338"/>
-      <c r="AG39" s="338"/>
-      <c r="AH39" s="339"/>
+      <c r="C39" s="288"/>
+      <c r="D39" s="288"/>
+      <c r="E39" s="288"/>
+      <c r="F39" s="288"/>
+      <c r="G39" s="288"/>
+      <c r="H39" s="288"/>
+      <c r="I39" s="288"/>
+      <c r="J39" s="288"/>
+      <c r="K39" s="288"/>
+      <c r="L39" s="288"/>
+      <c r="M39" s="288"/>
+      <c r="N39" s="288"/>
+      <c r="O39" s="288"/>
+      <c r="P39" s="288"/>
+      <c r="Q39" s="288"/>
+      <c r="R39" s="288"/>
+      <c r="S39" s="288"/>
+      <c r="T39" s="288"/>
+      <c r="U39" s="288"/>
+      <c r="V39" s="288"/>
+      <c r="W39" s="288"/>
+      <c r="X39" s="288"/>
+      <c r="Y39" s="288"/>
+      <c r="Z39" s="288"/>
+      <c r="AA39" s="288"/>
+      <c r="AB39" s="288"/>
+      <c r="AC39" s="288"/>
+      <c r="AD39" s="288"/>
+      <c r="AE39" s="288"/>
+      <c r="AF39" s="288"/>
+      <c r="AG39" s="288"/>
+      <c r="AH39" s="289"/>
     </row>
     <row r="40" spans="2:34" ht="20.100000000000001" customHeight="1"/>
     <row r="41" spans="2:34" ht="20.100000000000001" customHeight="1">
@@ -40146,68 +40146,68 @@
       <c r="C44" s="160"/>
     </row>
     <row r="45" spans="2:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="Y45" s="341" t="str">
+      <c r="Y45" s="280" t="str">
         <f>'YADAO, MELENCIO'!D22</f>
         <v>YADAO, MELENCIO C.</v>
       </c>
-      <c r="Z45" s="341"/>
-      <c r="AA45" s="341"/>
-      <c r="AB45" s="341"/>
-      <c r="AC45" s="341"/>
-      <c r="AD45" s="341"/>
-      <c r="AE45" s="341"/>
-      <c r="AF45" s="341"/>
-      <c r="AG45" s="341"/>
+      <c r="Z45" s="280"/>
+      <c r="AA45" s="280"/>
+      <c r="AB45" s="280"/>
+      <c r="AC45" s="280"/>
+      <c r="AD45" s="280"/>
+      <c r="AE45" s="280"/>
+      <c r="AF45" s="280"/>
+      <c r="AG45" s="280"/>
     </row>
     <row r="46" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="Y46" s="340" t="s">
+      <c r="Y46" s="273" t="s">
         <v>165</v>
       </c>
-      <c r="Z46" s="232"/>
-      <c r="AA46" s="232"/>
-      <c r="AB46" s="232"/>
-      <c r="AC46" s="232"/>
-      <c r="AD46" s="232"/>
-      <c r="AE46" s="232"/>
-      <c r="AF46" s="232"/>
-      <c r="AG46" s="232"/>
+      <c r="Z46" s="251"/>
+      <c r="AA46" s="251"/>
+      <c r="AB46" s="251"/>
+      <c r="AC46" s="251"/>
+      <c r="AD46" s="251"/>
+      <c r="AE46" s="251"/>
+      <c r="AF46" s="251"/>
+      <c r="AG46" s="251"/>
     </row>
     <row r="47" spans="2:34" ht="20.100000000000001" customHeight="1">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="287" t="s">
         <v>166</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
-      <c r="G47" s="338"/>
-      <c r="H47" s="338"/>
-      <c r="I47" s="338"/>
-      <c r="J47" s="338"/>
-      <c r="K47" s="338"/>
-      <c r="L47" s="338"/>
-      <c r="M47" s="338"/>
-      <c r="N47" s="338"/>
-      <c r="O47" s="338"/>
-      <c r="P47" s="338"/>
-      <c r="Q47" s="338"/>
-      <c r="R47" s="338"/>
-      <c r="S47" s="338"/>
-      <c r="T47" s="338"/>
-      <c r="U47" s="338"/>
-      <c r="V47" s="338"/>
-      <c r="W47" s="338"/>
-      <c r="X47" s="338"/>
-      <c r="Y47" s="338"/>
-      <c r="Z47" s="338"/>
-      <c r="AA47" s="338"/>
-      <c r="AB47" s="338"/>
-      <c r="AC47" s="338"/>
-      <c r="AD47" s="338"/>
-      <c r="AE47" s="338"/>
-      <c r="AF47" s="338"/>
-      <c r="AG47" s="338"/>
-      <c r="AH47" s="339"/>
+      <c r="C47" s="288"/>
+      <c r="D47" s="288"/>
+      <c r="E47" s="288"/>
+      <c r="F47" s="288"/>
+      <c r="G47" s="288"/>
+      <c r="H47" s="288"/>
+      <c r="I47" s="288"/>
+      <c r="J47" s="288"/>
+      <c r="K47" s="288"/>
+      <c r="L47" s="288"/>
+      <c r="M47" s="288"/>
+      <c r="N47" s="288"/>
+      <c r="O47" s="288"/>
+      <c r="P47" s="288"/>
+      <c r="Q47" s="288"/>
+      <c r="R47" s="288"/>
+      <c r="S47" s="288"/>
+      <c r="T47" s="288"/>
+      <c r="U47" s="288"/>
+      <c r="V47" s="288"/>
+      <c r="W47" s="288"/>
+      <c r="X47" s="288"/>
+      <c r="Y47" s="288"/>
+      <c r="Z47" s="288"/>
+      <c r="AA47" s="288"/>
+      <c r="AB47" s="288"/>
+      <c r="AC47" s="288"/>
+      <c r="AD47" s="288"/>
+      <c r="AE47" s="288"/>
+      <c r="AF47" s="288"/>
+      <c r="AG47" s="288"/>
+      <c r="AH47" s="289"/>
     </row>
     <row r="48" spans="2:34" ht="20.100000000000001" customHeight="1"/>
     <row r="49" spans="2:37" ht="20.100000000000001" customHeight="1">
@@ -40258,452 +40258,452 @@
       <c r="AH52" s="161"/>
     </row>
     <row r="53" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="273" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
-      <c r="G53" s="340"/>
-      <c r="H53" s="340"/>
-      <c r="I53" s="340"/>
-      <c r="K53" s="340" t="s">
+      <c r="C53" s="273"/>
+      <c r="D53" s="273"/>
+      <c r="E53" s="273"/>
+      <c r="F53" s="273"/>
+      <c r="G53" s="273"/>
+      <c r="H53" s="273"/>
+      <c r="I53" s="273"/>
+      <c r="K53" s="273" t="s">
         <v>170</v>
       </c>
-      <c r="L53" s="340"/>
-      <c r="M53" s="340"/>
-      <c r="N53" s="340"/>
-      <c r="O53" s="340"/>
-      <c r="P53" s="340"/>
-      <c r="Q53" s="340"/>
-      <c r="T53" s="340" t="s">
+      <c r="L53" s="273"/>
+      <c r="M53" s="273"/>
+      <c r="N53" s="273"/>
+      <c r="O53" s="273"/>
+      <c r="P53" s="273"/>
+      <c r="Q53" s="273"/>
+      <c r="T53" s="273" t="s">
         <v>171</v>
       </c>
-      <c r="U53" s="340"/>
-      <c r="V53" s="340"/>
-      <c r="W53" s="340"/>
-      <c r="X53" s="340"/>
-      <c r="Y53" s="340"/>
-      <c r="Z53" s="340"/>
-      <c r="AB53" s="340" t="s">
+      <c r="U53" s="273"/>
+      <c r="V53" s="273"/>
+      <c r="W53" s="273"/>
+      <c r="X53" s="273"/>
+      <c r="Y53" s="273"/>
+      <c r="Z53" s="273"/>
+      <c r="AB53" s="273" t="s">
         <v>172</v>
       </c>
-      <c r="AC53" s="340"/>
-      <c r="AD53" s="340"/>
-      <c r="AE53" s="340"/>
-      <c r="AF53" s="340"/>
-      <c r="AG53" s="340"/>
-      <c r="AH53" s="340"/>
+      <c r="AC53" s="273"/>
+      <c r="AD53" s="273"/>
+      <c r="AE53" s="273"/>
+      <c r="AF53" s="273"/>
+      <c r="AG53" s="273"/>
+      <c r="AH53" s="273"/>
     </row>
     <row r="54" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="273" t="s">
         <v>173</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
-      <c r="G54" s="340"/>
-      <c r="H54" s="340"/>
-      <c r="I54" s="340"/>
+      <c r="C54" s="273"/>
+      <c r="D54" s="273"/>
+      <c r="E54" s="273"/>
+      <c r="F54" s="273"/>
+      <c r="G54" s="273"/>
+      <c r="H54" s="273"/>
+      <c r="I54" s="273"/>
     </row>
     <row r="55" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B55" s="337" t="s">
+      <c r="B55" s="287" t="s">
         <v>174</v>
       </c>
-      <c r="C55" s="342"/>
-      <c r="D55" s="342"/>
-      <c r="E55" s="342"/>
-      <c r="F55" s="342"/>
-      <c r="G55" s="342"/>
-      <c r="H55" s="342"/>
-      <c r="I55" s="342"/>
-      <c r="J55" s="342"/>
-      <c r="K55" s="342"/>
-      <c r="L55" s="342"/>
-      <c r="M55" s="342"/>
-      <c r="N55" s="342"/>
-      <c r="O55" s="342"/>
-      <c r="P55" s="342"/>
-      <c r="Q55" s="342"/>
-      <c r="R55" s="342"/>
-      <c r="S55" s="342"/>
-      <c r="T55" s="342"/>
-      <c r="U55" s="342"/>
-      <c r="V55" s="342"/>
-      <c r="W55" s="342"/>
-      <c r="X55" s="342"/>
-      <c r="Y55" s="342"/>
-      <c r="Z55" s="342"/>
-      <c r="AA55" s="342"/>
-      <c r="AB55" s="342"/>
-      <c r="AC55" s="342"/>
-      <c r="AD55" s="342"/>
-      <c r="AE55" s="342"/>
-      <c r="AF55" s="342"/>
-      <c r="AG55" s="342"/>
-      <c r="AH55" s="343"/>
+      <c r="C55" s="300"/>
+      <c r="D55" s="300"/>
+      <c r="E55" s="300"/>
+      <c r="F55" s="300"/>
+      <c r="G55" s="300"/>
+      <c r="H55" s="300"/>
+      <c r="I55" s="300"/>
+      <c r="J55" s="300"/>
+      <c r="K55" s="300"/>
+      <c r="L55" s="300"/>
+      <c r="M55" s="300"/>
+      <c r="N55" s="300"/>
+      <c r="O55" s="300"/>
+      <c r="P55" s="300"/>
+      <c r="Q55" s="300"/>
+      <c r="R55" s="300"/>
+      <c r="S55" s="300"/>
+      <c r="T55" s="300"/>
+      <c r="U55" s="300"/>
+      <c r="V55" s="300"/>
+      <c r="W55" s="300"/>
+      <c r="X55" s="300"/>
+      <c r="Y55" s="300"/>
+      <c r="Z55" s="300"/>
+      <c r="AA55" s="300"/>
+      <c r="AB55" s="300"/>
+      <c r="AC55" s="300"/>
+      <c r="AD55" s="300"/>
+      <c r="AE55" s="300"/>
+      <c r="AF55" s="300"/>
+      <c r="AG55" s="300"/>
+      <c r="AH55" s="301"/>
     </row>
     <row r="56" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B56" s="344" t="s">
+      <c r="B56" s="302" t="s">
         <v>175</v>
       </c>
-      <c r="C56" s="344"/>
-      <c r="D56" s="344"/>
-      <c r="E56" s="344" t="s">
+      <c r="C56" s="302"/>
+      <c r="D56" s="302"/>
+      <c r="E56" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="F56" s="344"/>
-      <c r="G56" s="344"/>
-      <c r="H56" s="344"/>
-      <c r="I56" s="344" t="s">
+      <c r="F56" s="302"/>
+      <c r="G56" s="302"/>
+      <c r="H56" s="302"/>
+      <c r="I56" s="302" t="s">
         <v>177</v>
       </c>
-      <c r="J56" s="344"/>
-      <c r="K56" s="344"/>
-      <c r="L56" s="344"/>
-      <c r="M56" s="344"/>
-      <c r="N56" s="344" t="s">
+      <c r="J56" s="302"/>
+      <c r="K56" s="302"/>
+      <c r="L56" s="302"/>
+      <c r="M56" s="302"/>
+      <c r="N56" s="302" t="s">
         <v>178</v>
       </c>
-      <c r="O56" s="344"/>
-      <c r="P56" s="344"/>
-      <c r="Q56" s="344" t="s">
+      <c r="O56" s="302"/>
+      <c r="P56" s="302"/>
+      <c r="Q56" s="302" t="s">
         <v>49</v>
       </c>
-      <c r="R56" s="344"/>
-      <c r="S56" s="344"/>
-      <c r="T56" s="344"/>
-      <c r="U56" s="344"/>
-      <c r="V56" s="344" t="s">
+      <c r="R56" s="302"/>
+      <c r="S56" s="302"/>
+      <c r="T56" s="302"/>
+      <c r="U56" s="302"/>
+      <c r="V56" s="302" t="s">
         <v>179</v>
       </c>
-      <c r="W56" s="344"/>
-      <c r="X56" s="344"/>
-      <c r="Y56" s="344" t="s">
+      <c r="W56" s="302"/>
+      <c r="X56" s="302"/>
+      <c r="Y56" s="302" t="s">
         <v>180</v>
       </c>
-      <c r="Z56" s="344"/>
-      <c r="AA56" s="344"/>
-      <c r="AB56" s="344"/>
-      <c r="AC56" s="344"/>
-      <c r="AD56" s="344" t="s">
+      <c r="Z56" s="302"/>
+      <c r="AA56" s="302"/>
+      <c r="AB56" s="302"/>
+      <c r="AC56" s="302"/>
+      <c r="AD56" s="302" t="s">
         <v>181</v>
       </c>
-      <c r="AE56" s="344"/>
-      <c r="AF56" s="344"/>
-      <c r="AG56" s="344"/>
-      <c r="AH56" s="344"/>
+      <c r="AE56" s="302"/>
+      <c r="AF56" s="302"/>
+      <c r="AG56" s="302"/>
+      <c r="AH56" s="302"/>
     </row>
     <row r="57" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B57" s="345"/>
-      <c r="C57" s="345"/>
-      <c r="D57" s="345"/>
-      <c r="E57" s="347"/>
-      <c r="F57" s="345"/>
-      <c r="G57" s="345"/>
-      <c r="H57" s="345"/>
-      <c r="I57" s="346"/>
-      <c r="J57" s="346"/>
-      <c r="K57" s="346"/>
-      <c r="L57" s="346"/>
-      <c r="M57" s="346"/>
-      <c r="N57" s="345"/>
-      <c r="O57" s="345"/>
-      <c r="P57" s="345"/>
-      <c r="Q57" s="348"/>
-      <c r="R57" s="349"/>
-      <c r="S57" s="349"/>
-      <c r="T57" s="349"/>
-      <c r="U57" s="350"/>
-      <c r="V57" s="351"/>
-      <c r="W57" s="351"/>
-      <c r="X57" s="351"/>
-      <c r="Y57" s="345"/>
-      <c r="Z57" s="345"/>
-      <c r="AA57" s="345"/>
-      <c r="AB57" s="345"/>
-      <c r="AC57" s="345"/>
-      <c r="AD57" s="346"/>
-      <c r="AE57" s="346"/>
-      <c r="AF57" s="346"/>
-      <c r="AG57" s="346"/>
-      <c r="AH57" s="346"/>
+      <c r="B57" s="293"/>
+      <c r="C57" s="293"/>
+      <c r="D57" s="293"/>
+      <c r="E57" s="295"/>
+      <c r="F57" s="293"/>
+      <c r="G57" s="293"/>
+      <c r="H57" s="293"/>
+      <c r="I57" s="294"/>
+      <c r="J57" s="294"/>
+      <c r="K57" s="294"/>
+      <c r="L57" s="294"/>
+      <c r="M57" s="294"/>
+      <c r="N57" s="293"/>
+      <c r="O57" s="293"/>
+      <c r="P57" s="293"/>
+      <c r="Q57" s="296"/>
+      <c r="R57" s="297"/>
+      <c r="S57" s="297"/>
+      <c r="T57" s="297"/>
+      <c r="U57" s="298"/>
+      <c r="V57" s="299"/>
+      <c r="W57" s="299"/>
+      <c r="X57" s="299"/>
+      <c r="Y57" s="293"/>
+      <c r="Z57" s="293"/>
+      <c r="AA57" s="293"/>
+      <c r="AB57" s="293"/>
+      <c r="AC57" s="293"/>
+      <c r="AD57" s="294"/>
+      <c r="AE57" s="294"/>
+      <c r="AF57" s="294"/>
+      <c r="AG57" s="294"/>
+      <c r="AH57" s="294"/>
       <c r="AK57" s="1"/>
     </row>
     <row r="58" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B58" s="345"/>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
-      <c r="G58" s="345"/>
-      <c r="H58" s="345"/>
-      <c r="I58" s="345"/>
-      <c r="J58" s="345"/>
-      <c r="K58" s="345"/>
-      <c r="L58" s="345"/>
-      <c r="M58" s="345"/>
-      <c r="N58" s="345"/>
-      <c r="O58" s="345"/>
-      <c r="P58" s="345"/>
-      <c r="Q58" s="345"/>
-      <c r="R58" s="345"/>
-      <c r="S58" s="345"/>
-      <c r="T58" s="345"/>
-      <c r="U58" s="345"/>
-      <c r="V58" s="345"/>
-      <c r="W58" s="345"/>
-      <c r="X58" s="345"/>
-      <c r="Y58" s="345"/>
-      <c r="Z58" s="345"/>
-      <c r="AA58" s="345"/>
-      <c r="AB58" s="345"/>
-      <c r="AC58" s="345"/>
-      <c r="AD58" s="345"/>
-      <c r="AE58" s="345"/>
-      <c r="AF58" s="345"/>
-      <c r="AG58" s="345"/>
-      <c r="AH58" s="345"/>
+      <c r="B58" s="293"/>
+      <c r="C58" s="293"/>
+      <c r="D58" s="293"/>
+      <c r="E58" s="293"/>
+      <c r="F58" s="293"/>
+      <c r="G58" s="293"/>
+      <c r="H58" s="293"/>
+      <c r="I58" s="293"/>
+      <c r="J58" s="293"/>
+      <c r="K58" s="293"/>
+      <c r="L58" s="293"/>
+      <c r="M58" s="293"/>
+      <c r="N58" s="293"/>
+      <c r="O58" s="293"/>
+      <c r="P58" s="293"/>
+      <c r="Q58" s="293"/>
+      <c r="R58" s="293"/>
+      <c r="S58" s="293"/>
+      <c r="T58" s="293"/>
+      <c r="U58" s="293"/>
+      <c r="V58" s="293"/>
+      <c r="W58" s="293"/>
+      <c r="X58" s="293"/>
+      <c r="Y58" s="293"/>
+      <c r="Z58" s="293"/>
+      <c r="AA58" s="293"/>
+      <c r="AB58" s="293"/>
+      <c r="AC58" s="293"/>
+      <c r="AD58" s="293"/>
+      <c r="AE58" s="293"/>
+      <c r="AF58" s="293"/>
+      <c r="AG58" s="293"/>
+      <c r="AH58" s="293"/>
     </row>
     <row r="59" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B59" s="345"/>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
-      <c r="G59" s="345"/>
-      <c r="H59" s="345"/>
-      <c r="I59" s="345"/>
-      <c r="J59" s="345"/>
-      <c r="K59" s="345"/>
-      <c r="L59" s="345"/>
-      <c r="M59" s="345"/>
-      <c r="N59" s="345"/>
-      <c r="O59" s="345"/>
-      <c r="P59" s="345"/>
-      <c r="Q59" s="345"/>
-      <c r="R59" s="345"/>
-      <c r="S59" s="345"/>
-      <c r="T59" s="345"/>
-      <c r="U59" s="345"/>
-      <c r="V59" s="345"/>
-      <c r="W59" s="345"/>
-      <c r="X59" s="345"/>
-      <c r="Y59" s="345"/>
-      <c r="Z59" s="345"/>
-      <c r="AA59" s="345"/>
-      <c r="AB59" s="345"/>
-      <c r="AC59" s="345"/>
-      <c r="AD59" s="345"/>
-      <c r="AE59" s="345"/>
-      <c r="AF59" s="345"/>
-      <c r="AG59" s="345"/>
-      <c r="AH59" s="345"/>
+      <c r="B59" s="293"/>
+      <c r="C59" s="293"/>
+      <c r="D59" s="293"/>
+      <c r="E59" s="293"/>
+      <c r="F59" s="293"/>
+      <c r="G59" s="293"/>
+      <c r="H59" s="293"/>
+      <c r="I59" s="293"/>
+      <c r="J59" s="293"/>
+      <c r="K59" s="293"/>
+      <c r="L59" s="293"/>
+      <c r="M59" s="293"/>
+      <c r="N59" s="293"/>
+      <c r="O59" s="293"/>
+      <c r="P59" s="293"/>
+      <c r="Q59" s="293"/>
+      <c r="R59" s="293"/>
+      <c r="S59" s="293"/>
+      <c r="T59" s="293"/>
+      <c r="U59" s="293"/>
+      <c r="V59" s="293"/>
+      <c r="W59" s="293"/>
+      <c r="X59" s="293"/>
+      <c r="Y59" s="293"/>
+      <c r="Z59" s="293"/>
+      <c r="AA59" s="293"/>
+      <c r="AB59" s="293"/>
+      <c r="AC59" s="293"/>
+      <c r="AD59" s="293"/>
+      <c r="AE59" s="293"/>
+      <c r="AF59" s="293"/>
+      <c r="AG59" s="293"/>
+      <c r="AH59" s="293"/>
     </row>
     <row r="60" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B60" s="345"/>
-      <c r="C60" s="345"/>
-      <c r="D60" s="345"/>
-      <c r="E60" s="345"/>
-      <c r="F60" s="345"/>
-      <c r="G60" s="345"/>
-      <c r="H60" s="345"/>
-      <c r="I60" s="345"/>
-      <c r="J60" s="345"/>
-      <c r="K60" s="345"/>
-      <c r="L60" s="345"/>
-      <c r="M60" s="345"/>
-      <c r="N60" s="345"/>
-      <c r="O60" s="345"/>
-      <c r="P60" s="345"/>
-      <c r="Q60" s="345"/>
-      <c r="R60" s="345"/>
-      <c r="S60" s="345"/>
-      <c r="T60" s="345"/>
-      <c r="U60" s="345"/>
-      <c r="V60" s="345"/>
-      <c r="W60" s="345"/>
-      <c r="X60" s="345"/>
-      <c r="Y60" s="345"/>
-      <c r="Z60" s="345"/>
-      <c r="AA60" s="345"/>
-      <c r="AB60" s="345"/>
-      <c r="AC60" s="345"/>
-      <c r="AD60" s="345"/>
-      <c r="AE60" s="345"/>
-      <c r="AF60" s="345"/>
-      <c r="AG60" s="345"/>
-      <c r="AH60" s="345"/>
+      <c r="B60" s="293"/>
+      <c r="C60" s="293"/>
+      <c r="D60" s="293"/>
+      <c r="E60" s="293"/>
+      <c r="F60" s="293"/>
+      <c r="G60" s="293"/>
+      <c r="H60" s="293"/>
+      <c r="I60" s="293"/>
+      <c r="J60" s="293"/>
+      <c r="K60" s="293"/>
+      <c r="L60" s="293"/>
+      <c r="M60" s="293"/>
+      <c r="N60" s="293"/>
+      <c r="O60" s="293"/>
+      <c r="P60" s="293"/>
+      <c r="Q60" s="293"/>
+      <c r="R60" s="293"/>
+      <c r="S60" s="293"/>
+      <c r="T60" s="293"/>
+      <c r="U60" s="293"/>
+      <c r="V60" s="293"/>
+      <c r="W60" s="293"/>
+      <c r="X60" s="293"/>
+      <c r="Y60" s="293"/>
+      <c r="Z60" s="293"/>
+      <c r="AA60" s="293"/>
+      <c r="AB60" s="293"/>
+      <c r="AC60" s="293"/>
+      <c r="AD60" s="293"/>
+      <c r="AE60" s="293"/>
+      <c r="AF60" s="293"/>
+      <c r="AG60" s="293"/>
+      <c r="AH60" s="293"/>
     </row>
     <row r="61" spans="2:37" ht="20.100000000000001" customHeight="1"/>
     <row r="62" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B62" s="337" t="s">
+      <c r="B62" s="287" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="338"/>
-      <c r="D62" s="338"/>
-      <c r="E62" s="338"/>
-      <c r="F62" s="338"/>
-      <c r="G62" s="338"/>
-      <c r="H62" s="338"/>
-      <c r="I62" s="338"/>
-      <c r="J62" s="338"/>
-      <c r="K62" s="338"/>
-      <c r="L62" s="338"/>
-      <c r="M62" s="338"/>
-      <c r="N62" s="338"/>
-      <c r="O62" s="338"/>
-      <c r="P62" s="338"/>
-      <c r="Q62" s="338"/>
-      <c r="R62" s="338"/>
-      <c r="S62" s="338"/>
-      <c r="T62" s="338"/>
-      <c r="U62" s="338"/>
-      <c r="V62" s="338"/>
-      <c r="W62" s="338"/>
-      <c r="X62" s="338"/>
-      <c r="Y62" s="338"/>
-      <c r="Z62" s="338"/>
-      <c r="AA62" s="338"/>
-      <c r="AB62" s="338"/>
-      <c r="AC62" s="338"/>
-      <c r="AD62" s="338"/>
-      <c r="AE62" s="338"/>
-      <c r="AF62" s="338"/>
-      <c r="AG62" s="338"/>
-      <c r="AH62" s="339"/>
+      <c r="C62" s="288"/>
+      <c r="D62" s="288"/>
+      <c r="E62" s="288"/>
+      <c r="F62" s="288"/>
+      <c r="G62" s="288"/>
+      <c r="H62" s="288"/>
+      <c r="I62" s="288"/>
+      <c r="J62" s="288"/>
+      <c r="K62" s="288"/>
+      <c r="L62" s="288"/>
+      <c r="M62" s="288"/>
+      <c r="N62" s="288"/>
+      <c r="O62" s="288"/>
+      <c r="P62" s="288"/>
+      <c r="Q62" s="288"/>
+      <c r="R62" s="288"/>
+      <c r="S62" s="288"/>
+      <c r="T62" s="288"/>
+      <c r="U62" s="288"/>
+      <c r="V62" s="288"/>
+      <c r="W62" s="288"/>
+      <c r="X62" s="288"/>
+      <c r="Y62" s="288"/>
+      <c r="Z62" s="288"/>
+      <c r="AA62" s="288"/>
+      <c r="AB62" s="288"/>
+      <c r="AC62" s="288"/>
+      <c r="AD62" s="288"/>
+      <c r="AE62" s="288"/>
+      <c r="AF62" s="288"/>
+      <c r="AG62" s="288"/>
+      <c r="AH62" s="289"/>
     </row>
     <row r="63" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B63" s="352" t="s">
+      <c r="B63" s="290" t="s">
         <v>183</v>
       </c>
-      <c r="C63" s="353"/>
-      <c r="D63" s="353"/>
-      <c r="E63" s="353"/>
-      <c r="F63" s="354"/>
-      <c r="G63" s="352" t="s">
+      <c r="C63" s="291"/>
+      <c r="D63" s="291"/>
+      <c r="E63" s="291"/>
+      <c r="F63" s="292"/>
+      <c r="G63" s="290" t="s">
         <v>184</v>
       </c>
-      <c r="H63" s="353"/>
-      <c r="I63" s="353"/>
-      <c r="J63" s="354"/>
-      <c r="K63" s="352" t="s">
+      <c r="H63" s="291"/>
+      <c r="I63" s="291"/>
+      <c r="J63" s="292"/>
+      <c r="K63" s="290" t="s">
         <v>50</v>
       </c>
-      <c r="L63" s="353"/>
-      <c r="M63" s="353"/>
-      <c r="N63" s="354"/>
-      <c r="O63" s="352" t="s">
+      <c r="L63" s="291"/>
+      <c r="M63" s="291"/>
+      <c r="N63" s="292"/>
+      <c r="O63" s="290" t="s">
         <v>185</v>
       </c>
-      <c r="P63" s="353"/>
-      <c r="Q63" s="353"/>
-      <c r="R63" s="353"/>
-      <c r="S63" s="353"/>
-      <c r="T63" s="353"/>
-      <c r="U63" s="354"/>
-      <c r="V63" s="352" t="s">
+      <c r="P63" s="291"/>
+      <c r="Q63" s="291"/>
+      <c r="R63" s="291"/>
+      <c r="S63" s="291"/>
+      <c r="T63" s="291"/>
+      <c r="U63" s="292"/>
+      <c r="V63" s="290" t="s">
         <v>186</v>
       </c>
-      <c r="W63" s="353"/>
-      <c r="X63" s="353"/>
-      <c r="Y63" s="353"/>
-      <c r="Z63" s="354"/>
-      <c r="AA63" s="352" t="s">
+      <c r="W63" s="291"/>
+      <c r="X63" s="291"/>
+      <c r="Y63" s="291"/>
+      <c r="Z63" s="292"/>
+      <c r="AA63" s="290" t="s">
         <v>187</v>
       </c>
-      <c r="AB63" s="353"/>
-      <c r="AC63" s="353"/>
-      <c r="AD63" s="353"/>
-      <c r="AE63" s="353"/>
-      <c r="AF63" s="353"/>
-      <c r="AG63" s="353"/>
-      <c r="AH63" s="354"/>
+      <c r="AB63" s="291"/>
+      <c r="AC63" s="291"/>
+      <c r="AD63" s="291"/>
+      <c r="AE63" s="291"/>
+      <c r="AF63" s="291"/>
+      <c r="AG63" s="291"/>
+      <c r="AH63" s="292"/>
     </row>
     <row r="64" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B64" s="362">
+      <c r="B64" s="281">
         <f>'DATA ENTRY'!D13</f>
-        <v>42486.859499999999</v>
-      </c>
-      <c r="C64" s="283"/>
-      <c r="D64" s="283"/>
-      <c r="E64" s="283"/>
-      <c r="F64" s="284"/>
-      <c r="G64" s="362">
+        <v>20181.172399999999</v>
+      </c>
+      <c r="C64" s="282"/>
+      <c r="D64" s="282"/>
+      <c r="E64" s="282"/>
+      <c r="F64" s="283"/>
+      <c r="G64" s="281">
         <f>'DATA ENTRY'!D16</f>
-        <v>2000.0040005269973</v>
-      </c>
-      <c r="H64" s="283"/>
-      <c r="I64" s="283"/>
-      <c r="J64" s="284"/>
-      <c r="K64" s="363">
+        <v>949.99785840431502</v>
+      </c>
+      <c r="H64" s="282"/>
+      <c r="I64" s="282"/>
+      <c r="J64" s="283"/>
+      <c r="K64" s="284">
         <v>24</v>
       </c>
-      <c r="L64" s="364"/>
-      <c r="M64" s="364"/>
-      <c r="N64" s="365"/>
-      <c r="O64" s="362"/>
-      <c r="P64" s="283"/>
-      <c r="Q64" s="283"/>
-      <c r="R64" s="283"/>
-      <c r="S64" s="283"/>
-      <c r="T64" s="283"/>
-      <c r="U64" s="284"/>
-      <c r="V64" s="363"/>
-      <c r="W64" s="364"/>
-      <c r="X64" s="364"/>
-      <c r="Y64" s="364"/>
-      <c r="Z64" s="365"/>
-      <c r="AA64" s="362">
+      <c r="L64" s="285"/>
+      <c r="M64" s="285"/>
+      <c r="N64" s="286"/>
+      <c r="O64" s="281"/>
+      <c r="P64" s="282"/>
+      <c r="Q64" s="282"/>
+      <c r="R64" s="282"/>
+      <c r="S64" s="282"/>
+      <c r="T64" s="282"/>
+      <c r="U64" s="283"/>
+      <c r="V64" s="284"/>
+      <c r="W64" s="285"/>
+      <c r="X64" s="285"/>
+      <c r="Y64" s="285"/>
+      <c r="Z64" s="286"/>
+      <c r="AA64" s="281">
         <f>'YADAO, MELENCIO'!C3</f>
-        <v>48000.096012647933</v>
-      </c>
-      <c r="AB64" s="283"/>
-      <c r="AC64" s="283"/>
-      <c r="AD64" s="283"/>
-      <c r="AE64" s="283"/>
-      <c r="AF64" s="283"/>
-      <c r="AG64" s="283"/>
-      <c r="AH64" s="284"/>
+        <v>22799.94860170356</v>
+      </c>
+      <c r="AB64" s="282"/>
+      <c r="AC64" s="282"/>
+      <c r="AD64" s="282"/>
+      <c r="AE64" s="282"/>
+      <c r="AF64" s="282"/>
+      <c r="AG64" s="282"/>
+      <c r="AH64" s="283"/>
     </row>
     <row r="65" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B65" s="355" t="s">
+      <c r="B65" s="272" t="s">
         <v>188</v>
       </c>
-      <c r="C65" s="355"/>
-      <c r="D65" s="355"/>
-      <c r="E65" s="355"/>
-      <c r="F65" s="355"/>
-      <c r="G65" s="355"/>
-      <c r="H65" s="355"/>
-      <c r="I65" s="355"/>
-      <c r="J65" s="355"/>
-      <c r="K65" s="355"/>
-      <c r="L65" s="355"/>
-      <c r="M65" s="355"/>
-      <c r="N65" s="355"/>
-      <c r="O65" s="355"/>
-      <c r="P65" s="355"/>
-      <c r="Q65" s="355"/>
-      <c r="R65" s="355"/>
-      <c r="S65" s="355"/>
-      <c r="T65" s="355"/>
-      <c r="U65" s="355"/>
-      <c r="V65" s="355"/>
-      <c r="W65" s="355"/>
-      <c r="X65" s="355"/>
-      <c r="Y65" s="355"/>
-      <c r="Z65" s="355"/>
-      <c r="AA65" s="355"/>
-      <c r="AB65" s="355"/>
-      <c r="AC65" s="355"/>
-      <c r="AD65" s="355"/>
-      <c r="AE65" s="355"/>
-      <c r="AF65" s="355"/>
-      <c r="AG65" s="355"/>
-      <c r="AH65" s="355"/>
+      <c r="C65" s="272"/>
+      <c r="D65" s="272"/>
+      <c r="E65" s="272"/>
+      <c r="F65" s="272"/>
+      <c r="G65" s="272"/>
+      <c r="H65" s="272"/>
+      <c r="I65" s="272"/>
+      <c r="J65" s="272"/>
+      <c r="K65" s="272"/>
+      <c r="L65" s="272"/>
+      <c r="M65" s="272"/>
+      <c r="N65" s="272"/>
+      <c r="O65" s="272"/>
+      <c r="P65" s="272"/>
+      <c r="Q65" s="272"/>
+      <c r="R65" s="272"/>
+      <c r="S65" s="272"/>
+      <c r="T65" s="272"/>
+      <c r="U65" s="272"/>
+      <c r="V65" s="272"/>
+      <c r="W65" s="272"/>
+      <c r="X65" s="272"/>
+      <c r="Y65" s="272"/>
+      <c r="Z65" s="272"/>
+      <c r="AA65" s="272"/>
+      <c r="AB65" s="272"/>
+      <c r="AC65" s="272"/>
+      <c r="AD65" s="272"/>
+      <c r="AE65" s="272"/>
+      <c r="AF65" s="272"/>
+      <c r="AG65" s="272"/>
+      <c r="AH65" s="272"/>
     </row>
     <row r="66" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="B66" s="130"/>
@@ -40778,84 +40778,84 @@
       <c r="AH67" s="130"/>
     </row>
     <row r="68" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="340" t="s">
+      <c r="A68" s="273" t="s">
         <v>190</v>
       </c>
-      <c r="B68" s="340"/>
-      <c r="C68" s="340"/>
-      <c r="D68" s="340"/>
-      <c r="E68" s="340"/>
-      <c r="F68" s="340"/>
-      <c r="G68" s="340"/>
-      <c r="H68" s="340"/>
-      <c r="I68" s="340"/>
-      <c r="J68" s="340"/>
-      <c r="K68" s="340"/>
-      <c r="L68" s="340"/>
-      <c r="M68" s="340"/>
-      <c r="N68" s="340"/>
-      <c r="O68" s="340"/>
-      <c r="P68" s="340"/>
-      <c r="Q68" s="340"/>
-      <c r="R68" s="340"/>
-      <c r="S68" s="340"/>
-      <c r="T68" s="340"/>
-      <c r="U68" s="340"/>
-      <c r="V68" s="340"/>
-      <c r="W68" s="340"/>
-      <c r="X68" s="340"/>
-      <c r="Y68" s="340"/>
-      <c r="Z68" s="340"/>
-      <c r="AA68" s="340"/>
-      <c r="AB68" s="340"/>
-      <c r="AC68" s="340"/>
-      <c r="AD68" s="340"/>
-      <c r="AE68" s="340"/>
-      <c r="AF68" s="340"/>
-      <c r="AG68" s="340"/>
-      <c r="AH68" s="340"/>
-      <c r="AI68" s="340"/>
+      <c r="B68" s="273"/>
+      <c r="C68" s="273"/>
+      <c r="D68" s="273"/>
+      <c r="E68" s="273"/>
+      <c r="F68" s="273"/>
+      <c r="G68" s="273"/>
+      <c r="H68" s="273"/>
+      <c r="I68" s="273"/>
+      <c r="J68" s="273"/>
+      <c r="K68" s="273"/>
+      <c r="L68" s="273"/>
+      <c r="M68" s="273"/>
+      <c r="N68" s="273"/>
+      <c r="O68" s="273"/>
+      <c r="P68" s="273"/>
+      <c r="Q68" s="273"/>
+      <c r="R68" s="273"/>
+      <c r="S68" s="273"/>
+      <c r="T68" s="273"/>
+      <c r="U68" s="273"/>
+      <c r="V68" s="273"/>
+      <c r="W68" s="273"/>
+      <c r="X68" s="273"/>
+      <c r="Y68" s="273"/>
+      <c r="Z68" s="273"/>
+      <c r="AA68" s="273"/>
+      <c r="AB68" s="273"/>
+      <c r="AC68" s="273"/>
+      <c r="AD68" s="273"/>
+      <c r="AE68" s="273"/>
+      <c r="AF68" s="273"/>
+      <c r="AG68" s="273"/>
+      <c r="AH68" s="273"/>
+      <c r="AI68" s="273"/>
     </row>
     <row r="69" spans="1:35" ht="20.100000000000001" customHeight="1"/>
     <row r="70" spans="1:35" ht="20.100000000000001" customHeight="1"/>
     <row r="71" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B71" s="356" t="s">
+      <c r="B71" s="274" t="s">
         <v>191</v>
       </c>
-      <c r="C71" s="355"/>
-      <c r="D71" s="355"/>
-      <c r="E71" s="355"/>
-      <c r="F71" s="355"/>
-      <c r="G71" s="355"/>
-      <c r="H71" s="355"/>
-      <c r="I71" s="355"/>
-      <c r="J71" s="355"/>
-      <c r="K71" s="355"/>
-      <c r="L71" s="355"/>
-      <c r="M71" s="355"/>
-      <c r="N71" s="355"/>
-      <c r="O71" s="355"/>
-      <c r="P71" s="355"/>
-      <c r="Q71" s="355"/>
-      <c r="R71" s="357"/>
-      <c r="S71" s="356" t="s">
+      <c r="C71" s="272"/>
+      <c r="D71" s="272"/>
+      <c r="E71" s="272"/>
+      <c r="F71" s="272"/>
+      <c r="G71" s="272"/>
+      <c r="H71" s="272"/>
+      <c r="I71" s="272"/>
+      <c r="J71" s="272"/>
+      <c r="K71" s="272"/>
+      <c r="L71" s="272"/>
+      <c r="M71" s="272"/>
+      <c r="N71" s="272"/>
+      <c r="O71" s="272"/>
+      <c r="P71" s="272"/>
+      <c r="Q71" s="272"/>
+      <c r="R71" s="275"/>
+      <c r="S71" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="T71" s="355"/>
-      <c r="U71" s="355"/>
-      <c r="V71" s="355"/>
-      <c r="W71" s="355"/>
-      <c r="X71" s="355"/>
-      <c r="Y71" s="355"/>
-      <c r="Z71" s="355"/>
-      <c r="AA71" s="355"/>
-      <c r="AB71" s="355"/>
-      <c r="AC71" s="355"/>
-      <c r="AD71" s="355"/>
-      <c r="AE71" s="355"/>
-      <c r="AF71" s="355"/>
-      <c r="AG71" s="355"/>
-      <c r="AH71" s="357"/>
+      <c r="T71" s="272"/>
+      <c r="U71" s="272"/>
+      <c r="V71" s="272"/>
+      <c r="W71" s="272"/>
+      <c r="X71" s="272"/>
+      <c r="Y71" s="272"/>
+      <c r="Z71" s="272"/>
+      <c r="AA71" s="272"/>
+      <c r="AB71" s="272"/>
+      <c r="AC71" s="272"/>
+      <c r="AD71" s="272"/>
+      <c r="AE71" s="272"/>
+      <c r="AF71" s="272"/>
+      <c r="AG71" s="272"/>
+      <c r="AH71" s="275"/>
     </row>
     <row r="72" spans="1:35" ht="20.100000000000001" customHeight="1">
       <c r="B72" s="165"/>
@@ -40898,14 +40898,14 @@
       <c r="D73" s="123"/>
       <c r="E73" s="168"/>
       <c r="F73" s="169"/>
-      <c r="G73" s="360" t="s">
+      <c r="G73" s="278" t="s">
         <v>189</v>
       </c>
-      <c r="H73" s="361"/>
-      <c r="I73" s="361"/>
-      <c r="J73" s="361"/>
-      <c r="K73" s="361"/>
-      <c r="L73" s="361"/>
+      <c r="H73" s="279"/>
+      <c r="I73" s="279"/>
+      <c r="J73" s="279"/>
+      <c r="K73" s="279"/>
+      <c r="L73" s="279"/>
       <c r="M73" s="169"/>
       <c r="N73" s="169"/>
       <c r="O73" s="168"/>
@@ -40915,73 +40915,158 @@
       <c r="S73" s="167"/>
       <c r="W73" s="161"/>
       <c r="X73" s="161"/>
-      <c r="Y73" s="341" t="s">
+      <c r="Y73" s="280" t="s">
         <v>236</v>
       </c>
-      <c r="Z73" s="341"/>
-      <c r="AA73" s="341"/>
-      <c r="AB73" s="341"/>
-      <c r="AC73" s="341"/>
+      <c r="Z73" s="280"/>
+      <c r="AA73" s="280"/>
+      <c r="AB73" s="280"/>
+      <c r="AC73" s="280"/>
       <c r="AD73" s="161"/>
       <c r="AH73" s="171"/>
     </row>
     <row r="74" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="B74" s="358" t="s">
+      <c r="B74" s="276" t="s">
         <v>190</v>
       </c>
-      <c r="C74" s="234"/>
-      <c r="D74" s="234"/>
-      <c r="E74" s="234"/>
-      <c r="F74" s="234"/>
-      <c r="G74" s="234"/>
-      <c r="H74" s="234"/>
-      <c r="I74" s="234"/>
-      <c r="J74" s="234"/>
-      <c r="K74" s="234"/>
-      <c r="L74" s="234"/>
-      <c r="M74" s="234"/>
-      <c r="N74" s="234"/>
-      <c r="O74" s="234"/>
-      <c r="P74" s="234"/>
-      <c r="Q74" s="234"/>
-      <c r="R74" s="359"/>
-      <c r="S74" s="358" t="s">
+      <c r="C74" s="253"/>
+      <c r="D74" s="253"/>
+      <c r="E74" s="253"/>
+      <c r="F74" s="253"/>
+      <c r="G74" s="253"/>
+      <c r="H74" s="253"/>
+      <c r="I74" s="253"/>
+      <c r="J74" s="253"/>
+      <c r="K74" s="253"/>
+      <c r="L74" s="253"/>
+      <c r="M74" s="253"/>
+      <c r="N74" s="253"/>
+      <c r="O74" s="253"/>
+      <c r="P74" s="253"/>
+      <c r="Q74" s="253"/>
+      <c r="R74" s="277"/>
+      <c r="S74" s="276" t="s">
         <v>190</v>
       </c>
-      <c r="T74" s="234"/>
-      <c r="U74" s="234"/>
-      <c r="V74" s="234"/>
-      <c r="W74" s="234"/>
-      <c r="X74" s="234"/>
-      <c r="Y74" s="234"/>
-      <c r="Z74" s="234"/>
-      <c r="AA74" s="234"/>
-      <c r="AB74" s="234"/>
-      <c r="AC74" s="234"/>
-      <c r="AD74" s="234"/>
-      <c r="AE74" s="234"/>
-      <c r="AF74" s="234"/>
-      <c r="AG74" s="234"/>
-      <c r="AH74" s="359"/>
+      <c r="T74" s="253"/>
+      <c r="U74" s="253"/>
+      <c r="V74" s="253"/>
+      <c r="W74" s="253"/>
+      <c r="X74" s="253"/>
+      <c r="Y74" s="253"/>
+      <c r="Z74" s="253"/>
+      <c r="AA74" s="253"/>
+      <c r="AB74" s="253"/>
+      <c r="AC74" s="253"/>
+      <c r="AD74" s="253"/>
+      <c r="AE74" s="253"/>
+      <c r="AF74" s="253"/>
+      <c r="AG74" s="253"/>
+      <c r="AH74" s="277"/>
     </row>
     <row r="75" spans="1:35" ht="20.100000000000001" customHeight="1"/>
     <row r="76" spans="1:35" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="B65:AH65"/>
-    <mergeCell ref="A68:AI68"/>
-    <mergeCell ref="B71:R71"/>
-    <mergeCell ref="S71:AH71"/>
-    <mergeCell ref="B74:R74"/>
-    <mergeCell ref="S74:AH74"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="Y73:AC73"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="K64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="V64:Z64"/>
-    <mergeCell ref="AA64:AH64"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B7:AH7"/>
+    <mergeCell ref="B8:AH8"/>
+    <mergeCell ref="B10:AH10"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Y15:AH15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="AA16:AE16"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:P13"/>
+    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="X13:AH13"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Y14:AH14"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="F20:Q21"/>
+    <mergeCell ref="X20:AH21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="Z22:AH22"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="L19:P19"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="D23:I24"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="W24:Y24"/>
+    <mergeCell ref="B25:AH25"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="M28:R28"/>
+    <mergeCell ref="S28:Z28"/>
+    <mergeCell ref="AA28:AH28"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:T33"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="AB32:AH32"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="H29:L29"/>
+    <mergeCell ref="M29:R29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:AA35"/>
+    <mergeCell ref="AB35:AH35"/>
+    <mergeCell ref="X36:AH36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="K37:W37"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="I33:P33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="AB33:AH33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I34:X34"/>
+    <mergeCell ref="F38:AH38"/>
+    <mergeCell ref="B39:AH39"/>
+    <mergeCell ref="Y46:AG46"/>
+    <mergeCell ref="B47:AH47"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="K53:Q53"/>
+    <mergeCell ref="T53:Z53"/>
+    <mergeCell ref="AB53:AH53"/>
+    <mergeCell ref="Y45:AG45"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B55:AH55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:M56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="Q56:U56"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="Y56:AC56"/>
+    <mergeCell ref="AD56:AH56"/>
+    <mergeCell ref="Y57:AC57"/>
+    <mergeCell ref="AD57:AH57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:P58"/>
+    <mergeCell ref="Q58:U58"/>
+    <mergeCell ref="V58:X58"/>
+    <mergeCell ref="Y58:AC58"/>
+    <mergeCell ref="AD58:AH58"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:M57"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="Q57:U57"/>
+    <mergeCell ref="V57:X57"/>
     <mergeCell ref="B62:AH62"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="G63:J63"/>
@@ -41005,105 +41090,20 @@
     <mergeCell ref="N59:P59"/>
     <mergeCell ref="Q59:U59"/>
     <mergeCell ref="V59:X59"/>
-    <mergeCell ref="Y57:AC57"/>
-    <mergeCell ref="AD57:AH57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:P58"/>
-    <mergeCell ref="Q58:U58"/>
-    <mergeCell ref="V58:X58"/>
-    <mergeCell ref="Y58:AC58"/>
-    <mergeCell ref="AD58:AH58"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:M57"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="Q57:U57"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B55:AH55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:M56"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="Q56:U56"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Y56:AC56"/>
-    <mergeCell ref="AD56:AH56"/>
-    <mergeCell ref="F38:AH38"/>
-    <mergeCell ref="B39:AH39"/>
-    <mergeCell ref="Y46:AG46"/>
-    <mergeCell ref="B47:AH47"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="K53:Q53"/>
-    <mergeCell ref="T53:Z53"/>
-    <mergeCell ref="AB53:AH53"/>
-    <mergeCell ref="Y45:AG45"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:AA35"/>
-    <mergeCell ref="AB35:AH35"/>
-    <mergeCell ref="X36:AH36"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="K37:W37"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="I33:P33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="AB33:AH33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I34:X34"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:T33"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="AB32:AH32"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="H29:L29"/>
-    <mergeCell ref="M29:R29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="D23:I24"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="W24:Y24"/>
-    <mergeCell ref="B25:AH25"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="H28:L28"/>
-    <mergeCell ref="M28:R28"/>
-    <mergeCell ref="S28:Z28"/>
-    <mergeCell ref="AA28:AH28"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="F20:Q21"/>
-    <mergeCell ref="X20:AH21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="N22:U22"/>
-    <mergeCell ref="Z22:AH22"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="L19:P19"/>
-    <mergeCell ref="B6:AH6"/>
-    <mergeCell ref="B7:AH7"/>
-    <mergeCell ref="B8:AH8"/>
-    <mergeCell ref="B10:AH10"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Y15:AH15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="AA16:AE16"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:P13"/>
-    <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="X13:AH13"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Y14:AH14"/>
+    <mergeCell ref="B65:AH65"/>
+    <mergeCell ref="A68:AI68"/>
+    <mergeCell ref="B71:R71"/>
+    <mergeCell ref="S71:AH71"/>
+    <mergeCell ref="B74:R74"/>
+    <mergeCell ref="S74:AH74"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="Y73:AC73"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="K64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="V64:Z64"/>
+    <mergeCell ref="AA64:AH64"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -41140,123 +41140,123 @@
       </c>
     </row>
     <row r="2" spans="2:75" ht="30" customHeight="1">
-      <c r="B2" s="273" t="s">
+      <c r="B2" s="345" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="274"/>
-      <c r="D2" s="274"/>
-      <c r="E2" s="274"/>
-      <c r="F2" s="274"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="274"/>
-      <c r="I2" s="274"/>
-      <c r="J2" s="274"/>
-      <c r="K2" s="274"/>
-      <c r="L2" s="274"/>
-      <c r="M2" s="274"/>
-      <c r="N2" s="274"/>
-      <c r="O2" s="274"/>
-      <c r="P2" s="307" t="str">
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
+      <c r="I2" s="346"/>
+      <c r="J2" s="346"/>
+      <c r="K2" s="346"/>
+      <c r="L2" s="346"/>
+      <c r="M2" s="346"/>
+      <c r="N2" s="346"/>
+      <c r="O2" s="346"/>
+      <c r="P2" s="323" t="str">
         <f>'YADAO, MELENCIO'!H22</f>
         <v>LRV-060</v>
       </c>
-      <c r="Q2" s="366"/>
-      <c r="R2" s="366"/>
-      <c r="S2" s="366"/>
-      <c r="T2" s="308"/>
+      <c r="Q2" s="391"/>
+      <c r="R2" s="391"/>
+      <c r="S2" s="391"/>
+      <c r="T2" s="324"/>
     </row>
     <row r="3" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="367" t="s">
+      <c r="C3" s="378" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
-      <c r="H3" s="367"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="367"/>
-      <c r="K3" s="367"/>
-      <c r="L3" s="367"/>
-      <c r="M3" s="367"/>
-      <c r="N3" s="367"/>
-      <c r="O3" s="367"/>
-      <c r="P3" s="367"/>
-      <c r="Q3" s="367"/>
-      <c r="R3" s="367"/>
-      <c r="S3" s="367"/>
-      <c r="T3" s="367"/>
-      <c r="U3" s="367"/>
-      <c r="V3" s="367"/>
-      <c r="W3" s="367"/>
-      <c r="X3" s="367"/>
-      <c r="Y3" s="367"/>
-      <c r="Z3" s="367"/>
-      <c r="AA3" s="367"/>
-      <c r="AB3" s="367"/>
-      <c r="AC3" s="367"/>
-      <c r="AD3" s="367"/>
-      <c r="AE3" s="367"/>
-      <c r="AF3" s="367"/>
-      <c r="AG3" s="367"/>
-      <c r="AH3" s="367"/>
-      <c r="AI3" s="367"/>
-      <c r="AJ3" s="367"/>
-      <c r="AK3" s="367"/>
-      <c r="AL3" s="367"/>
+      <c r="D3" s="378"/>
+      <c r="E3" s="378"/>
+      <c r="F3" s="378"/>
+      <c r="G3" s="378"/>
+      <c r="H3" s="378"/>
+      <c r="I3" s="378"/>
+      <c r="J3" s="378"/>
+      <c r="K3" s="378"/>
+      <c r="L3" s="378"/>
+      <c r="M3" s="378"/>
+      <c r="N3" s="378"/>
+      <c r="O3" s="378"/>
+      <c r="P3" s="378"/>
+      <c r="Q3" s="378"/>
+      <c r="R3" s="378"/>
+      <c r="S3" s="378"/>
+      <c r="T3" s="378"/>
+      <c r="U3" s="378"/>
+      <c r="V3" s="378"/>
+      <c r="W3" s="378"/>
+      <c r="X3" s="378"/>
+      <c r="Y3" s="378"/>
+      <c r="Z3" s="378"/>
+      <c r="AA3" s="378"/>
+      <c r="AB3" s="378"/>
+      <c r="AC3" s="378"/>
+      <c r="AD3" s="378"/>
+      <c r="AE3" s="378"/>
+      <c r="AF3" s="378"/>
+      <c r="AG3" s="378"/>
+      <c r="AH3" s="378"/>
+      <c r="AI3" s="378"/>
+      <c r="AJ3" s="378"/>
+      <c r="AK3" s="378"/>
+      <c r="AL3" s="378"/>
     </row>
     <row r="4" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B4" s="369">
+      <c r="B4" s="367">
         <f>'YADAO, MELENCIO'!C3</f>
-        <v>48000.096012647933</v>
-      </c>
-      <c r="C4" s="369"/>
-      <c r="D4" s="369"/>
+        <v>22799.94860170356</v>
+      </c>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
       <c r="E4" s="198" t="s">
         <v>232</v>
       </c>
       <c r="F4" s="228">
         <v>24</v>
       </c>
-      <c r="G4" s="367" t="s">
+      <c r="G4" s="378" t="s">
         <v>233</v>
       </c>
-      <c r="H4" s="367"/>
-      <c r="I4" s="367"/>
-      <c r="J4" s="367"/>
-      <c r="K4" s="367"/>
-      <c r="L4" s="367"/>
-      <c r="M4" s="367"/>
-      <c r="N4" s="367"/>
-      <c r="O4" s="367"/>
-      <c r="P4" s="367"/>
-      <c r="Q4" s="367"/>
-      <c r="R4" s="367"/>
-      <c r="S4" s="367"/>
-      <c r="T4" s="369">
+      <c r="H4" s="378"/>
+      <c r="I4" s="378"/>
+      <c r="J4" s="378"/>
+      <c r="K4" s="378"/>
+      <c r="L4" s="378"/>
+      <c r="M4" s="378"/>
+      <c r="N4" s="378"/>
+      <c r="O4" s="378"/>
+      <c r="P4" s="378"/>
+      <c r="Q4" s="378"/>
+      <c r="R4" s="378"/>
+      <c r="S4" s="378"/>
+      <c r="T4" s="367">
         <f>'YADAO, MELENCIO'!C1</f>
-        <v>2000.0040005269973</v>
-      </c>
-      <c r="U4" s="369"/>
-      <c r="V4" s="367" t="s">
+        <v>949.99785840431502</v>
+      </c>
+      <c r="U4" s="367"/>
+      <c r="V4" s="378" t="s">
         <v>241</v>
       </c>
-      <c r="W4" s="367"/>
-      <c r="X4" s="367"/>
-      <c r="Y4" s="367"/>
-      <c r="Z4" s="367"/>
-      <c r="AA4" s="367"/>
-      <c r="AB4" s="367"/>
-      <c r="AC4" s="367"/>
-      <c r="AD4" s="367"/>
-      <c r="AE4" s="367"/>
-      <c r="AF4" s="367"/>
-      <c r="AG4" s="367"/>
-      <c r="AH4" s="367"/>
-      <c r="AI4" s="367"/>
-      <c r="AJ4" s="367"/>
-      <c r="AK4" s="367"/>
-      <c r="AL4" s="367"/>
+      <c r="W4" s="378"/>
+      <c r="X4" s="378"/>
+      <c r="Y4" s="378"/>
+      <c r="Z4" s="378"/>
+      <c r="AA4" s="378"/>
+      <c r="AB4" s="378"/>
+      <c r="AC4" s="378"/>
+      <c r="AD4" s="378"/>
+      <c r="AE4" s="378"/>
+      <c r="AF4" s="378"/>
+      <c r="AG4" s="378"/>
+      <c r="AH4" s="378"/>
+      <c r="AI4" s="378"/>
+      <c r="AJ4" s="378"/>
+      <c r="AK4" s="378"/>
+      <c r="AL4" s="378"/>
       <c r="AN4" s="164"/>
       <c r="AO4" s="172"/>
       <c r="AP4" s="172"/>
@@ -41295,48 +41295,48 @@
       <c r="BW4" s="174"/>
     </row>
     <row r="5" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B5" s="368">
+      <c r="B5" s="392">
         <f>'YADAO, MELENCIO'!B28</f>
         <v>46125</v>
       </c>
-      <c r="C5" s="368"/>
-      <c r="D5" s="368"/>
-      <c r="E5" s="368"/>
-      <c r="F5" s="367" t="s">
+      <c r="C5" s="392"/>
+      <c r="D5" s="392"/>
+      <c r="E5" s="392"/>
+      <c r="F5" s="378" t="s">
         <v>234</v>
       </c>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="367"/>
-      <c r="L5" s="367"/>
-      <c r="M5" s="367"/>
-      <c r="N5" s="367"/>
-      <c r="O5" s="367"/>
-      <c r="P5" s="367"/>
-      <c r="Q5" s="367"/>
-      <c r="R5" s="367"/>
-      <c r="S5" s="367"/>
-      <c r="T5" s="367"/>
-      <c r="U5" s="367"/>
-      <c r="V5" s="367"/>
-      <c r="W5" s="367"/>
-      <c r="X5" s="367"/>
-      <c r="Y5" s="367"/>
-      <c r="Z5" s="367"/>
-      <c r="AA5" s="367"/>
-      <c r="AB5" s="367"/>
-      <c r="AC5" s="367"/>
-      <c r="AD5" s="367"/>
-      <c r="AE5" s="367"/>
-      <c r="AF5" s="367"/>
-      <c r="AG5" s="367"/>
-      <c r="AH5" s="367"/>
-      <c r="AI5" s="367"/>
-      <c r="AJ5" s="367"/>
-      <c r="AK5" s="367"/>
-      <c r="AL5" s="367"/>
+      <c r="G5" s="378"/>
+      <c r="H5" s="378"/>
+      <c r="I5" s="378"/>
+      <c r="J5" s="378"/>
+      <c r="K5" s="378"/>
+      <c r="L5" s="378"/>
+      <c r="M5" s="378"/>
+      <c r="N5" s="378"/>
+      <c r="O5" s="378"/>
+      <c r="P5" s="378"/>
+      <c r="Q5" s="378"/>
+      <c r="R5" s="378"/>
+      <c r="S5" s="378"/>
+      <c r="T5" s="378"/>
+      <c r="U5" s="378"/>
+      <c r="V5" s="378"/>
+      <c r="W5" s="378"/>
+      <c r="X5" s="378"/>
+      <c r="Y5" s="378"/>
+      <c r="Z5" s="378"/>
+      <c r="AA5" s="378"/>
+      <c r="AB5" s="378"/>
+      <c r="AC5" s="378"/>
+      <c r="AD5" s="378"/>
+      <c r="AE5" s="378"/>
+      <c r="AF5" s="378"/>
+      <c r="AG5" s="378"/>
+      <c r="AH5" s="378"/>
+      <c r="AI5" s="378"/>
+      <c r="AJ5" s="378"/>
+      <c r="AK5" s="378"/>
+      <c r="AL5" s="378"/>
       <c r="AN5" s="175"/>
       <c r="AO5" s="176"/>
       <c r="AP5" s="176"/>
@@ -41375,45 +41375,45 @@
       <c r="BW5" s="179"/>
     </row>
     <row r="6" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="378" t="s">
         <v>235</v>
       </c>
-      <c r="C6" s="367"/>
-      <c r="D6" s="367"/>
-      <c r="E6" s="367"/>
-      <c r="F6" s="367"/>
-      <c r="G6" s="367"/>
-      <c r="H6" s="367"/>
-      <c r="I6" s="367"/>
-      <c r="J6" s="367"/>
-      <c r="K6" s="367"/>
-      <c r="L6" s="367"/>
-      <c r="M6" s="367"/>
-      <c r="N6" s="367"/>
-      <c r="O6" s="367"/>
-      <c r="P6" s="367"/>
-      <c r="Q6" s="367"/>
-      <c r="R6" s="367"/>
-      <c r="S6" s="367"/>
-      <c r="T6" s="367"/>
-      <c r="U6" s="367"/>
-      <c r="V6" s="367"/>
-      <c r="W6" s="367"/>
-      <c r="X6" s="367"/>
-      <c r="Y6" s="367"/>
-      <c r="Z6" s="367"/>
-      <c r="AA6" s="367"/>
-      <c r="AB6" s="367"/>
-      <c r="AC6" s="367"/>
-      <c r="AD6" s="367"/>
-      <c r="AE6" s="367"/>
-      <c r="AF6" s="367"/>
-      <c r="AG6" s="367"/>
-      <c r="AH6" s="367"/>
-      <c r="AI6" s="367"/>
-      <c r="AJ6" s="367"/>
-      <c r="AK6" s="367"/>
-      <c r="AL6" s="367"/>
+      <c r="C6" s="378"/>
+      <c r="D6" s="378"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
+      <c r="G6" s="378"/>
+      <c r="H6" s="378"/>
+      <c r="I6" s="378"/>
+      <c r="J6" s="378"/>
+      <c r="K6" s="378"/>
+      <c r="L6" s="378"/>
+      <c r="M6" s="378"/>
+      <c r="N6" s="378"/>
+      <c r="O6" s="378"/>
+      <c r="P6" s="378"/>
+      <c r="Q6" s="378"/>
+      <c r="R6" s="378"/>
+      <c r="S6" s="378"/>
+      <c r="T6" s="378"/>
+      <c r="U6" s="378"/>
+      <c r="V6" s="378"/>
+      <c r="W6" s="378"/>
+      <c r="X6" s="378"/>
+      <c r="Y6" s="378"/>
+      <c r="Z6" s="378"/>
+      <c r="AA6" s="378"/>
+      <c r="AB6" s="378"/>
+      <c r="AC6" s="378"/>
+      <c r="AD6" s="378"/>
+      <c r="AE6" s="378"/>
+      <c r="AF6" s="378"/>
+      <c r="AG6" s="378"/>
+      <c r="AH6" s="378"/>
+      <c r="AI6" s="378"/>
+      <c r="AJ6" s="378"/>
+      <c r="AK6" s="378"/>
+      <c r="AL6" s="378"/>
       <c r="AN6" s="174"/>
       <c r="AO6" s="179"/>
       <c r="AP6" s="179"/>
@@ -41452,44 +41452,44 @@
       <c r="BW6" s="179"/>
     </row>
     <row r="7" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="367" t="s">
+      <c r="B7" s="378" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="367"/>
-      <c r="D7" s="367"/>
-      <c r="E7" s="367"/>
-      <c r="F7" s="367"/>
-      <c r="G7" s="367"/>
-      <c r="H7" s="367"/>
-      <c r="I7" s="367"/>
-      <c r="J7" s="367"/>
-      <c r="K7" s="367"/>
-      <c r="L7" s="367"/>
-      <c r="M7" s="367"/>
-      <c r="N7" s="367"/>
-      <c r="O7" s="367"/>
-      <c r="P7" s="367"/>
-      <c r="Q7" s="367"/>
-      <c r="R7" s="367"/>
-      <c r="S7" s="367"/>
-      <c r="T7" s="367"/>
-      <c r="U7" s="367"/>
-      <c r="V7" s="367"/>
-      <c r="W7" s="367"/>
-      <c r="X7" s="367"/>
-      <c r="Y7" s="367"/>
-      <c r="Z7" s="367"/>
-      <c r="AA7" s="367"/>
-      <c r="AB7" s="367"/>
-      <c r="AC7" s="367"/>
-      <c r="AD7" s="367"/>
-      <c r="AE7" s="367"/>
-      <c r="AF7" s="367"/>
-      <c r="AG7" s="367"/>
-      <c r="AH7" s="367"/>
-      <c r="AI7" s="367"/>
-      <c r="AJ7" s="367"/>
-      <c r="AK7" s="367"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="378"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
+      <c r="G7" s="378"/>
+      <c r="H7" s="378"/>
+      <c r="I7" s="378"/>
+      <c r="J7" s="378"/>
+      <c r="K7" s="378"/>
+      <c r="L7" s="378"/>
+      <c r="M7" s="378"/>
+      <c r="N7" s="378"/>
+      <c r="O7" s="378"/>
+      <c r="P7" s="378"/>
+      <c r="Q7" s="378"/>
+      <c r="R7" s="378"/>
+      <c r="S7" s="378"/>
+      <c r="T7" s="378"/>
+      <c r="U7" s="378"/>
+      <c r="V7" s="378"/>
+      <c r="W7" s="378"/>
+      <c r="X7" s="378"/>
+      <c r="Y7" s="378"/>
+      <c r="Z7" s="378"/>
+      <c r="AA7" s="378"/>
+      <c r="AB7" s="378"/>
+      <c r="AC7" s="378"/>
+      <c r="AD7" s="378"/>
+      <c r="AE7" s="378"/>
+      <c r="AF7" s="378"/>
+      <c r="AG7" s="378"/>
+      <c r="AH7" s="378"/>
+      <c r="AI7" s="378"/>
+      <c r="AJ7" s="378"/>
+      <c r="AK7" s="378"/>
       <c r="AN7" s="174"/>
       <c r="AO7" s="179"/>
       <c r="AP7" s="179"/>
@@ -41528,42 +41528,42 @@
       <c r="BW7" s="179"/>
     </row>
     <row r="8" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="367"/>
-      <c r="C8" s="367"/>
-      <c r="D8" s="367"/>
-      <c r="E8" s="367"/>
-      <c r="F8" s="367"/>
-      <c r="G8" s="367"/>
-      <c r="H8" s="367"/>
-      <c r="I8" s="367"/>
-      <c r="J8" s="367"/>
-      <c r="K8" s="367"/>
-      <c r="L8" s="367"/>
-      <c r="M8" s="367"/>
-      <c r="N8" s="367"/>
-      <c r="O8" s="367"/>
-      <c r="P8" s="367"/>
-      <c r="Q8" s="367"/>
-      <c r="R8" s="367"/>
-      <c r="S8" s="367"/>
-      <c r="T8" s="367"/>
-      <c r="U8" s="367"/>
-      <c r="V8" s="367"/>
-      <c r="W8" s="367"/>
-      <c r="X8" s="367"/>
-      <c r="Y8" s="367"/>
-      <c r="Z8" s="367"/>
-      <c r="AA8" s="367"/>
-      <c r="AB8" s="367"/>
-      <c r="AC8" s="367"/>
-      <c r="AD8" s="367"/>
-      <c r="AE8" s="367"/>
-      <c r="AF8" s="367"/>
-      <c r="AG8" s="367"/>
-      <c r="AH8" s="367"/>
-      <c r="AI8" s="367"/>
-      <c r="AJ8" s="367"/>
-      <c r="AK8" s="367"/>
+      <c r="B8" s="378"/>
+      <c r="C8" s="378"/>
+      <c r="D8" s="378"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
+      <c r="G8" s="378"/>
+      <c r="H8" s="378"/>
+      <c r="I8" s="378"/>
+      <c r="J8" s="378"/>
+      <c r="K8" s="378"/>
+      <c r="L8" s="378"/>
+      <c r="M8" s="378"/>
+      <c r="N8" s="378"/>
+      <c r="O8" s="378"/>
+      <c r="P8" s="378"/>
+      <c r="Q8" s="378"/>
+      <c r="R8" s="378"/>
+      <c r="S8" s="378"/>
+      <c r="T8" s="378"/>
+      <c r="U8" s="378"/>
+      <c r="V8" s="378"/>
+      <c r="W8" s="378"/>
+      <c r="X8" s="378"/>
+      <c r="Y8" s="378"/>
+      <c r="Z8" s="378"/>
+      <c r="AA8" s="378"/>
+      <c r="AB8" s="378"/>
+      <c r="AC8" s="378"/>
+      <c r="AD8" s="378"/>
+      <c r="AE8" s="378"/>
+      <c r="AF8" s="378"/>
+      <c r="AG8" s="378"/>
+      <c r="AH8" s="378"/>
+      <c r="AI8" s="378"/>
+      <c r="AJ8" s="378"/>
+      <c r="AK8" s="378"/>
       <c r="AN8" s="179"/>
       <c r="AO8" s="174"/>
       <c r="AP8" s="179"/>
@@ -41602,42 +41602,42 @@
       <c r="BW8" s="179"/>
     </row>
     <row r="9" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="367"/>
-      <c r="C9" s="367"/>
-      <c r="D9" s="367"/>
-      <c r="E9" s="367"/>
-      <c r="F9" s="367"/>
-      <c r="G9" s="367"/>
-      <c r="H9" s="367"/>
-      <c r="I9" s="367"/>
-      <c r="J9" s="367"/>
-      <c r="K9" s="367"/>
-      <c r="L9" s="367"/>
-      <c r="M9" s="367"/>
-      <c r="N9" s="367"/>
-      <c r="O9" s="367"/>
-      <c r="P9" s="367"/>
-      <c r="Q9" s="367"/>
-      <c r="R9" s="367"/>
-      <c r="S9" s="367"/>
-      <c r="T9" s="367"/>
-      <c r="U9" s="367"/>
-      <c r="V9" s="367"/>
-      <c r="W9" s="367"/>
-      <c r="X9" s="367"/>
-      <c r="Y9" s="367"/>
-      <c r="Z9" s="367"/>
-      <c r="AA9" s="367"/>
-      <c r="AB9" s="367"/>
-      <c r="AC9" s="367"/>
-      <c r="AD9" s="367"/>
-      <c r="AE9" s="367"/>
-      <c r="AF9" s="367"/>
-      <c r="AG9" s="367"/>
-      <c r="AH9" s="367"/>
-      <c r="AI9" s="367"/>
-      <c r="AJ9" s="367"/>
-      <c r="AK9" s="367"/>
+      <c r="B9" s="378"/>
+      <c r="C9" s="378"/>
+      <c r="D9" s="378"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
+      <c r="G9" s="378"/>
+      <c r="H9" s="378"/>
+      <c r="I9" s="378"/>
+      <c r="J9" s="378"/>
+      <c r="K9" s="378"/>
+      <c r="L9" s="378"/>
+      <c r="M9" s="378"/>
+      <c r="N9" s="378"/>
+      <c r="O9" s="378"/>
+      <c r="P9" s="378"/>
+      <c r="Q9" s="378"/>
+      <c r="R9" s="378"/>
+      <c r="S9" s="378"/>
+      <c r="T9" s="378"/>
+      <c r="U9" s="378"/>
+      <c r="V9" s="378"/>
+      <c r="W9" s="378"/>
+      <c r="X9" s="378"/>
+      <c r="Y9" s="378"/>
+      <c r="Z9" s="378"/>
+      <c r="AA9" s="378"/>
+      <c r="AB9" s="378"/>
+      <c r="AC9" s="378"/>
+      <c r="AD9" s="378"/>
+      <c r="AE9" s="378"/>
+      <c r="AF9" s="378"/>
+      <c r="AG9" s="378"/>
+      <c r="AH9" s="378"/>
+      <c r="AI9" s="378"/>
+      <c r="AJ9" s="378"/>
+      <c r="AK9" s="378"/>
       <c r="AN9" s="174"/>
       <c r="AO9" s="179"/>
       <c r="AP9" s="179"/>
@@ -41676,44 +41676,44 @@
       <c r="BW9" s="179"/>
     </row>
     <row r="10" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="367" t="s">
+      <c r="B10" s="378" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367"/>
-      <c r="E10" s="367"/>
-      <c r="F10" s="367"/>
-      <c r="G10" s="367"/>
-      <c r="H10" s="367"/>
-      <c r="I10" s="367"/>
-      <c r="J10" s="367"/>
-      <c r="K10" s="367"/>
-      <c r="L10" s="367"/>
-      <c r="M10" s="367"/>
-      <c r="N10" s="367"/>
-      <c r="O10" s="367"/>
-      <c r="P10" s="367"/>
-      <c r="Q10" s="367"/>
-      <c r="R10" s="367"/>
-      <c r="S10" s="367"/>
-      <c r="T10" s="367"/>
-      <c r="U10" s="367"/>
-      <c r="V10" s="367"/>
-      <c r="W10" s="367"/>
-      <c r="X10" s="367"/>
-      <c r="Y10" s="367"/>
-      <c r="Z10" s="367"/>
-      <c r="AA10" s="367"/>
-      <c r="AB10" s="367"/>
-      <c r="AC10" s="367"/>
-      <c r="AD10" s="367"/>
-      <c r="AE10" s="367"/>
-      <c r="AF10" s="367"/>
-      <c r="AG10" s="367"/>
-      <c r="AH10" s="367"/>
-      <c r="AI10" s="367"/>
-      <c r="AJ10" s="367"/>
-      <c r="AK10" s="367"/>
+      <c r="C10" s="378"/>
+      <c r="D10" s="378"/>
+      <c r="E10" s="378"/>
+      <c r="F10" s="378"/>
+      <c r="G10" s="378"/>
+      <c r="H10" s="378"/>
+      <c r="I10" s="378"/>
+      <c r="J10" s="378"/>
+      <c r="K10" s="378"/>
+      <c r="L10" s="378"/>
+      <c r="M10" s="378"/>
+      <c r="N10" s="378"/>
+      <c r="O10" s="378"/>
+      <c r="P10" s="378"/>
+      <c r="Q10" s="378"/>
+      <c r="R10" s="378"/>
+      <c r="S10" s="378"/>
+      <c r="T10" s="378"/>
+      <c r="U10" s="378"/>
+      <c r="V10" s="378"/>
+      <c r="W10" s="378"/>
+      <c r="X10" s="378"/>
+      <c r="Y10" s="378"/>
+      <c r="Z10" s="378"/>
+      <c r="AA10" s="378"/>
+      <c r="AB10" s="378"/>
+      <c r="AC10" s="378"/>
+      <c r="AD10" s="378"/>
+      <c r="AE10" s="378"/>
+      <c r="AF10" s="378"/>
+      <c r="AG10" s="378"/>
+      <c r="AH10" s="378"/>
+      <c r="AI10" s="378"/>
+      <c r="AJ10" s="378"/>
+      <c r="AK10" s="378"/>
       <c r="AN10" s="179"/>
       <c r="AO10" s="172"/>
       <c r="AP10" s="172"/>
@@ -41752,42 +41752,42 @@
       <c r="BW10" s="172"/>
     </row>
     <row r="11" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="367"/>
-      <c r="C11" s="367"/>
-      <c r="D11" s="367"/>
-      <c r="E11" s="367"/>
-      <c r="F11" s="367"/>
-      <c r="G11" s="367"/>
-      <c r="H11" s="367"/>
-      <c r="I11" s="367"/>
-      <c r="J11" s="367"/>
-      <c r="K11" s="367"/>
-      <c r="L11" s="367"/>
-      <c r="M11" s="367"/>
-      <c r="N11" s="367"/>
-      <c r="O11" s="367"/>
-      <c r="P11" s="367"/>
-      <c r="Q11" s="367"/>
-      <c r="R11" s="367"/>
-      <c r="S11" s="367"/>
-      <c r="T11" s="367"/>
-      <c r="U11" s="367"/>
-      <c r="V11" s="367"/>
-      <c r="W11" s="367"/>
-      <c r="X11" s="367"/>
-      <c r="Y11" s="367"/>
-      <c r="Z11" s="367"/>
-      <c r="AA11" s="367"/>
-      <c r="AB11" s="367"/>
-      <c r="AC11" s="367"/>
-      <c r="AD11" s="367"/>
-      <c r="AE11" s="367"/>
-      <c r="AF11" s="367"/>
-      <c r="AG11" s="367"/>
-      <c r="AH11" s="367"/>
-      <c r="AI11" s="367"/>
-      <c r="AJ11" s="367"/>
-      <c r="AK11" s="367"/>
+      <c r="B11" s="378"/>
+      <c r="C11" s="378"/>
+      <c r="D11" s="378"/>
+      <c r="E11" s="378"/>
+      <c r="F11" s="378"/>
+      <c r="G11" s="378"/>
+      <c r="H11" s="378"/>
+      <c r="I11" s="378"/>
+      <c r="J11" s="378"/>
+      <c r="K11" s="378"/>
+      <c r="L11" s="378"/>
+      <c r="M11" s="378"/>
+      <c r="N11" s="378"/>
+      <c r="O11" s="378"/>
+      <c r="P11" s="378"/>
+      <c r="Q11" s="378"/>
+      <c r="R11" s="378"/>
+      <c r="S11" s="378"/>
+      <c r="T11" s="378"/>
+      <c r="U11" s="378"/>
+      <c r="V11" s="378"/>
+      <c r="W11" s="378"/>
+      <c r="X11" s="378"/>
+      <c r="Y11" s="378"/>
+      <c r="Z11" s="378"/>
+      <c r="AA11" s="378"/>
+      <c r="AB11" s="378"/>
+      <c r="AC11" s="378"/>
+      <c r="AD11" s="378"/>
+      <c r="AE11" s="378"/>
+      <c r="AF11" s="378"/>
+      <c r="AG11" s="378"/>
+      <c r="AH11" s="378"/>
+      <c r="AI11" s="378"/>
+      <c r="AJ11" s="378"/>
+      <c r="AK11" s="378"/>
       <c r="AN11" s="174"/>
       <c r="AO11" s="179"/>
       <c r="AP11" s="179"/>
@@ -41826,42 +41826,42 @@
       <c r="BW11" s="179"/>
     </row>
     <row r="12" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="367"/>
-      <c r="C12" s="367"/>
-      <c r="D12" s="367"/>
-      <c r="E12" s="367"/>
-      <c r="F12" s="367"/>
-      <c r="G12" s="367"/>
-      <c r="H12" s="367"/>
-      <c r="I12" s="367"/>
-      <c r="J12" s="367"/>
-      <c r="K12" s="367"/>
-      <c r="L12" s="367"/>
-      <c r="M12" s="367"/>
-      <c r="N12" s="367"/>
-      <c r="O12" s="367"/>
-      <c r="P12" s="367"/>
-      <c r="Q12" s="367"/>
-      <c r="R12" s="367"/>
-      <c r="S12" s="367"/>
-      <c r="T12" s="367"/>
-      <c r="U12" s="367"/>
-      <c r="V12" s="367"/>
-      <c r="W12" s="367"/>
-      <c r="X12" s="367"/>
-      <c r="Y12" s="367"/>
-      <c r="Z12" s="367"/>
-      <c r="AA12" s="367"/>
-      <c r="AB12" s="367"/>
-      <c r="AC12" s="367"/>
-      <c r="AD12" s="367"/>
-      <c r="AE12" s="367"/>
-      <c r="AF12" s="367"/>
-      <c r="AG12" s="367"/>
-      <c r="AH12" s="367"/>
-      <c r="AI12" s="367"/>
-      <c r="AJ12" s="367"/>
-      <c r="AK12" s="367"/>
+      <c r="B12" s="378"/>
+      <c r="C12" s="378"/>
+      <c r="D12" s="378"/>
+      <c r="E12" s="378"/>
+      <c r="F12" s="378"/>
+      <c r="G12" s="378"/>
+      <c r="H12" s="378"/>
+      <c r="I12" s="378"/>
+      <c r="J12" s="378"/>
+      <c r="K12" s="378"/>
+      <c r="L12" s="378"/>
+      <c r="M12" s="378"/>
+      <c r="N12" s="378"/>
+      <c r="O12" s="378"/>
+      <c r="P12" s="378"/>
+      <c r="Q12" s="378"/>
+      <c r="R12" s="378"/>
+      <c r="S12" s="378"/>
+      <c r="T12" s="378"/>
+      <c r="U12" s="378"/>
+      <c r="V12" s="378"/>
+      <c r="W12" s="378"/>
+      <c r="X12" s="378"/>
+      <c r="Y12" s="378"/>
+      <c r="Z12" s="378"/>
+      <c r="AA12" s="378"/>
+      <c r="AB12" s="378"/>
+      <c r="AC12" s="378"/>
+      <c r="AD12" s="378"/>
+      <c r="AE12" s="378"/>
+      <c r="AF12" s="378"/>
+      <c r="AG12" s="378"/>
+      <c r="AH12" s="378"/>
+      <c r="AI12" s="378"/>
+      <c r="AJ12" s="378"/>
+      <c r="AK12" s="378"/>
       <c r="AN12" s="179"/>
       <c r="AO12" s="174"/>
       <c r="AP12" s="179"/>
@@ -41900,44 +41900,44 @@
       <c r="BW12" s="179"/>
     </row>
     <row r="13" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="367" t="s">
+      <c r="B13" s="378" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="367"/>
-      <c r="D13" s="367"/>
-      <c r="E13" s="367"/>
-      <c r="F13" s="367"/>
-      <c r="G13" s="367"/>
-      <c r="H13" s="367"/>
-      <c r="I13" s="367"/>
-      <c r="J13" s="367"/>
-      <c r="K13" s="367"/>
-      <c r="L13" s="367"/>
-      <c r="M13" s="367"/>
-      <c r="N13" s="367"/>
-      <c r="O13" s="367"/>
-      <c r="P13" s="367"/>
-      <c r="Q13" s="367"/>
-      <c r="R13" s="367"/>
-      <c r="S13" s="367"/>
-      <c r="T13" s="367"/>
-      <c r="U13" s="367"/>
-      <c r="V13" s="367"/>
-      <c r="W13" s="367"/>
-      <c r="X13" s="367"/>
-      <c r="Y13" s="367"/>
-      <c r="Z13" s="367"/>
-      <c r="AA13" s="367"/>
-      <c r="AB13" s="367"/>
-      <c r="AC13" s="367"/>
-      <c r="AD13" s="367"/>
-      <c r="AE13" s="367"/>
-      <c r="AF13" s="367"/>
-      <c r="AG13" s="367"/>
-      <c r="AH13" s="367"/>
-      <c r="AI13" s="367"/>
-      <c r="AJ13" s="367"/>
-      <c r="AK13" s="367"/>
+      <c r="C13" s="378"/>
+      <c r="D13" s="378"/>
+      <c r="E13" s="378"/>
+      <c r="F13" s="378"/>
+      <c r="G13" s="378"/>
+      <c r="H13" s="378"/>
+      <c r="I13" s="378"/>
+      <c r="J13" s="378"/>
+      <c r="K13" s="378"/>
+      <c r="L13" s="378"/>
+      <c r="M13" s="378"/>
+      <c r="N13" s="378"/>
+      <c r="O13" s="378"/>
+      <c r="P13" s="378"/>
+      <c r="Q13" s="378"/>
+      <c r="R13" s="378"/>
+      <c r="S13" s="378"/>
+      <c r="T13" s="378"/>
+      <c r="U13" s="378"/>
+      <c r="V13" s="378"/>
+      <c r="W13" s="378"/>
+      <c r="X13" s="378"/>
+      <c r="Y13" s="378"/>
+      <c r="Z13" s="378"/>
+      <c r="AA13" s="378"/>
+      <c r="AB13" s="378"/>
+      <c r="AC13" s="378"/>
+      <c r="AD13" s="378"/>
+      <c r="AE13" s="378"/>
+      <c r="AF13" s="378"/>
+      <c r="AG13" s="378"/>
+      <c r="AH13" s="378"/>
+      <c r="AI13" s="378"/>
+      <c r="AJ13" s="378"/>
+      <c r="AK13" s="378"/>
       <c r="AN13" s="172"/>
       <c r="AO13" s="172"/>
       <c r="AP13" s="172"/>
@@ -41976,42 +41976,42 @@
       <c r="BW13" s="172"/>
     </row>
     <row r="14" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="367"/>
-      <c r="C14" s="367"/>
-      <c r="D14" s="367"/>
-      <c r="E14" s="367"/>
-      <c r="F14" s="367"/>
-      <c r="G14" s="367"/>
-      <c r="H14" s="367"/>
-      <c r="I14" s="367"/>
-      <c r="J14" s="367"/>
-      <c r="K14" s="367"/>
-      <c r="L14" s="367"/>
-      <c r="M14" s="367"/>
-      <c r="N14" s="367"/>
-      <c r="O14" s="367"/>
-      <c r="P14" s="367"/>
-      <c r="Q14" s="367"/>
-      <c r="R14" s="367"/>
-      <c r="S14" s="367"/>
-      <c r="T14" s="367"/>
-      <c r="U14" s="367"/>
-      <c r="V14" s="367"/>
-      <c r="W14" s="367"/>
-      <c r="X14" s="367"/>
-      <c r="Y14" s="367"/>
-      <c r="Z14" s="367"/>
-      <c r="AA14" s="367"/>
-      <c r="AB14" s="367"/>
-      <c r="AC14" s="367"/>
-      <c r="AD14" s="367"/>
-      <c r="AE14" s="367"/>
-      <c r="AF14" s="367"/>
-      <c r="AG14" s="367"/>
-      <c r="AH14" s="367"/>
-      <c r="AI14" s="367"/>
-      <c r="AJ14" s="367"/>
-      <c r="AK14" s="367"/>
+      <c r="B14" s="378"/>
+      <c r="C14" s="378"/>
+      <c r="D14" s="378"/>
+      <c r="E14" s="378"/>
+      <c r="F14" s="378"/>
+      <c r="G14" s="378"/>
+      <c r="H14" s="378"/>
+      <c r="I14" s="378"/>
+      <c r="J14" s="378"/>
+      <c r="K14" s="378"/>
+      <c r="L14" s="378"/>
+      <c r="M14" s="378"/>
+      <c r="N14" s="378"/>
+      <c r="O14" s="378"/>
+      <c r="P14" s="378"/>
+      <c r="Q14" s="378"/>
+      <c r="R14" s="378"/>
+      <c r="S14" s="378"/>
+      <c r="T14" s="378"/>
+      <c r="U14" s="378"/>
+      <c r="V14" s="378"/>
+      <c r="W14" s="378"/>
+      <c r="X14" s="378"/>
+      <c r="Y14" s="378"/>
+      <c r="Z14" s="378"/>
+      <c r="AA14" s="378"/>
+      <c r="AB14" s="378"/>
+      <c r="AC14" s="378"/>
+      <c r="AD14" s="378"/>
+      <c r="AE14" s="378"/>
+      <c r="AF14" s="378"/>
+      <c r="AG14" s="378"/>
+      <c r="AH14" s="378"/>
+      <c r="AI14" s="378"/>
+      <c r="AJ14" s="378"/>
+      <c r="AK14" s="378"/>
       <c r="AN14" s="174"/>
       <c r="AO14" s="179"/>
       <c r="AP14" s="179"/>
@@ -42050,42 +42050,42 @@
       <c r="BW14" s="179"/>
     </row>
     <row r="15" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="367"/>
-      <c r="C15" s="367"/>
-      <c r="D15" s="367"/>
-      <c r="E15" s="367"/>
-      <c r="F15" s="367"/>
-      <c r="G15" s="367"/>
-      <c r="H15" s="367"/>
-      <c r="I15" s="367"/>
-      <c r="J15" s="367"/>
-      <c r="K15" s="367"/>
-      <c r="L15" s="367"/>
-      <c r="M15" s="367"/>
-      <c r="N15" s="367"/>
-      <c r="O15" s="367"/>
-      <c r="P15" s="367"/>
-      <c r="Q15" s="367"/>
-      <c r="R15" s="367"/>
-      <c r="S15" s="367"/>
-      <c r="T15" s="367"/>
-      <c r="U15" s="367"/>
-      <c r="V15" s="367"/>
-      <c r="W15" s="367"/>
-      <c r="X15" s="367"/>
-      <c r="Y15" s="367"/>
-      <c r="Z15" s="367"/>
-      <c r="AA15" s="367"/>
-      <c r="AB15" s="367"/>
-      <c r="AC15" s="367"/>
-      <c r="AD15" s="367"/>
-      <c r="AE15" s="367"/>
-      <c r="AF15" s="367"/>
-      <c r="AG15" s="367"/>
-      <c r="AH15" s="367"/>
-      <c r="AI15" s="367"/>
-      <c r="AJ15" s="367"/>
-      <c r="AK15" s="367"/>
+      <c r="B15" s="378"/>
+      <c r="C15" s="378"/>
+      <c r="D15" s="378"/>
+      <c r="E15" s="378"/>
+      <c r="F15" s="378"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="378"/>
+      <c r="K15" s="378"/>
+      <c r="L15" s="378"/>
+      <c r="M15" s="378"/>
+      <c r="N15" s="378"/>
+      <c r="O15" s="378"/>
+      <c r="P15" s="378"/>
+      <c r="Q15" s="378"/>
+      <c r="R15" s="378"/>
+      <c r="S15" s="378"/>
+      <c r="T15" s="378"/>
+      <c r="U15" s="378"/>
+      <c r="V15" s="378"/>
+      <c r="W15" s="378"/>
+      <c r="X15" s="378"/>
+      <c r="Y15" s="378"/>
+      <c r="Z15" s="378"/>
+      <c r="AA15" s="378"/>
+      <c r="AB15" s="378"/>
+      <c r="AC15" s="378"/>
+      <c r="AD15" s="378"/>
+      <c r="AE15" s="378"/>
+      <c r="AF15" s="378"/>
+      <c r="AG15" s="378"/>
+      <c r="AH15" s="378"/>
+      <c r="AI15" s="378"/>
+      <c r="AJ15" s="378"/>
+      <c r="AK15" s="378"/>
       <c r="AN15" s="174"/>
       <c r="AO15" s="179"/>
       <c r="AP15" s="179"/>
@@ -42124,42 +42124,42 @@
       <c r="BW15" s="179"/>
     </row>
     <row r="16" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="367"/>
-      <c r="C16" s="367"/>
-      <c r="D16" s="367"/>
-      <c r="E16" s="367"/>
-      <c r="F16" s="367"/>
-      <c r="G16" s="367"/>
-      <c r="H16" s="367"/>
-      <c r="I16" s="367"/>
-      <c r="J16" s="367"/>
-      <c r="K16" s="367"/>
-      <c r="L16" s="367"/>
-      <c r="M16" s="367"/>
-      <c r="N16" s="367"/>
-      <c r="O16" s="367"/>
-      <c r="P16" s="367"/>
-      <c r="Q16" s="367"/>
-      <c r="R16" s="367"/>
-      <c r="S16" s="367"/>
-      <c r="T16" s="367"/>
-      <c r="U16" s="367"/>
-      <c r="V16" s="367"/>
-      <c r="W16" s="367"/>
-      <c r="X16" s="367"/>
-      <c r="Y16" s="367"/>
-      <c r="Z16" s="367"/>
-      <c r="AA16" s="367"/>
-      <c r="AB16" s="367"/>
-      <c r="AC16" s="367"/>
-      <c r="AD16" s="367"/>
-      <c r="AE16" s="367"/>
-      <c r="AF16" s="367"/>
-      <c r="AG16" s="367"/>
-      <c r="AH16" s="367"/>
-      <c r="AI16" s="367"/>
-      <c r="AJ16" s="367"/>
-      <c r="AK16" s="367"/>
+      <c r="B16" s="378"/>
+      <c r="C16" s="378"/>
+      <c r="D16" s="378"/>
+      <c r="E16" s="378"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="378"/>
+      <c r="J16" s="378"/>
+      <c r="K16" s="378"/>
+      <c r="L16" s="378"/>
+      <c r="M16" s="378"/>
+      <c r="N16" s="378"/>
+      <c r="O16" s="378"/>
+      <c r="P16" s="378"/>
+      <c r="Q16" s="378"/>
+      <c r="R16" s="378"/>
+      <c r="S16" s="378"/>
+      <c r="T16" s="378"/>
+      <c r="U16" s="378"/>
+      <c r="V16" s="378"/>
+      <c r="W16" s="378"/>
+      <c r="X16" s="378"/>
+      <c r="Y16" s="378"/>
+      <c r="Z16" s="378"/>
+      <c r="AA16" s="378"/>
+      <c r="AB16" s="378"/>
+      <c r="AC16" s="378"/>
+      <c r="AD16" s="378"/>
+      <c r="AE16" s="378"/>
+      <c r="AF16" s="378"/>
+      <c r="AG16" s="378"/>
+      <c r="AH16" s="378"/>
+      <c r="AI16" s="378"/>
+      <c r="AJ16" s="378"/>
+      <c r="AK16" s="378"/>
       <c r="AN16" s="179"/>
       <c r="AO16" s="174"/>
       <c r="AP16" s="179"/>
@@ -42198,42 +42198,42 @@
       <c r="BW16" s="179"/>
     </row>
     <row r="17" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="367"/>
-      <c r="C17" s="367"/>
-      <c r="D17" s="367"/>
-      <c r="E17" s="367"/>
-      <c r="F17" s="367"/>
-      <c r="G17" s="367"/>
-      <c r="H17" s="367"/>
-      <c r="I17" s="367"/>
-      <c r="J17" s="367"/>
-      <c r="K17" s="367"/>
-      <c r="L17" s="367"/>
-      <c r="M17" s="367"/>
-      <c r="N17" s="367"/>
-      <c r="O17" s="367"/>
-      <c r="P17" s="367"/>
-      <c r="Q17" s="367"/>
-      <c r="R17" s="367"/>
-      <c r="S17" s="367"/>
-      <c r="T17" s="367"/>
-      <c r="U17" s="367"/>
-      <c r="V17" s="367"/>
-      <c r="W17" s="367"/>
-      <c r="X17" s="367"/>
-      <c r="Y17" s="367"/>
-      <c r="Z17" s="367"/>
-      <c r="AA17" s="367"/>
-      <c r="AB17" s="367"/>
-      <c r="AC17" s="367"/>
-      <c r="AD17" s="367"/>
-      <c r="AE17" s="367"/>
-      <c r="AF17" s="367"/>
-      <c r="AG17" s="367"/>
-      <c r="AH17" s="367"/>
-      <c r="AI17" s="367"/>
-      <c r="AJ17" s="367"/>
-      <c r="AK17" s="367"/>
+      <c r="B17" s="378"/>
+      <c r="C17" s="378"/>
+      <c r="D17" s="378"/>
+      <c r="E17" s="378"/>
+      <c r="F17" s="378"/>
+      <c r="G17" s="378"/>
+      <c r="H17" s="378"/>
+      <c r="I17" s="378"/>
+      <c r="J17" s="378"/>
+      <c r="K17" s="378"/>
+      <c r="L17" s="378"/>
+      <c r="M17" s="378"/>
+      <c r="N17" s="378"/>
+      <c r="O17" s="378"/>
+      <c r="P17" s="378"/>
+      <c r="Q17" s="378"/>
+      <c r="R17" s="378"/>
+      <c r="S17" s="378"/>
+      <c r="T17" s="378"/>
+      <c r="U17" s="378"/>
+      <c r="V17" s="378"/>
+      <c r="W17" s="378"/>
+      <c r="X17" s="378"/>
+      <c r="Y17" s="378"/>
+      <c r="Z17" s="378"/>
+      <c r="AA17" s="378"/>
+      <c r="AB17" s="378"/>
+      <c r="AC17" s="378"/>
+      <c r="AD17" s="378"/>
+      <c r="AE17" s="378"/>
+      <c r="AF17" s="378"/>
+      <c r="AG17" s="378"/>
+      <c r="AH17" s="378"/>
+      <c r="AI17" s="378"/>
+      <c r="AJ17" s="378"/>
+      <c r="AK17" s="378"/>
       <c r="AN17" s="172"/>
       <c r="AO17" s="172"/>
       <c r="AP17" s="172"/>
@@ -42272,44 +42272,44 @@
       <c r="BW17" s="172"/>
     </row>
     <row r="18" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="378" t="s">
         <v>197</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
-      <c r="G18" s="367"/>
-      <c r="H18" s="367"/>
-      <c r="I18" s="367"/>
-      <c r="J18" s="367"/>
-      <c r="K18" s="367"/>
-      <c r="L18" s="367"/>
-      <c r="M18" s="367"/>
-      <c r="N18" s="367"/>
-      <c r="O18" s="367"/>
-      <c r="P18" s="367"/>
-      <c r="Q18" s="367"/>
-      <c r="R18" s="367"/>
-      <c r="S18" s="367"/>
-      <c r="T18" s="367"/>
-      <c r="U18" s="367"/>
-      <c r="V18" s="367"/>
-      <c r="W18" s="367"/>
-      <c r="X18" s="367"/>
-      <c r="Y18" s="367"/>
-      <c r="Z18" s="367"/>
-      <c r="AA18" s="367"/>
-      <c r="AB18" s="367"/>
-      <c r="AC18" s="367"/>
-      <c r="AD18" s="367"/>
-      <c r="AE18" s="367"/>
-      <c r="AF18" s="367"/>
-      <c r="AG18" s="367"/>
-      <c r="AH18" s="367"/>
-      <c r="AI18" s="367"/>
-      <c r="AJ18" s="367"/>
-      <c r="AK18" s="367"/>
+      <c r="C18" s="378"/>
+      <c r="D18" s="378"/>
+      <c r="E18" s="378"/>
+      <c r="F18" s="378"/>
+      <c r="G18" s="378"/>
+      <c r="H18" s="378"/>
+      <c r="I18" s="378"/>
+      <c r="J18" s="378"/>
+      <c r="K18" s="378"/>
+      <c r="L18" s="378"/>
+      <c r="M18" s="378"/>
+      <c r="N18" s="378"/>
+      <c r="O18" s="378"/>
+      <c r="P18" s="378"/>
+      <c r="Q18" s="378"/>
+      <c r="R18" s="378"/>
+      <c r="S18" s="378"/>
+      <c r="T18" s="378"/>
+      <c r="U18" s="378"/>
+      <c r="V18" s="378"/>
+      <c r="W18" s="378"/>
+      <c r="X18" s="378"/>
+      <c r="Y18" s="378"/>
+      <c r="Z18" s="378"/>
+      <c r="AA18" s="378"/>
+      <c r="AB18" s="378"/>
+      <c r="AC18" s="378"/>
+      <c r="AD18" s="378"/>
+      <c r="AE18" s="378"/>
+      <c r="AF18" s="378"/>
+      <c r="AG18" s="378"/>
+      <c r="AH18" s="378"/>
+      <c r="AI18" s="378"/>
+      <c r="AJ18" s="378"/>
+      <c r="AK18" s="378"/>
       <c r="AN18" s="172"/>
       <c r="AO18" s="172"/>
       <c r="AP18" s="172"/>
@@ -42348,42 +42348,42 @@
       <c r="BW18" s="172"/>
     </row>
     <row r="19" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="367"/>
-      <c r="C19" s="367"/>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="367"/>
-      <c r="H19" s="367"/>
-      <c r="I19" s="367"/>
-      <c r="J19" s="367"/>
-      <c r="K19" s="367"/>
-      <c r="L19" s="367"/>
-      <c r="M19" s="367"/>
-      <c r="N19" s="367"/>
-      <c r="O19" s="367"/>
-      <c r="P19" s="367"/>
-      <c r="Q19" s="367"/>
-      <c r="R19" s="367"/>
-      <c r="S19" s="367"/>
-      <c r="T19" s="367"/>
-      <c r="U19" s="367"/>
-      <c r="V19" s="367"/>
-      <c r="W19" s="367"/>
-      <c r="X19" s="367"/>
-      <c r="Y19" s="367"/>
-      <c r="Z19" s="367"/>
-      <c r="AA19" s="367"/>
-      <c r="AB19" s="367"/>
-      <c r="AC19" s="367"/>
-      <c r="AD19" s="367"/>
-      <c r="AE19" s="367"/>
-      <c r="AF19" s="367"/>
-      <c r="AG19" s="367"/>
-      <c r="AH19" s="367"/>
-      <c r="AI19" s="367"/>
-      <c r="AJ19" s="367"/>
-      <c r="AK19" s="367"/>
+      <c r="B19" s="378"/>
+      <c r="C19" s="378"/>
+      <c r="D19" s="378"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
+      <c r="G19" s="378"/>
+      <c r="H19" s="378"/>
+      <c r="I19" s="378"/>
+      <c r="J19" s="378"/>
+      <c r="K19" s="378"/>
+      <c r="L19" s="378"/>
+      <c r="M19" s="378"/>
+      <c r="N19" s="378"/>
+      <c r="O19" s="378"/>
+      <c r="P19" s="378"/>
+      <c r="Q19" s="378"/>
+      <c r="R19" s="378"/>
+      <c r="S19" s="378"/>
+      <c r="T19" s="378"/>
+      <c r="U19" s="378"/>
+      <c r="V19" s="378"/>
+      <c r="W19" s="378"/>
+      <c r="X19" s="378"/>
+      <c r="Y19" s="378"/>
+      <c r="Z19" s="378"/>
+      <c r="AA19" s="378"/>
+      <c r="AB19" s="378"/>
+      <c r="AC19" s="378"/>
+      <c r="AD19" s="378"/>
+      <c r="AE19" s="378"/>
+      <c r="AF19" s="378"/>
+      <c r="AG19" s="378"/>
+      <c r="AH19" s="378"/>
+      <c r="AI19" s="378"/>
+      <c r="AJ19" s="378"/>
+      <c r="AK19" s="378"/>
       <c r="AN19" s="172"/>
       <c r="AO19" s="172"/>
       <c r="AP19" s="172"/>
@@ -42422,42 +42422,42 @@
       <c r="BW19" s="172"/>
     </row>
     <row r="20" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="367"/>
-      <c r="C20" s="367"/>
-      <c r="D20" s="367"/>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
-      <c r="G20" s="367"/>
-      <c r="H20" s="367"/>
-      <c r="I20" s="367"/>
-      <c r="J20" s="367"/>
-      <c r="K20" s="367"/>
-      <c r="L20" s="367"/>
-      <c r="M20" s="367"/>
-      <c r="N20" s="367"/>
-      <c r="O20" s="367"/>
-      <c r="P20" s="367"/>
-      <c r="Q20" s="367"/>
-      <c r="R20" s="367"/>
-      <c r="S20" s="367"/>
-      <c r="T20" s="367"/>
-      <c r="U20" s="367"/>
-      <c r="V20" s="367"/>
-      <c r="W20" s="367"/>
-      <c r="X20" s="367"/>
-      <c r="Y20" s="367"/>
-      <c r="Z20" s="367"/>
-      <c r="AA20" s="367"/>
-      <c r="AB20" s="367"/>
-      <c r="AC20" s="367"/>
-      <c r="AD20" s="367"/>
-      <c r="AE20" s="367"/>
-      <c r="AF20" s="367"/>
-      <c r="AG20" s="367"/>
-      <c r="AH20" s="367"/>
-      <c r="AI20" s="367"/>
-      <c r="AJ20" s="367"/>
-      <c r="AK20" s="367"/>
+      <c r="B20" s="378"/>
+      <c r="C20" s="378"/>
+      <c r="D20" s="378"/>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
+      <c r="G20" s="378"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="378"/>
+      <c r="J20" s="378"/>
+      <c r="K20" s="378"/>
+      <c r="L20" s="378"/>
+      <c r="M20" s="378"/>
+      <c r="N20" s="378"/>
+      <c r="O20" s="378"/>
+      <c r="P20" s="378"/>
+      <c r="Q20" s="378"/>
+      <c r="R20" s="378"/>
+      <c r="S20" s="378"/>
+      <c r="T20" s="378"/>
+      <c r="U20" s="378"/>
+      <c r="V20" s="378"/>
+      <c r="W20" s="378"/>
+      <c r="X20" s="378"/>
+      <c r="Y20" s="378"/>
+      <c r="Z20" s="378"/>
+      <c r="AA20" s="378"/>
+      <c r="AB20" s="378"/>
+      <c r="AC20" s="378"/>
+      <c r="AD20" s="378"/>
+      <c r="AE20" s="378"/>
+      <c r="AF20" s="378"/>
+      <c r="AG20" s="378"/>
+      <c r="AH20" s="378"/>
+      <c r="AI20" s="378"/>
+      <c r="AJ20" s="378"/>
+      <c r="AK20" s="378"/>
       <c r="AN20" s="174"/>
       <c r="AO20" s="179"/>
       <c r="AP20" s="179"/>
@@ -42496,42 +42496,42 @@
       <c r="BW20" s="179"/>
     </row>
     <row r="21" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="367"/>
-      <c r="C21" s="367"/>
-      <c r="D21" s="367"/>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
-      <c r="G21" s="367"/>
-      <c r="H21" s="367"/>
-      <c r="I21" s="367"/>
-      <c r="J21" s="367"/>
-      <c r="K21" s="367"/>
-      <c r="L21" s="367"/>
-      <c r="M21" s="367"/>
-      <c r="N21" s="367"/>
-      <c r="O21" s="367"/>
-      <c r="P21" s="367"/>
-      <c r="Q21" s="367"/>
-      <c r="R21" s="367"/>
-      <c r="S21" s="367"/>
-      <c r="T21" s="367"/>
-      <c r="U21" s="367"/>
-      <c r="V21" s="367"/>
-      <c r="W21" s="367"/>
-      <c r="X21" s="367"/>
-      <c r="Y21" s="367"/>
-      <c r="Z21" s="367"/>
-      <c r="AA21" s="367"/>
-      <c r="AB21" s="367"/>
-      <c r="AC21" s="367"/>
-      <c r="AD21" s="367"/>
-      <c r="AE21" s="367"/>
-      <c r="AF21" s="367"/>
-      <c r="AG21" s="367"/>
-      <c r="AH21" s="367"/>
-      <c r="AI21" s="367"/>
-      <c r="AJ21" s="367"/>
-      <c r="AK21" s="367"/>
+      <c r="B21" s="378"/>
+      <c r="C21" s="378"/>
+      <c r="D21" s="378"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
+      <c r="G21" s="378"/>
+      <c r="H21" s="378"/>
+      <c r="I21" s="378"/>
+      <c r="J21" s="378"/>
+      <c r="K21" s="378"/>
+      <c r="L21" s="378"/>
+      <c r="M21" s="378"/>
+      <c r="N21" s="378"/>
+      <c r="O21" s="378"/>
+      <c r="P21" s="378"/>
+      <c r="Q21" s="378"/>
+      <c r="R21" s="378"/>
+      <c r="S21" s="378"/>
+      <c r="T21" s="378"/>
+      <c r="U21" s="378"/>
+      <c r="V21" s="378"/>
+      <c r="W21" s="378"/>
+      <c r="X21" s="378"/>
+      <c r="Y21" s="378"/>
+      <c r="Z21" s="378"/>
+      <c r="AA21" s="378"/>
+      <c r="AB21" s="378"/>
+      <c r="AC21" s="378"/>
+      <c r="AD21" s="378"/>
+      <c r="AE21" s="378"/>
+      <c r="AF21" s="378"/>
+      <c r="AG21" s="378"/>
+      <c r="AH21" s="378"/>
+      <c r="AI21" s="378"/>
+      <c r="AJ21" s="378"/>
+      <c r="AK21" s="378"/>
       <c r="AN21" s="174"/>
       <c r="AO21" s="179"/>
       <c r="AP21" s="179"/>
@@ -42593,17 +42593,17 @@
       <c r="W22" s="181"/>
       <c r="X22" s="181"/>
       <c r="Y22" s="181"/>
-      <c r="Z22" s="370"/>
-      <c r="AA22" s="371"/>
-      <c r="AB22" s="371"/>
-      <c r="AC22" s="371"/>
-      <c r="AD22" s="372"/>
+      <c r="Z22" s="379"/>
+      <c r="AA22" s="380"/>
+      <c r="AB22" s="380"/>
+      <c r="AC22" s="380"/>
+      <c r="AD22" s="381"/>
       <c r="AE22" s="181"/>
-      <c r="AF22" s="370"/>
-      <c r="AG22" s="371"/>
-      <c r="AH22" s="371"/>
-      <c r="AI22" s="371"/>
-      <c r="AJ22" s="372"/>
+      <c r="AF22" s="379"/>
+      <c r="AG22" s="380"/>
+      <c r="AH22" s="380"/>
+      <c r="AI22" s="380"/>
+      <c r="AJ22" s="381"/>
       <c r="AK22" s="181"/>
     </row>
     <row r="23" spans="2:75" ht="20.100000000000001" customHeight="1">
@@ -42611,46 +42611,46 @@
       <c r="Q23" s="160" t="s">
         <v>199</v>
       </c>
-      <c r="Z23" s="373"/>
-      <c r="AA23" s="374"/>
-      <c r="AB23" s="374"/>
-      <c r="AC23" s="374"/>
-      <c r="AD23" s="375"/>
-      <c r="AF23" s="373"/>
-      <c r="AG23" s="374"/>
-      <c r="AH23" s="374"/>
-      <c r="AI23" s="374"/>
-      <c r="AJ23" s="375"/>
+      <c r="Z23" s="382"/>
+      <c r="AA23" s="383"/>
+      <c r="AB23" s="383"/>
+      <c r="AC23" s="383"/>
+      <c r="AD23" s="384"/>
+      <c r="AF23" s="382"/>
+      <c r="AG23" s="383"/>
+      <c r="AH23" s="383"/>
+      <c r="AI23" s="383"/>
+      <c r="AJ23" s="384"/>
     </row>
     <row r="24" spans="2:75" ht="20.100000000000001" customHeight="1">
       <c r="P24" s="182"/>
       <c r="Q24" s="160" t="s">
         <v>200</v>
       </c>
-      <c r="Z24" s="373"/>
-      <c r="AA24" s="374"/>
-      <c r="AB24" s="374"/>
-      <c r="AC24" s="374"/>
-      <c r="AD24" s="375"/>
-      <c r="AF24" s="373"/>
-      <c r="AG24" s="374"/>
-      <c r="AH24" s="374"/>
-      <c r="AI24" s="374"/>
-      <c r="AJ24" s="375"/>
+      <c r="Z24" s="382"/>
+      <c r="AA24" s="383"/>
+      <c r="AB24" s="383"/>
+      <c r="AC24" s="383"/>
+      <c r="AD24" s="384"/>
+      <c r="AF24" s="382"/>
+      <c r="AG24" s="383"/>
+      <c r="AH24" s="383"/>
+      <c r="AI24" s="383"/>
+      <c r="AJ24" s="384"/>
     </row>
     <row r="25" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="D25" s="381" t="str">
+      <c r="D25" s="390" t="str">
         <f>'YADAO, MELENCIO'!D22</f>
         <v>YADAO, MELENCIO C.</v>
       </c>
-      <c r="E25" s="381"/>
-      <c r="F25" s="381"/>
-      <c r="G25" s="381"/>
-      <c r="H25" s="381"/>
-      <c r="I25" s="381"/>
-      <c r="J25" s="381"/>
-      <c r="K25" s="381"/>
-      <c r="L25" s="381"/>
+      <c r="E25" s="390"/>
+      <c r="F25" s="390"/>
+      <c r="G25" s="390"/>
+      <c r="H25" s="390"/>
+      <c r="I25" s="390"/>
+      <c r="J25" s="390"/>
+      <c r="K25" s="390"/>
+      <c r="L25" s="390"/>
       <c r="P25" s="182"/>
       <c r="Q25" s="160" t="s">
         <v>116</v>
@@ -42658,56 +42658,56 @@
       <c r="S25" s="184"/>
       <c r="T25" s="184"/>
       <c r="U25" s="184"/>
-      <c r="Z25" s="373"/>
-      <c r="AA25" s="374"/>
-      <c r="AB25" s="374"/>
-      <c r="AC25" s="374"/>
-      <c r="AD25" s="375"/>
-      <c r="AF25" s="373"/>
-      <c r="AG25" s="374"/>
-      <c r="AH25" s="374"/>
-      <c r="AI25" s="374"/>
-      <c r="AJ25" s="375"/>
+      <c r="Z25" s="382"/>
+      <c r="AA25" s="383"/>
+      <c r="AB25" s="383"/>
+      <c r="AC25" s="383"/>
+      <c r="AD25" s="384"/>
+      <c r="AF25" s="382"/>
+      <c r="AG25" s="383"/>
+      <c r="AH25" s="383"/>
+      <c r="AI25" s="383"/>
+      <c r="AJ25" s="384"/>
     </row>
     <row r="26" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="379" t="s">
+      <c r="B26" s="388" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="379"/>
-      <c r="D26" s="379"/>
-      <c r="E26" s="379"/>
-      <c r="F26" s="379"/>
-      <c r="G26" s="379"/>
-      <c r="H26" s="379"/>
-      <c r="I26" s="379"/>
-      <c r="J26" s="379"/>
-      <c r="K26" s="379"/>
-      <c r="L26" s="379"/>
-      <c r="M26" s="379"/>
-      <c r="N26" s="379"/>
-      <c r="Z26" s="373"/>
-      <c r="AA26" s="374"/>
-      <c r="AB26" s="374"/>
-      <c r="AC26" s="374"/>
-      <c r="AD26" s="375"/>
-      <c r="AF26" s="373"/>
-      <c r="AG26" s="374"/>
-      <c r="AH26" s="374"/>
-      <c r="AI26" s="374"/>
-      <c r="AJ26" s="375"/>
+      <c r="C26" s="388"/>
+      <c r="D26" s="388"/>
+      <c r="E26" s="388"/>
+      <c r="F26" s="388"/>
+      <c r="G26" s="388"/>
+      <c r="H26" s="388"/>
+      <c r="I26" s="388"/>
+      <c r="J26" s="388"/>
+      <c r="K26" s="388"/>
+      <c r="L26" s="388"/>
+      <c r="M26" s="388"/>
+      <c r="N26" s="388"/>
+      <c r="Z26" s="382"/>
+      <c r="AA26" s="383"/>
+      <c r="AB26" s="383"/>
+      <c r="AC26" s="383"/>
+      <c r="AD26" s="384"/>
+      <c r="AF26" s="382"/>
+      <c r="AG26" s="383"/>
+      <c r="AH26" s="383"/>
+      <c r="AI26" s="383"/>
+      <c r="AJ26" s="384"/>
     </row>
     <row r="27" spans="2:75" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="131"/>
-      <c r="Z27" s="373"/>
-      <c r="AA27" s="374"/>
-      <c r="AB27" s="374"/>
-      <c r="AC27" s="374"/>
-      <c r="AD27" s="375"/>
-      <c r="AF27" s="373"/>
-      <c r="AG27" s="374"/>
-      <c r="AH27" s="374"/>
-      <c r="AI27" s="374"/>
-      <c r="AJ27" s="375"/>
+      <c r="Z27" s="382"/>
+      <c r="AA27" s="383"/>
+      <c r="AB27" s="383"/>
+      <c r="AC27" s="383"/>
+      <c r="AD27" s="384"/>
+      <c r="AF27" s="382"/>
+      <c r="AG27" s="383"/>
+      <c r="AH27" s="383"/>
+      <c r="AI27" s="383"/>
+      <c r="AJ27" s="384"/>
     </row>
     <row r="28" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B28" s="160" t="s">
@@ -42726,16 +42726,16 @@
       <c r="K28" s="184"/>
       <c r="L28" s="184"/>
       <c r="M28" s="184"/>
-      <c r="Z28" s="376"/>
-      <c r="AA28" s="377"/>
-      <c r="AB28" s="377"/>
-      <c r="AC28" s="377"/>
-      <c r="AD28" s="378"/>
-      <c r="AF28" s="376"/>
-      <c r="AG28" s="377"/>
-      <c r="AH28" s="377"/>
-      <c r="AI28" s="377"/>
-      <c r="AJ28" s="378"/>
+      <c r="Z28" s="385"/>
+      <c r="AA28" s="386"/>
+      <c r="AB28" s="386"/>
+      <c r="AC28" s="386"/>
+      <c r="AD28" s="387"/>
+      <c r="AF28" s="385"/>
+      <c r="AG28" s="386"/>
+      <c r="AH28" s="386"/>
+      <c r="AI28" s="386"/>
+      <c r="AJ28" s="387"/>
     </row>
     <row r="29" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B29" s="160" t="s">
@@ -42749,60 +42749,60 @@
       <c r="K29" s="185"/>
       <c r="L29" s="185"/>
       <c r="M29" s="185"/>
-      <c r="Z29" s="380" t="s">
+      <c r="Z29" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="AA29" s="380"/>
-      <c r="AB29" s="380"/>
-      <c r="AC29" s="380"/>
-      <c r="AD29" s="380"/>
-      <c r="AF29" s="380" t="s">
+      <c r="AA29" s="389"/>
+      <c r="AB29" s="389"/>
+      <c r="AC29" s="389"/>
+      <c r="AD29" s="389"/>
+      <c r="AF29" s="389" t="s">
         <v>205</v>
       </c>
-      <c r="AG29" s="380"/>
-      <c r="AH29" s="380"/>
-      <c r="AI29" s="380"/>
-      <c r="AJ29" s="380"/>
+      <c r="AG29" s="389"/>
+      <c r="AH29" s="389"/>
+      <c r="AI29" s="389"/>
+      <c r="AJ29" s="389"/>
     </row>
     <row r="32" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="384" t="s">
+      <c r="B32" s="369" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="385"/>
-      <c r="D32" s="385"/>
-      <c r="E32" s="385"/>
-      <c r="F32" s="385"/>
-      <c r="G32" s="385"/>
-      <c r="H32" s="385"/>
-      <c r="I32" s="385"/>
-      <c r="J32" s="385"/>
-      <c r="K32" s="385"/>
-      <c r="L32" s="385"/>
-      <c r="M32" s="385"/>
-      <c r="N32" s="385"/>
-      <c r="O32" s="385"/>
-      <c r="P32" s="385"/>
-      <c r="Q32" s="385"/>
-      <c r="R32" s="385"/>
-      <c r="S32" s="385"/>
-      <c r="T32" s="385"/>
-      <c r="U32" s="385"/>
-      <c r="V32" s="385"/>
-      <c r="W32" s="385"/>
-      <c r="X32" s="385"/>
-      <c r="Y32" s="385"/>
-      <c r="Z32" s="385"/>
-      <c r="AA32" s="385"/>
-      <c r="AB32" s="385"/>
-      <c r="AC32" s="385"/>
-      <c r="AD32" s="385"/>
-      <c r="AE32" s="385"/>
-      <c r="AF32" s="385"/>
-      <c r="AG32" s="385"/>
-      <c r="AH32" s="385"/>
-      <c r="AI32" s="385"/>
-      <c r="AJ32" s="385"/>
-      <c r="AK32" s="385"/>
+      <c r="C32" s="370"/>
+      <c r="D32" s="370"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
+      <c r="G32" s="370"/>
+      <c r="H32" s="370"/>
+      <c r="I32" s="370"/>
+      <c r="J32" s="370"/>
+      <c r="K32" s="370"/>
+      <c r="L32" s="370"/>
+      <c r="M32" s="370"/>
+      <c r="N32" s="370"/>
+      <c r="O32" s="370"/>
+      <c r="P32" s="370"/>
+      <c r="Q32" s="370"/>
+      <c r="R32" s="370"/>
+      <c r="S32" s="370"/>
+      <c r="T32" s="370"/>
+      <c r="U32" s="370"/>
+      <c r="V32" s="370"/>
+      <c r="W32" s="370"/>
+      <c r="X32" s="370"/>
+      <c r="Y32" s="370"/>
+      <c r="Z32" s="370"/>
+      <c r="AA32" s="370"/>
+      <c r="AB32" s="370"/>
+      <c r="AC32" s="370"/>
+      <c r="AD32" s="370"/>
+      <c r="AE32" s="370"/>
+      <c r="AF32" s="370"/>
+      <c r="AG32" s="370"/>
+      <c r="AH32" s="370"/>
+      <c r="AI32" s="370"/>
+      <c r="AJ32" s="370"/>
+      <c r="AK32" s="370"/>
     </row>
     <row r="34" spans="2:75" ht="20.100000000000001" customHeight="1">
       <c r="B34" s="186" t="s">
@@ -42836,44 +42836,44 @@
       <c r="H36" s="164"/>
     </row>
     <row r="37" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="390" t="s">
+      <c r="B37" s="375" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="390"/>
-      <c r="D37" s="390"/>
-      <c r="E37" s="390"/>
-      <c r="F37" s="390"/>
-      <c r="G37" s="390"/>
-      <c r="H37" s="390"/>
-      <c r="I37" s="390"/>
-      <c r="J37" s="390"/>
-      <c r="K37" s="390"/>
-      <c r="L37" s="390"/>
-      <c r="M37" s="390"/>
-      <c r="N37" s="390"/>
-      <c r="O37" s="390"/>
-      <c r="P37" s="390"/>
-      <c r="Q37" s="390"/>
-      <c r="R37" s="390"/>
-      <c r="S37" s="390"/>
-      <c r="T37" s="390"/>
-      <c r="U37" s="390"/>
-      <c r="V37" s="390"/>
-      <c r="W37" s="390"/>
-      <c r="X37" s="390"/>
-      <c r="Y37" s="390"/>
-      <c r="Z37" s="390"/>
-      <c r="AA37" s="390"/>
-      <c r="AB37" s="390"/>
-      <c r="AC37" s="390"/>
-      <c r="AD37" s="390"/>
-      <c r="AE37" s="390"/>
-      <c r="AF37" s="390"/>
-      <c r="AG37" s="390"/>
-      <c r="AH37" s="390"/>
-      <c r="AI37" s="390"/>
-      <c r="AJ37" s="390"/>
-      <c r="AK37" s="390"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
+      <c r="G37" s="375"/>
+      <c r="H37" s="375"/>
+      <c r="I37" s="375"/>
+      <c r="J37" s="375"/>
+      <c r="K37" s="375"/>
+      <c r="L37" s="375"/>
+      <c r="M37" s="375"/>
+      <c r="N37" s="375"/>
+      <c r="O37" s="375"/>
+      <c r="P37" s="375"/>
+      <c r="Q37" s="375"/>
+      <c r="R37" s="375"/>
+      <c r="S37" s="375"/>
+      <c r="T37" s="375"/>
+      <c r="U37" s="375"/>
+      <c r="V37" s="375"/>
+      <c r="W37" s="375"/>
+      <c r="X37" s="375"/>
+      <c r="Y37" s="375"/>
+      <c r="Z37" s="375"/>
+      <c r="AA37" s="375"/>
+      <c r="AB37" s="375"/>
+      <c r="AC37" s="375"/>
+      <c r="AD37" s="375"/>
+      <c r="AE37" s="375"/>
+      <c r="AF37" s="375"/>
+      <c r="AG37" s="375"/>
+      <c r="AH37" s="375"/>
+      <c r="AI37" s="375"/>
+      <c r="AJ37" s="375"/>
+      <c r="AK37" s="375"/>
       <c r="AN37" s="164"/>
       <c r="AO37" s="172"/>
       <c r="AP37" s="164"/>
@@ -42895,44 +42895,44 @@
       <c r="BW37" s="188"/>
     </row>
     <row r="38" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B38" s="391" t="s">
+      <c r="B38" s="376" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="391"/>
-      <c r="D38" s="391"/>
-      <c r="E38" s="391"/>
-      <c r="F38" s="391"/>
-      <c r="G38" s="391"/>
-      <c r="H38" s="391"/>
-      <c r="I38" s="391"/>
-      <c r="J38" s="391"/>
-      <c r="K38" s="391"/>
-      <c r="L38" s="391"/>
-      <c r="M38" s="391"/>
-      <c r="N38" s="391"/>
-      <c r="O38" s="391"/>
-      <c r="P38" s="391"/>
-      <c r="Q38" s="391"/>
-      <c r="R38" s="391"/>
-      <c r="S38" s="391"/>
-      <c r="T38" s="391"/>
-      <c r="U38" s="391"/>
-      <c r="V38" s="391"/>
-      <c r="W38" s="391"/>
-      <c r="X38" s="391"/>
-      <c r="Y38" s="391"/>
-      <c r="Z38" s="391"/>
-      <c r="AA38" s="391"/>
-      <c r="AB38" s="391"/>
-      <c r="AC38" s="391"/>
-      <c r="AD38" s="391"/>
-      <c r="AE38" s="391"/>
-      <c r="AF38" s="391"/>
-      <c r="AG38" s="391"/>
-      <c r="AH38" s="391"/>
-      <c r="AI38" s="391"/>
-      <c r="AJ38" s="391"/>
-      <c r="AK38" s="391"/>
+      <c r="C38" s="376"/>
+      <c r="D38" s="376"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
+      <c r="G38" s="376"/>
+      <c r="H38" s="376"/>
+      <c r="I38" s="376"/>
+      <c r="J38" s="376"/>
+      <c r="K38" s="376"/>
+      <c r="L38" s="376"/>
+      <c r="M38" s="376"/>
+      <c r="N38" s="376"/>
+      <c r="O38" s="376"/>
+      <c r="P38" s="376"/>
+      <c r="Q38" s="376"/>
+      <c r="R38" s="376"/>
+      <c r="S38" s="376"/>
+      <c r="T38" s="376"/>
+      <c r="U38" s="376"/>
+      <c r="V38" s="376"/>
+      <c r="W38" s="376"/>
+      <c r="X38" s="376"/>
+      <c r="Y38" s="376"/>
+      <c r="Z38" s="376"/>
+      <c r="AA38" s="376"/>
+      <c r="AB38" s="376"/>
+      <c r="AC38" s="376"/>
+      <c r="AD38" s="376"/>
+      <c r="AE38" s="376"/>
+      <c r="AF38" s="376"/>
+      <c r="AG38" s="376"/>
+      <c r="AH38" s="376"/>
+      <c r="AI38" s="376"/>
+      <c r="AJ38" s="376"/>
+      <c r="AK38" s="376"/>
       <c r="AN38" s="172"/>
       <c r="AO38" s="172"/>
       <c r="AP38" s="172"/>
@@ -42971,42 +42971,42 @@
       <c r="BW38" s="187"/>
     </row>
     <row r="39" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="391"/>
-      <c r="C39" s="391"/>
-      <c r="D39" s="391"/>
-      <c r="E39" s="391"/>
-      <c r="F39" s="391"/>
-      <c r="G39" s="391"/>
-      <c r="H39" s="391"/>
-      <c r="I39" s="391"/>
-      <c r="J39" s="391"/>
-      <c r="K39" s="391"/>
-      <c r="L39" s="391"/>
-      <c r="M39" s="391"/>
-      <c r="N39" s="391"/>
-      <c r="O39" s="391"/>
-      <c r="P39" s="391"/>
-      <c r="Q39" s="391"/>
-      <c r="R39" s="391"/>
-      <c r="S39" s="391"/>
-      <c r="T39" s="391"/>
-      <c r="U39" s="391"/>
-      <c r="V39" s="391"/>
-      <c r="W39" s="391"/>
-      <c r="X39" s="391"/>
-      <c r="Y39" s="391"/>
-      <c r="Z39" s="391"/>
-      <c r="AA39" s="391"/>
-      <c r="AB39" s="391"/>
-      <c r="AC39" s="391"/>
-      <c r="AD39" s="391"/>
-      <c r="AE39" s="391"/>
-      <c r="AF39" s="391"/>
-      <c r="AG39" s="391"/>
-      <c r="AH39" s="391"/>
-      <c r="AI39" s="391"/>
-      <c r="AJ39" s="391"/>
-      <c r="AK39" s="391"/>
+      <c r="B39" s="376"/>
+      <c r="C39" s="376"/>
+      <c r="D39" s="376"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
+      <c r="G39" s="376"/>
+      <c r="H39" s="376"/>
+      <c r="I39" s="376"/>
+      <c r="J39" s="376"/>
+      <c r="K39" s="376"/>
+      <c r="L39" s="376"/>
+      <c r="M39" s="376"/>
+      <c r="N39" s="376"/>
+      <c r="O39" s="376"/>
+      <c r="P39" s="376"/>
+      <c r="Q39" s="376"/>
+      <c r="R39" s="376"/>
+      <c r="S39" s="376"/>
+      <c r="T39" s="376"/>
+      <c r="U39" s="376"/>
+      <c r="V39" s="376"/>
+      <c r="W39" s="376"/>
+      <c r="X39" s="376"/>
+      <c r="Y39" s="376"/>
+      <c r="Z39" s="376"/>
+      <c r="AA39" s="376"/>
+      <c r="AB39" s="376"/>
+      <c r="AC39" s="376"/>
+      <c r="AD39" s="376"/>
+      <c r="AE39" s="376"/>
+      <c r="AF39" s="376"/>
+      <c r="AG39" s="376"/>
+      <c r="AH39" s="376"/>
+      <c r="AI39" s="376"/>
+      <c r="AJ39" s="376"/>
+      <c r="AK39" s="376"/>
       <c r="AN39" s="164"/>
       <c r="AO39" s="164"/>
       <c r="AP39" s="164"/>
@@ -43016,42 +43016,42 @@
       <c r="AT39" s="164"/>
     </row>
     <row r="40" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="391"/>
-      <c r="C40" s="391"/>
-      <c r="D40" s="391"/>
-      <c r="E40" s="391"/>
-      <c r="F40" s="391"/>
-      <c r="G40" s="391"/>
-      <c r="H40" s="391"/>
-      <c r="I40" s="391"/>
-      <c r="J40" s="391"/>
-      <c r="K40" s="391"/>
-      <c r="L40" s="391"/>
-      <c r="M40" s="391"/>
-      <c r="N40" s="391"/>
-      <c r="O40" s="391"/>
-      <c r="P40" s="391"/>
-      <c r="Q40" s="391"/>
-      <c r="R40" s="391"/>
-      <c r="S40" s="391"/>
-      <c r="T40" s="391"/>
-      <c r="U40" s="391"/>
-      <c r="V40" s="391"/>
-      <c r="W40" s="391"/>
-      <c r="X40" s="391"/>
-      <c r="Y40" s="391"/>
-      <c r="Z40" s="391"/>
-      <c r="AA40" s="391"/>
-      <c r="AB40" s="391"/>
-      <c r="AC40" s="391"/>
-      <c r="AD40" s="391"/>
-      <c r="AE40" s="391"/>
-      <c r="AF40" s="391"/>
-      <c r="AG40" s="391"/>
-      <c r="AH40" s="391"/>
-      <c r="AI40" s="391"/>
-      <c r="AJ40" s="391"/>
-      <c r="AK40" s="391"/>
+      <c r="B40" s="376"/>
+      <c r="C40" s="376"/>
+      <c r="D40" s="376"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
+      <c r="G40" s="376"/>
+      <c r="H40" s="376"/>
+      <c r="I40" s="376"/>
+      <c r="J40" s="376"/>
+      <c r="K40" s="376"/>
+      <c r="L40" s="376"/>
+      <c r="M40" s="376"/>
+      <c r="N40" s="376"/>
+      <c r="O40" s="376"/>
+      <c r="P40" s="376"/>
+      <c r="Q40" s="376"/>
+      <c r="R40" s="376"/>
+      <c r="S40" s="376"/>
+      <c r="T40" s="376"/>
+      <c r="U40" s="376"/>
+      <c r="V40" s="376"/>
+      <c r="W40" s="376"/>
+      <c r="X40" s="376"/>
+      <c r="Y40" s="376"/>
+      <c r="Z40" s="376"/>
+      <c r="AA40" s="376"/>
+      <c r="AB40" s="376"/>
+      <c r="AC40" s="376"/>
+      <c r="AD40" s="376"/>
+      <c r="AE40" s="376"/>
+      <c r="AF40" s="376"/>
+      <c r="AG40" s="376"/>
+      <c r="AH40" s="376"/>
+      <c r="AI40" s="376"/>
+      <c r="AJ40" s="376"/>
+      <c r="AK40" s="376"/>
       <c r="AN40" s="164"/>
       <c r="AO40" s="164"/>
       <c r="AP40" s="164"/>
@@ -43086,9 +43086,9 @@
       </c>
       <c r="C43" s="164"/>
       <c r="D43" s="164"/>
-      <c r="E43" s="392"/>
-      <c r="F43" s="392"/>
-      <c r="G43" s="392"/>
+      <c r="E43" s="377"/>
+      <c r="F43" s="377"/>
+      <c r="G43" s="377"/>
       <c r="H43" s="164"/>
     </row>
     <row r="44" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -43097,9 +43097,9 @@
       </c>
       <c r="C44" s="164"/>
       <c r="D44" s="164"/>
-      <c r="E44" s="383"/>
-      <c r="F44" s="383"/>
-      <c r="G44" s="383"/>
+      <c r="E44" s="368"/>
+      <c r="F44" s="368"/>
+      <c r="G44" s="368"/>
       <c r="H44" s="164"/>
     </row>
     <row r="45" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -43108,9 +43108,9 @@
       </c>
       <c r="C45" s="164"/>
       <c r="D45" s="164"/>
-      <c r="E45" s="383"/>
-      <c r="F45" s="383"/>
-      <c r="G45" s="383"/>
+      <c r="E45" s="368"/>
+      <c r="F45" s="368"/>
+      <c r="G45" s="368"/>
       <c r="H45" s="164"/>
     </row>
     <row r="46" spans="2:75" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -43119,9 +43119,9 @@
       </c>
       <c r="C46" s="164"/>
       <c r="D46" s="164"/>
-      <c r="E46" s="383"/>
-      <c r="F46" s="383"/>
-      <c r="G46" s="383"/>
+      <c r="E46" s="368"/>
+      <c r="F46" s="368"/>
+      <c r="G46" s="368"/>
       <c r="H46" s="164"/>
     </row>
     <row r="47" spans="2:75" ht="20.100000000000001" customHeight="1">
@@ -43131,44 +43131,44 @@
       <c r="G47" s="191"/>
     </row>
     <row r="48" spans="2:75" ht="20.100000000000001" customHeight="1">
-      <c r="B48" s="384" t="s">
+      <c r="B48" s="369" t="s">
         <v>216</v>
       </c>
-      <c r="C48" s="385"/>
-      <c r="D48" s="385"/>
-      <c r="E48" s="385"/>
-      <c r="F48" s="385"/>
-      <c r="G48" s="385"/>
-      <c r="H48" s="385"/>
-      <c r="I48" s="385"/>
-      <c r="J48" s="385"/>
-      <c r="K48" s="385"/>
-      <c r="L48" s="385"/>
-      <c r="M48" s="385"/>
-      <c r="N48" s="385"/>
-      <c r="O48" s="385"/>
-      <c r="P48" s="385"/>
-      <c r="Q48" s="385"/>
-      <c r="R48" s="385"/>
-      <c r="S48" s="385"/>
-      <c r="T48" s="385"/>
-      <c r="U48" s="385"/>
-      <c r="V48" s="385"/>
-      <c r="W48" s="385"/>
-      <c r="X48" s="385"/>
-      <c r="Y48" s="385"/>
-      <c r="Z48" s="385"/>
-      <c r="AA48" s="385"/>
-      <c r="AB48" s="385"/>
-      <c r="AC48" s="385"/>
-      <c r="AD48" s="385"/>
-      <c r="AE48" s="385"/>
-      <c r="AF48" s="385"/>
-      <c r="AG48" s="385"/>
-      <c r="AH48" s="385"/>
-      <c r="AI48" s="385"/>
-      <c r="AJ48" s="385"/>
-      <c r="AK48" s="385"/>
+      <c r="C48" s="370"/>
+      <c r="D48" s="370"/>
+      <c r="E48" s="370"/>
+      <c r="F48" s="370"/>
+      <c r="G48" s="370"/>
+      <c r="H48" s="370"/>
+      <c r="I48" s="370"/>
+      <c r="J48" s="370"/>
+      <c r="K48" s="370"/>
+      <c r="L48" s="370"/>
+      <c r="M48" s="370"/>
+      <c r="N48" s="370"/>
+      <c r="O48" s="370"/>
+      <c r="P48" s="370"/>
+      <c r="Q48" s="370"/>
+      <c r="R48" s="370"/>
+      <c r="S48" s="370"/>
+      <c r="T48" s="370"/>
+      <c r="U48" s="370"/>
+      <c r="V48" s="370"/>
+      <c r="W48" s="370"/>
+      <c r="X48" s="370"/>
+      <c r="Y48" s="370"/>
+      <c r="Z48" s="370"/>
+      <c r="AA48" s="370"/>
+      <c r="AB48" s="370"/>
+      <c r="AC48" s="370"/>
+      <c r="AD48" s="370"/>
+      <c r="AE48" s="370"/>
+      <c r="AF48" s="370"/>
+      <c r="AG48" s="370"/>
+      <c r="AH48" s="370"/>
+      <c r="AI48" s="370"/>
+      <c r="AJ48" s="370"/>
+      <c r="AK48" s="370"/>
     </row>
     <row r="49" spans="2:37" ht="20.100000000000001" customHeight="1">
       <c r="B49" s="192"/>
@@ -43226,34 +43226,34 @@
       </c>
       <c r="C52" s="164"/>
       <c r="G52" s="184"/>
-      <c r="H52" s="389">
+      <c r="H52" s="374">
         <f>'YADAO, MELENCIO'!C1</f>
-        <v>2000.0040005269973</v>
-      </c>
-      <c r="I52" s="389"/>
+        <v>949.99785840431502</v>
+      </c>
+      <c r="I52" s="374"/>
       <c r="J52" s="195"/>
       <c r="K52" s="195"/>
       <c r="L52" s="195"/>
       <c r="M52" s="187" t="s">
         <v>220</v>
       </c>
-      <c r="R52" s="386">
+      <c r="R52" s="371">
         <v>24</v>
       </c>
-      <c r="S52" s="386"/>
+      <c r="S52" s="371"/>
       <c r="T52" s="187" t="s">
         <v>221</v>
       </c>
       <c r="AA52" s="184"/>
       <c r="AB52" s="184"/>
-      <c r="AC52" s="387">
+      <c r="AC52" s="372">
         <f>'YADAO, MELENCIO'!C3</f>
-        <v>48000.096012647933</v>
-      </c>
-      <c r="AD52" s="388"/>
-      <c r="AE52" s="388"/>
-      <c r="AF52" s="388"/>
-      <c r="AG52" s="388"/>
+        <v>22799.94860170356</v>
+      </c>
+      <c r="AD52" s="373"/>
+      <c r="AE52" s="373"/>
+      <c r="AF52" s="373"/>
+      <c r="AG52" s="373"/>
       <c r="AH52" s="187" t="s">
         <v>222</v>
       </c>
@@ -43288,44 +43288,44 @@
       <c r="Y56" s="184"/>
     </row>
     <row r="57" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B57" s="382" t="s">
+      <c r="B57" s="366" t="s">
         <v>225</v>
       </c>
-      <c r="C57" s="382"/>
-      <c r="D57" s="382"/>
-      <c r="E57" s="382"/>
-      <c r="F57" s="382"/>
-      <c r="G57" s="382"/>
-      <c r="H57" s="382"/>
-      <c r="I57" s="382"/>
-      <c r="J57" s="382"/>
-      <c r="K57" s="382"/>
-      <c r="L57" s="382"/>
-      <c r="M57" s="382"/>
-      <c r="N57" s="382"/>
-      <c r="O57" s="382"/>
-      <c r="P57" s="382"/>
-      <c r="Q57" s="382"/>
-      <c r="R57" s="382"/>
-      <c r="S57" s="382"/>
-      <c r="T57" s="382"/>
-      <c r="U57" s="382"/>
-      <c r="V57" s="382"/>
-      <c r="W57" s="382"/>
-      <c r="X57" s="382"/>
-      <c r="Y57" s="382"/>
-      <c r="Z57" s="382"/>
-      <c r="AA57" s="382"/>
-      <c r="AB57" s="382"/>
-      <c r="AC57" s="382"/>
-      <c r="AD57" s="382"/>
-      <c r="AE57" s="382"/>
-      <c r="AF57" s="382"/>
-      <c r="AG57" s="382"/>
-      <c r="AH57" s="382"/>
-      <c r="AI57" s="382"/>
-      <c r="AJ57" s="382"/>
-      <c r="AK57" s="382"/>
+      <c r="C57" s="366"/>
+      <c r="D57" s="366"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
+      <c r="G57" s="366"/>
+      <c r="H57" s="366"/>
+      <c r="I57" s="366"/>
+      <c r="J57" s="366"/>
+      <c r="K57" s="366"/>
+      <c r="L57" s="366"/>
+      <c r="M57" s="366"/>
+      <c r="N57" s="366"/>
+      <c r="O57" s="366"/>
+      <c r="P57" s="366"/>
+      <c r="Q57" s="366"/>
+      <c r="R57" s="366"/>
+      <c r="S57" s="366"/>
+      <c r="T57" s="366"/>
+      <c r="U57" s="366"/>
+      <c r="V57" s="366"/>
+      <c r="W57" s="366"/>
+      <c r="X57" s="366"/>
+      <c r="Y57" s="366"/>
+      <c r="Z57" s="366"/>
+      <c r="AA57" s="366"/>
+      <c r="AB57" s="366"/>
+      <c r="AC57" s="366"/>
+      <c r="AD57" s="366"/>
+      <c r="AE57" s="366"/>
+      <c r="AF57" s="366"/>
+      <c r="AG57" s="366"/>
+      <c r="AH57" s="366"/>
+      <c r="AI57" s="366"/>
+      <c r="AJ57" s="366"/>
+      <c r="AK57" s="366"/>
     </row>
     <row r="58" spans="2:37" ht="20.100000000000001" customHeight="1">
       <c r="B58" s="196"/>
@@ -43366,44 +43366,44 @@
       <c r="AK58" s="196"/>
     </row>
     <row r="59" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B59" s="384" t="s">
+      <c r="B59" s="369" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="385"/>
-      <c r="D59" s="385"/>
-      <c r="E59" s="385"/>
-      <c r="F59" s="385"/>
-      <c r="G59" s="385"/>
-      <c r="H59" s="385"/>
-      <c r="I59" s="385"/>
-      <c r="J59" s="385"/>
-      <c r="K59" s="385"/>
-      <c r="L59" s="385"/>
-      <c r="M59" s="385"/>
-      <c r="N59" s="385"/>
-      <c r="O59" s="385"/>
-      <c r="P59" s="385"/>
-      <c r="Q59" s="385"/>
-      <c r="R59" s="385"/>
-      <c r="S59" s="385"/>
-      <c r="T59" s="385"/>
-      <c r="U59" s="385"/>
-      <c r="V59" s="385"/>
-      <c r="W59" s="385"/>
-      <c r="X59" s="385"/>
-      <c r="Y59" s="385"/>
-      <c r="Z59" s="385"/>
-      <c r="AA59" s="385"/>
-      <c r="AB59" s="385"/>
-      <c r="AC59" s="385"/>
-      <c r="AD59" s="385"/>
-      <c r="AE59" s="385"/>
-      <c r="AF59" s="385"/>
-      <c r="AG59" s="385"/>
-      <c r="AH59" s="385"/>
-      <c r="AI59" s="385"/>
-      <c r="AJ59" s="385"/>
-      <c r="AK59" s="385"/>
+      <c r="C59" s="370"/>
+      <c r="D59" s="370"/>
+      <c r="E59" s="370"/>
+      <c r="F59" s="370"/>
+      <c r="G59" s="370"/>
+      <c r="H59" s="370"/>
+      <c r="I59" s="370"/>
+      <c r="J59" s="370"/>
+      <c r="K59" s="370"/>
+      <c r="L59" s="370"/>
+      <c r="M59" s="370"/>
+      <c r="N59" s="370"/>
+      <c r="O59" s="370"/>
+      <c r="P59" s="370"/>
+      <c r="Q59" s="370"/>
+      <c r="R59" s="370"/>
+      <c r="S59" s="370"/>
+      <c r="T59" s="370"/>
+      <c r="U59" s="370"/>
+      <c r="V59" s="370"/>
+      <c r="W59" s="370"/>
+      <c r="X59" s="370"/>
+      <c r="Y59" s="370"/>
+      <c r="Z59" s="370"/>
+      <c r="AA59" s="370"/>
+      <c r="AB59" s="370"/>
+      <c r="AC59" s="370"/>
+      <c r="AD59" s="370"/>
+      <c r="AE59" s="370"/>
+      <c r="AF59" s="370"/>
+      <c r="AG59" s="370"/>
+      <c r="AH59" s="370"/>
+      <c r="AI59" s="370"/>
+      <c r="AJ59" s="370"/>
+      <c r="AK59" s="370"/>
     </row>
     <row r="61" spans="2:37" ht="20.100000000000001" customHeight="1">
       <c r="B61" s="164"/>
@@ -43446,44 +43446,44 @@
       <c r="AC64" s="184"/>
     </row>
     <row r="65" spans="2:37" ht="20.100000000000001" customHeight="1">
-      <c r="B65" s="382" t="s">
+      <c r="B65" s="366" t="s">
         <v>229</v>
       </c>
-      <c r="C65" s="382"/>
-      <c r="D65" s="382"/>
-      <c r="E65" s="382"/>
-      <c r="F65" s="382"/>
-      <c r="G65" s="382"/>
-      <c r="H65" s="382"/>
-      <c r="I65" s="382"/>
-      <c r="J65" s="382"/>
-      <c r="K65" s="382"/>
-      <c r="L65" s="382"/>
-      <c r="M65" s="382"/>
-      <c r="N65" s="382"/>
-      <c r="O65" s="382"/>
-      <c r="P65" s="382"/>
-      <c r="Q65" s="382"/>
-      <c r="R65" s="382"/>
-      <c r="S65" s="382"/>
-      <c r="T65" s="382"/>
-      <c r="U65" s="382"/>
-      <c r="V65" s="382"/>
-      <c r="W65" s="382"/>
-      <c r="X65" s="382"/>
-      <c r="Y65" s="382"/>
-      <c r="Z65" s="382"/>
-      <c r="AA65" s="382"/>
-      <c r="AB65" s="382"/>
-      <c r="AC65" s="382"/>
-      <c r="AD65" s="382"/>
-      <c r="AE65" s="382"/>
-      <c r="AF65" s="382"/>
-      <c r="AG65" s="382"/>
-      <c r="AH65" s="382"/>
-      <c r="AI65" s="382"/>
-      <c r="AJ65" s="382"/>
-      <c r="AK65" s="382"/>
+      <c r="C65" s="366"/>
+      <c r="D65" s="366"/>
+      <c r="E65" s="366"/>
+      <c r="F65" s="366"/>
+      <c r="G65" s="366"/>
+      <c r="H65" s="366"/>
+      <c r="I65" s="366"/>
+      <c r="J65" s="366"/>
+      <c r="K65" s="366"/>
+      <c r="L65" s="366"/>
+      <c r="M65" s="366"/>
+      <c r="N65" s="366"/>
+      <c r="O65" s="366"/>
+      <c r="P65" s="366"/>
+      <c r="Q65" s="366"/>
+      <c r="R65" s="366"/>
+      <c r="S65" s="366"/>
+      <c r="T65" s="366"/>
+      <c r="U65" s="366"/>
+      <c r="V65" s="366"/>
+      <c r="W65" s="366"/>
+      <c r="X65" s="366"/>
+      <c r="Y65" s="366"/>
+      <c r="Z65" s="366"/>
+      <c r="AA65" s="366"/>
+      <c r="AB65" s="366"/>
+      <c r="AC65" s="366"/>
+      <c r="AD65" s="366"/>
+      <c r="AE65" s="366"/>
+      <c r="AF65" s="366"/>
+      <c r="AG65" s="366"/>
+      <c r="AH65" s="366"/>
+      <c r="AI65" s="366"/>
+      <c r="AJ65" s="366"/>
+      <c r="AK65" s="366"/>
     </row>
     <row r="69" spans="2:37" ht="20.100000000000001" customHeight="1">
       <c r="Y69" s="131"/>
@@ -43521,6 +43521,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="B7:AK9"/>
+    <mergeCell ref="B10:AK12"/>
+    <mergeCell ref="B13:AK17"/>
+    <mergeCell ref="C3:AL3"/>
+    <mergeCell ref="V4:AL4"/>
+    <mergeCell ref="B6:AL6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:AL5"/>
+    <mergeCell ref="G4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Z22:AD28"/>
+    <mergeCell ref="AF22:AJ28"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="Z29:AD29"/>
+    <mergeCell ref="AF29:AJ29"/>
+    <mergeCell ref="D25:L25"/>
     <mergeCell ref="B65:AK65"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E46:G46"/>
@@ -43537,24 +43555,6 @@
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B18:AK21"/>
-    <mergeCell ref="Z22:AD28"/>
-    <mergeCell ref="AF22:AJ28"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="Z29:AD29"/>
-    <mergeCell ref="AF29:AJ29"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="B7:AK9"/>
-    <mergeCell ref="B10:AK12"/>
-    <mergeCell ref="B13:AK17"/>
-    <mergeCell ref="C3:AL3"/>
-    <mergeCell ref="V4:AL4"/>
-    <mergeCell ref="B6:AL6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:AL5"/>
-    <mergeCell ref="G4:S4"/>
-    <mergeCell ref="T4:U4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
